--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="F14" t="n">
-        <v>14.22</v>
+        <v>14.98</v>
       </c>
       <c r="G14" t="n">
-        <v>268</v>
+        <v>287.1</v>
       </c>
       <c r="H14" t="n">
-        <v>94.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>0.76</v>
+        <v>185.3</v>
       </c>
       <c r="K14" t="n">
-        <v>116.95</v>
+        <v>349.21</v>
       </c>
       <c r="L14" t="n">
-        <v>116.95</v>
+        <v>395.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:06:32</t>
+          <t>08:07:16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.21</v>
+        <v>4.69</v>
       </c>
       <c r="F15" t="n">
-        <v>15.65</v>
+        <v>14.42</v>
       </c>
       <c r="G15" t="n">
-        <v>300.6</v>
+        <v>282.3</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>216.72</v>
+        <v>190.01</v>
       </c>
       <c r="K15" t="n">
-        <v>-124.43</v>
+        <v>27.86</v>
       </c>
       <c r="L15" t="n">
-        <v>249.91</v>
+        <v>192.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:07:56</t>
+          <t>08:08:38</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>6.01</v>
+        <v>5.36</v>
       </c>
       <c r="F16" t="n">
-        <v>14.07</v>
+        <v>14.54</v>
       </c>
       <c r="G16" t="n">
-        <v>276.7</v>
+        <v>280.4</v>
       </c>
       <c r="H16" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>257.93</v>
+        <v>28.54</v>
       </c>
       <c r="K16" t="n">
-        <v>-93.56</v>
+        <v>181.82</v>
       </c>
       <c r="L16" t="n">
-        <v>274.37</v>
+        <v>184.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:11:45</t>
+          <t>08:13:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.87</v>
+        <v>5.67</v>
       </c>
       <c r="F17" t="n">
-        <v>15.24</v>
+        <v>15.03</v>
       </c>
       <c r="G17" t="n">
-        <v>284.4</v>
+        <v>282</v>
       </c>
       <c r="H17" t="n">
-        <v>96.3</v>
+        <v>91</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>164.05</v>
+        <v>-165.3</v>
       </c>
       <c r="K17" t="n">
-        <v>-63.36</v>
+        <v>-182.51</v>
       </c>
       <c r="L17" t="n">
-        <v>175.86</v>
+        <v>246.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:13:20</t>
+          <t>08:15:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.23</v>
+        <v>5.47</v>
       </c>
       <c r="F18" t="n">
-        <v>14.55</v>
+        <v>14.86</v>
       </c>
       <c r="G18" t="n">
-        <v>285.2</v>
+        <v>265.8</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-54.83</v>
+        <v>116.06</v>
       </c>
       <c r="K18" t="n">
-        <v>130.11</v>
+        <v>-40.53</v>
       </c>
       <c r="L18" t="n">
-        <v>141.19</v>
+        <v>122.93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:14:08</t>
+          <t>08:17:09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.35</v>
+        <v>5.02</v>
       </c>
       <c r="F19" t="n">
-        <v>14.61</v>
+        <v>14.15</v>
       </c>
       <c r="G19" t="n">
-        <v>293.4</v>
+        <v>276.1</v>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>96.7</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>52.86</v>
+        <v>193.28</v>
       </c>
       <c r="K19" t="n">
-        <v>229.54</v>
+        <v>108.25</v>
       </c>
       <c r="L19" t="n">
-        <v>235.55</v>
+        <v>221.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:17:40</t>
+          <t>08:22:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.31</v>
+        <v>5.16</v>
       </c>
       <c r="F20" t="n">
-        <v>14.99</v>
+        <v>14.27</v>
       </c>
       <c r="G20" t="n">
         <v>290.3</v>
       </c>
       <c r="H20" t="n">
-        <v>96.5</v>
+        <v>92.8</v>
       </c>
       <c r="I20" t="n">
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>239.79</v>
+        <v>132.29</v>
       </c>
       <c r="K20" t="n">
-        <v>280.11</v>
+        <v>327.5</v>
       </c>
       <c r="L20" t="n">
-        <v>368.73</v>
+        <v>353.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:18:26</t>
+          <t>08:24:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.48</v>
+        <v>5.98</v>
       </c>
       <c r="F21" t="n">
-        <v>15.08</v>
+        <v>14.45</v>
       </c>
       <c r="G21" t="n">
-        <v>281</v>
+        <v>284.1</v>
       </c>
       <c r="H21" t="n">
-        <v>89.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>162.94</v>
+        <v>-109.65</v>
       </c>
       <c r="K21" t="n">
-        <v>-379.5</v>
+        <v>-184.03</v>
       </c>
       <c r="L21" t="n">
-        <v>413</v>
+        <v>214.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:19:56</t>
+          <t>08:25:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.7</v>
+        <v>6.02</v>
       </c>
       <c r="F22" t="n">
-        <v>14.68</v>
+        <v>14.27</v>
       </c>
       <c r="G22" t="n">
-        <v>275.2</v>
+        <v>274.2</v>
       </c>
       <c r="H22" t="n">
-        <v>92.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>150.96</v>
+        <v>139.76</v>
       </c>
       <c r="K22" t="n">
-        <v>237.12</v>
+        <v>-297.74</v>
       </c>
       <c r="L22" t="n">
-        <v>281.1</v>
+        <v>328.91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:26:20</t>
+          <t>08:31:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.58</v>
+        <v>4.67</v>
       </c>
       <c r="F23" t="n">
-        <v>14.48</v>
+        <v>14.63</v>
       </c>
       <c r="G23" t="n">
-        <v>281.7</v>
+        <v>293.5</v>
       </c>
       <c r="H23" t="n">
-        <v>98.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>309.28</v>
+        <v>-77.63</v>
       </c>
       <c r="K23" t="n">
-        <v>-99.95999999999999</v>
+        <v>369.05</v>
       </c>
       <c r="L23" t="n">
-        <v>325.03</v>
+        <v>377.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:27:33</t>
+          <t>08:33:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5.43</v>
+        <v>5.31</v>
       </c>
       <c r="F24" t="n">
-        <v>14.52</v>
+        <v>14.51</v>
       </c>
       <c r="G24" t="n">
-        <v>290.4</v>
+        <v>276.7</v>
       </c>
       <c r="H24" t="n">
-        <v>95.5</v>
+        <v>91.8</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>461.44</v>
+        <v>-19.82</v>
       </c>
       <c r="K24" t="n">
-        <v>176.81</v>
+        <v>-156.86</v>
       </c>
       <c r="L24" t="n">
-        <v>494.15</v>
+        <v>158.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:29:11</t>
+          <t>08:34:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.58</v>
+        <v>5.68</v>
       </c>
       <c r="F25" t="n">
-        <v>14.43</v>
+        <v>15.36</v>
       </c>
       <c r="G25" t="n">
-        <v>277.5</v>
+        <v>295.1</v>
       </c>
       <c r="H25" t="n">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>116.02</v>
+        <v>-238.03</v>
       </c>
       <c r="K25" t="n">
-        <v>-51.09</v>
+        <v>253.09</v>
       </c>
       <c r="L25" t="n">
-        <v>126.77</v>
+        <v>347.44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:32:09</t>
+          <t>08:38:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
       <c r="F26" t="n">
-        <v>15.82</v>
+        <v>14.01</v>
       </c>
       <c r="G26" t="n">
-        <v>281.1</v>
+        <v>281.3</v>
       </c>
       <c r="H26" t="n">
-        <v>97.3</v>
+        <v>98.8</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>142.84</v>
+        <v>-284.48</v>
       </c>
       <c r="K26" t="n">
-        <v>-490.29</v>
+        <v>37.88</v>
       </c>
       <c r="L26" t="n">
-        <v>510.67</v>
+        <v>286.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:33:47</t>
+          <t>08:40:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.41</v>
+        <v>5.64</v>
       </c>
       <c r="F27" t="n">
-        <v>14.02</v>
+        <v>15.1</v>
       </c>
       <c r="G27" t="n">
-        <v>281.3</v>
+        <v>276.2</v>
       </c>
       <c r="H27" t="n">
-        <v>92.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-734.4</v>
+        <v>-306.15</v>
       </c>
       <c r="K27" t="n">
-        <v>-29.81</v>
+        <v>556.46</v>
       </c>
       <c r="L27" t="n">
-        <v>735.01</v>
+        <v>635.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:35:54</t>
+          <t>08:43:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.72</v>
+        <v>6.27</v>
       </c>
       <c r="F28" t="n">
-        <v>14.4</v>
+        <v>14.71</v>
       </c>
       <c r="G28" t="n">
-        <v>278.4</v>
+        <v>287.1</v>
       </c>
       <c r="H28" t="n">
-        <v>94.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-290.26</v>
+        <v>-92.31</v>
       </c>
       <c r="K28" t="n">
-        <v>31.38</v>
+        <v>727.89</v>
       </c>
       <c r="L28" t="n">
-        <v>291.95</v>
+        <v>733.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:44:11</t>
+          <t>08:53:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.49</v>
+        <v>6.21</v>
       </c>
       <c r="F29" t="n">
-        <v>14.99</v>
+        <v>13.95</v>
       </c>
       <c r="G29" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="H29" t="n">
-        <v>89.2</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-175.75</v>
+        <v>2.64</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.12</v>
+        <v>275.44</v>
       </c>
       <c r="L29" t="n">
-        <v>175.82</v>
+        <v>275.45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:45:30</t>
+          <t>08:54:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="F30" t="n">
-        <v>14.42</v>
+        <v>14.63</v>
       </c>
       <c r="G30" t="n">
-        <v>284.5</v>
+        <v>291.9</v>
       </c>
       <c r="H30" t="n">
-        <v>96.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-217.06</v>
+        <v>364.07</v>
       </c>
       <c r="K30" t="n">
-        <v>77.16</v>
+        <v>188.66</v>
       </c>
       <c r="L30" t="n">
-        <v>230.36</v>
+        <v>410.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:47:29</t>
+          <t>08:56:31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.46</v>
+        <v>5.9</v>
       </c>
       <c r="F31" t="n">
-        <v>14.85</v>
+        <v>15.13</v>
       </c>
       <c r="G31" t="n">
-        <v>265.7</v>
+        <v>268.4</v>
       </c>
       <c r="H31" t="n">
-        <v>97.2</v>
+        <v>99.2</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-110.65</v>
+        <v>241.36</v>
       </c>
       <c r="K31" t="n">
-        <v>-55.17</v>
+        <v>-136.5</v>
       </c>
       <c r="L31" t="n">
-        <v>123.64</v>
+        <v>277.29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:51:28</t>
+          <t>09:00:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5.81</v>
+        <v>6.02</v>
       </c>
       <c r="F32" t="n">
-        <v>15.34</v>
+        <v>14.07</v>
       </c>
       <c r="G32" t="n">
-        <v>275.7</v>
+        <v>288.2</v>
       </c>
       <c r="H32" t="n">
-        <v>96.7</v>
+        <v>94</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>43.42</v>
+        <v>-231.17</v>
       </c>
       <c r="K32" t="n">
-        <v>-30.1</v>
+        <v>-223.25</v>
       </c>
       <c r="L32" t="n">
-        <v>52.83</v>
+        <v>321.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:52:21</t>
+          <t>09:02:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.59</v>
+        <v>6.1</v>
       </c>
       <c r="F33" t="n">
-        <v>14.61</v>
+        <v>14.19</v>
       </c>
       <c r="G33" t="n">
-        <v>293</v>
+        <v>275.8</v>
       </c>
       <c r="H33" t="n">
-        <v>87.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>138.03</v>
+        <v>-40.03</v>
       </c>
       <c r="K33" t="n">
-        <v>180.75</v>
+        <v>119.92</v>
       </c>
       <c r="L33" t="n">
-        <v>227.42</v>
+        <v>126.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:53:35</t>
+          <t>09:03:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.41</v>
+        <v>5.98</v>
       </c>
       <c r="F34" t="n">
-        <v>14.77</v>
+        <v>14.66</v>
       </c>
       <c r="G34" t="n">
-        <v>269.1</v>
+        <v>277.3</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-41.38</v>
+        <v>44.03</v>
       </c>
       <c r="K34" t="n">
-        <v>81.76000000000001</v>
+        <v>-171.84</v>
       </c>
       <c r="L34" t="n">
-        <v>91.63</v>
+        <v>177.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:58:22</t>
+          <t>09:07:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.44</v>
+        <v>6.15</v>
       </c>
       <c r="F35" t="n">
-        <v>13.61</v>
+        <v>15.02</v>
       </c>
       <c r="G35" t="n">
-        <v>287.8</v>
+        <v>274.1</v>
       </c>
       <c r="H35" t="n">
-        <v>89.3</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-254.04</v>
+        <v>-536.28</v>
       </c>
       <c r="K35" t="n">
-        <v>-93.23</v>
+        <v>-458.08</v>
       </c>
       <c r="L35" t="n">
-        <v>270.6</v>
+        <v>705.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:59:01</t>
+          <t>09:09:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>6.08</v>
+        <v>5.92</v>
       </c>
       <c r="F36" t="n">
-        <v>14.7</v>
+        <v>14.95</v>
       </c>
       <c r="G36" t="n">
-        <v>284</v>
+        <v>292.9</v>
       </c>
       <c r="H36" t="n">
-        <v>91.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I36" t="n">
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>241.49</v>
+        <v>-307.9</v>
       </c>
       <c r="K36" t="n">
-        <v>152.52</v>
+        <v>266.76</v>
       </c>
       <c r="L36" t="n">
-        <v>285.62</v>
+        <v>407.39</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09:00:46</t>
+          <t>09:10:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.99</v>
+        <v>6.54</v>
       </c>
       <c r="F37" t="n">
-        <v>14.67</v>
+        <v>14.56</v>
       </c>
       <c r="G37" t="n">
-        <v>276.5</v>
+        <v>286.3</v>
       </c>
       <c r="H37" t="n">
-        <v>92.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>286.31</v>
+        <v>-38.82</v>
       </c>
       <c r="K37" t="n">
-        <v>-378.22</v>
+        <v>-254.69</v>
       </c>
       <c r="L37" t="n">
-        <v>474.36</v>
+        <v>257.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:05:57</t>
+          <t>09:14:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.88</v>
+        <v>6.11</v>
       </c>
       <c r="F38" t="n">
-        <v>14.59</v>
+        <v>14.65</v>
       </c>
       <c r="G38" t="n">
-        <v>284.3</v>
+        <v>295.9</v>
       </c>
       <c r="H38" t="n">
-        <v>95.7</v>
+        <v>99.2</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>15.92</v>
+        <v>-543.45</v>
       </c>
       <c r="K38" t="n">
-        <v>-103.24</v>
+        <v>728.25</v>
       </c>
       <c r="L38" t="n">
-        <v>104.46</v>
+        <v>908.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:07:05</t>
+          <t>09:17:03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.39</v>
+        <v>6.66</v>
       </c>
       <c r="F39" t="n">
-        <v>14.33</v>
+        <v>14.35</v>
       </c>
       <c r="G39" t="n">
-        <v>288.6</v>
+        <v>293.6</v>
       </c>
       <c r="H39" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="I39" t="n">
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>466.75</v>
+        <v>-581.76</v>
       </c>
       <c r="K39" t="n">
-        <v>112.76</v>
+        <v>-13.37</v>
       </c>
       <c r="L39" t="n">
-        <v>480.18</v>
+        <v>581.91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:09:18</t>
+          <t>09:18:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.52</v>
+        <v>6.66</v>
       </c>
       <c r="F40" t="n">
-        <v>14.24</v>
+        <v>14.34</v>
       </c>
       <c r="G40" t="n">
-        <v>286.5</v>
+        <v>261.7</v>
       </c>
       <c r="H40" t="n">
-        <v>92.7</v>
+        <v>96</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>183.91</v>
+        <v>-250.25</v>
       </c>
       <c r="K40" t="n">
-        <v>504.9</v>
+        <v>-1.49</v>
       </c>
       <c r="L40" t="n">
-        <v>537.35</v>
+        <v>250.26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:14:36</t>
+          <t>09:23:50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.7</v>
+        <v>6.09</v>
       </c>
       <c r="F41" t="n">
-        <v>14.69</v>
+        <v>15.34</v>
       </c>
       <c r="G41" t="n">
-        <v>292.3</v>
+        <v>277.6</v>
       </c>
       <c r="H41" t="n">
-        <v>95.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>186.95</v>
+        <v>-1196.71</v>
       </c>
       <c r="K41" t="n">
-        <v>-584.04</v>
+        <v>868.75</v>
       </c>
       <c r="L41" t="n">
-        <v>613.24</v>
+        <v>1478.79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09:15:15</t>
+          <t>09:24:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.54</v>
+        <v>5.59</v>
       </c>
       <c r="F42" t="n">
-        <v>15.08</v>
+        <v>14.58</v>
       </c>
       <c r="G42" t="n">
-        <v>282.7</v>
+        <v>287.8</v>
       </c>
       <c r="H42" t="n">
-        <v>95.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-1192.31</v>
+        <v>-227.24</v>
       </c>
       <c r="K42" t="n">
-        <v>46.76</v>
+        <v>-291.21</v>
       </c>
       <c r="L42" t="n">
-        <v>1193.23</v>
+        <v>369.38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09:17:19</t>
+          <t>09:26:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>6.03</v>
+        <v>6.11</v>
       </c>
       <c r="F43" t="n">
-        <v>14.36</v>
+        <v>13.87</v>
       </c>
       <c r="G43" t="n">
-        <v>287.2</v>
+        <v>306.2</v>
       </c>
       <c r="H43" t="n">
-        <v>95.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-293.83</v>
+        <v>-219.14</v>
       </c>
       <c r="K43" t="n">
-        <v>443.55</v>
+        <v>977.84</v>
       </c>
       <c r="L43" t="n">
-        <v>532.05</v>
+        <v>1002.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:30:12</t>
+          <t>09:37:21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>6.75</v>
+        <v>5.55</v>
       </c>
       <c r="F44" t="n">
-        <v>15.01</v>
+        <v>14.29</v>
       </c>
       <c r="G44" t="n">
-        <v>283.7</v>
+        <v>281.8</v>
       </c>
       <c r="H44" t="n">
-        <v>99.3</v>
+        <v>98.2</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>139.99</v>
+        <v>-73.23</v>
       </c>
       <c r="K44" t="n">
-        <v>-238.78</v>
+        <v>-63.66</v>
       </c>
       <c r="L44" t="n">
-        <v>276.79</v>
+        <v>97.04000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:31:58</t>
+          <t>09:39:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>6.35</v>
+        <v>7.25</v>
       </c>
       <c r="F45" t="n">
-        <v>14.74</v>
+        <v>14.49</v>
       </c>
       <c r="G45" t="n">
-        <v>285.2</v>
+        <v>293.6</v>
       </c>
       <c r="H45" t="n">
-        <v>90.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>26.14</v>
+        <v>-317.78</v>
       </c>
       <c r="K45" t="n">
-        <v>123.47</v>
+        <v>-527.15</v>
       </c>
       <c r="L45" t="n">
-        <v>126.2</v>
+        <v>615.53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:33:47</t>
+          <t>09:41:13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.11</v>
+        <v>6.95</v>
       </c>
       <c r="F46" t="n">
-        <v>14.77</v>
+        <v>14.09</v>
       </c>
       <c r="G46" t="n">
-        <v>263.6</v>
+        <v>273.4</v>
       </c>
       <c r="H46" t="n">
-        <v>91.3</v>
+        <v>96.5</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-157.25</v>
+        <v>132.6</v>
       </c>
       <c r="K46" t="n">
-        <v>431.13</v>
+        <v>-115.08</v>
       </c>
       <c r="L46" t="n">
-        <v>458.91</v>
+        <v>175.57</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:39:16</t>
+          <t>09:46:37</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>6.08</v>
+        <v>5.98</v>
       </c>
       <c r="F47" t="n">
-        <v>14.07</v>
+        <v>14.87</v>
       </c>
       <c r="G47" t="n">
-        <v>292.3</v>
+        <v>279.3</v>
       </c>
       <c r="H47" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>6.24</v>
+        <v>-124.29</v>
       </c>
       <c r="K47" t="n">
-        <v>-377.24</v>
+        <v>-11.46</v>
       </c>
       <c r="L47" t="n">
-        <v>377.29</v>
+        <v>124.82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:41:34</t>
+          <t>09:48:05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>6.53</v>
+        <v>6.45</v>
       </c>
       <c r="F48" t="n">
-        <v>14.53</v>
+        <v>14.67</v>
       </c>
       <c r="G48" t="n">
-        <v>282.1</v>
+        <v>303.2</v>
       </c>
       <c r="H48" t="n">
-        <v>93.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-52.97</v>
+        <v>-44.21</v>
       </c>
       <c r="K48" t="n">
-        <v>-208.97</v>
+        <v>153.15</v>
       </c>
       <c r="L48" t="n">
-        <v>215.58</v>
+        <v>159.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:43:44</t>
+          <t>09:49:24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6.19</v>
+        <v>5.4</v>
       </c>
       <c r="F49" t="n">
-        <v>14.62</v>
+        <v>14.61</v>
       </c>
       <c r="G49" t="n">
-        <v>295.6</v>
+        <v>278</v>
       </c>
       <c r="H49" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>255.59</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>15.29</v>
+        <v>20.91</v>
       </c>
       <c r="L49" t="n">
-        <v>256.05</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:48:45</t>
+          <t>09:53:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.13</v>
+        <v>6.29</v>
       </c>
       <c r="F50" t="n">
-        <v>13.5</v>
+        <v>14.39</v>
       </c>
       <c r="G50" t="n">
-        <v>288</v>
+        <v>292.4</v>
       </c>
       <c r="H50" t="n">
-        <v>99.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>54.14</v>
+        <v>-90.45999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>202.07</v>
+        <v>760.7</v>
       </c>
       <c r="L50" t="n">
-        <v>209.2</v>
+        <v>766.0599999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:50:51</t>
+          <t>09:54:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.23</v>
+        <v>6.59</v>
       </c>
       <c r="F51" t="n">
-        <v>14.44</v>
+        <v>14.26</v>
       </c>
       <c r="G51" t="n">
-        <v>290.3</v>
+        <v>269.1</v>
       </c>
       <c r="H51" t="n">
-        <v>95.8</v>
+        <v>98.2</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>248.89</v>
+        <v>477.07</v>
       </c>
       <c r="K51" t="n">
-        <v>259.91</v>
+        <v>-147.18</v>
       </c>
       <c r="L51" t="n">
-        <v>359.86</v>
+        <v>499.25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:52:06</t>
+          <t>09:56:55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>6.14</v>
+        <v>6.94</v>
       </c>
       <c r="F52" t="n">
-        <v>13.94</v>
+        <v>14.82</v>
       </c>
       <c r="G52" t="n">
-        <v>285.2</v>
+        <v>289.2</v>
       </c>
       <c r="H52" t="n">
-        <v>93.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>71.3</v>
+        <v>220.31</v>
       </c>
       <c r="K52" t="n">
-        <v>73.61</v>
+        <v>101.95</v>
       </c>
       <c r="L52" t="n">
-        <v>102.48</v>
+        <v>242.75</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:58:30</t>
+          <t>10:01:01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6.45</v>
+        <v>6.11</v>
       </c>
       <c r="F53" t="n">
-        <v>14.98</v>
+        <v>14.11</v>
       </c>
       <c r="G53" t="n">
-        <v>271.8</v>
+        <v>268.7</v>
       </c>
       <c r="H53" t="n">
-        <v>93.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-227.54</v>
+        <v>-962.37</v>
       </c>
       <c r="K53" t="n">
-        <v>-599.83</v>
+        <v>-785.4299999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>641.54</v>
+        <v>1242.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10:00:25</t>
+          <t>10:02:11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.58</v>
+        <v>6.08</v>
       </c>
       <c r="F54" t="n">
-        <v>14.65</v>
+        <v>15.22</v>
       </c>
       <c r="G54" t="n">
-        <v>283</v>
+        <v>264.2</v>
       </c>
       <c r="H54" t="n">
         <v>94.2</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-427.96</v>
+        <v>-423.68</v>
       </c>
       <c r="K54" t="n">
-        <v>242.38</v>
+        <v>-522.51</v>
       </c>
       <c r="L54" t="n">
-        <v>491.83</v>
+        <v>672.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10:01:25</t>
+          <t>10:03:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.74</v>
+        <v>6.85</v>
       </c>
       <c r="F55" t="n">
-        <v>14.24</v>
+        <v>14.1</v>
       </c>
       <c r="G55" t="n">
-        <v>284</v>
+        <v>284.6</v>
       </c>
       <c r="H55" t="n">
-        <v>95.3</v>
+        <v>93.3</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>67.68000000000001</v>
+        <v>-362.18</v>
       </c>
       <c r="K55" t="n">
-        <v>-187.32</v>
+        <v>266.93</v>
       </c>
       <c r="L55" t="n">
-        <v>199.17</v>
+        <v>449.92</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10:06:11</t>
+          <t>10:07:09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.63</v>
+        <v>6.5</v>
       </c>
       <c r="F56" t="n">
-        <v>14.24</v>
+        <v>14.02</v>
       </c>
       <c r="G56" t="n">
-        <v>289.5</v>
+        <v>281.2</v>
       </c>
       <c r="H56" t="n">
-        <v>96.8</v>
+        <v>87.3</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>341.05</v>
+        <v>-375.37</v>
       </c>
       <c r="K56" t="n">
-        <v>-891.9400000000001</v>
+        <v>-403.51</v>
       </c>
       <c r="L56" t="n">
-        <v>954.92</v>
+        <v>551.11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10:08:49</t>
+          <t>10:08:35</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>6.76</v>
+        <v>5.67</v>
       </c>
       <c r="F57" t="n">
-        <v>14.4</v>
+        <v>14.74</v>
       </c>
       <c r="G57" t="n">
         <v>283.5</v>
       </c>
       <c r="H57" t="n">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>532.01</v>
+        <v>52.06</v>
       </c>
       <c r="K57" t="n">
-        <v>2.22</v>
+        <v>608.53</v>
       </c>
       <c r="L57" t="n">
-        <v>532.01</v>
+        <v>610.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10:09:55</t>
+          <t>10:10:59</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>7.34</v>
+        <v>6.81</v>
       </c>
       <c r="F58" t="n">
-        <v>14.51</v>
+        <v>14.61</v>
       </c>
       <c r="G58" t="n">
-        <v>274.7</v>
+        <v>287.2</v>
       </c>
       <c r="H58" t="n">
-        <v>97.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>154.97</v>
+        <v>841.86</v>
       </c>
       <c r="K58" t="n">
-        <v>169.62</v>
+        <v>544.13</v>
       </c>
       <c r="L58" t="n">
-        <v>229.75</v>
+        <v>1002.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10:22:03</t>
+          <t>10:19:16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.73</v>
+        <v>6.08</v>
       </c>
       <c r="F59" t="n">
-        <v>14.78</v>
+        <v>15.03</v>
       </c>
       <c r="G59" t="n">
-        <v>277.7</v>
+        <v>267</v>
       </c>
       <c r="H59" t="n">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-431.48</v>
+        <v>-336.63</v>
       </c>
       <c r="K59" t="n">
-        <v>150.26</v>
+        <v>84.81</v>
       </c>
       <c r="L59" t="n">
-        <v>456.9</v>
+        <v>347.14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10:23:11</t>
+          <t>10:20:22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.61</v>
+        <v>6.77</v>
       </c>
       <c r="F60" t="n">
-        <v>14.13</v>
+        <v>14.33</v>
       </c>
       <c r="G60" t="n">
-        <v>291.2</v>
+        <v>296.9</v>
       </c>
       <c r="H60" t="n">
-        <v>97.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="I60" t="n">
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-88.56</v>
+        <v>-317.44</v>
       </c>
       <c r="K60" t="n">
-        <v>1.25</v>
+        <v>89.39</v>
       </c>
       <c r="L60" t="n">
-        <v>88.56999999999999</v>
+        <v>329.79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:25:36</t>
+          <t>10:22:24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>6.06</v>
+        <v>6.54</v>
       </c>
       <c r="F61" t="n">
-        <v>14.59</v>
+        <v>14.05</v>
       </c>
       <c r="G61" t="n">
-        <v>280.3</v>
+        <v>287.4</v>
       </c>
       <c r="H61" t="n">
-        <v>95.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>263.65</v>
+        <v>-140.16</v>
       </c>
       <c r="K61" t="n">
-        <v>-287.78</v>
+        <v>95.12</v>
       </c>
       <c r="L61" t="n">
-        <v>390.29</v>
+        <v>169.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:29:45</t>
+          <t>10:27:59</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.67</v>
+        <v>7.17</v>
       </c>
       <c r="F62" t="n">
-        <v>14.37</v>
+        <v>14.98</v>
       </c>
       <c r="G62" t="n">
-        <v>279.4</v>
+        <v>285.6</v>
       </c>
       <c r="H62" t="n">
-        <v>90.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-283.38</v>
+        <v>-98.91</v>
       </c>
       <c r="K62" t="n">
-        <v>149.4</v>
+        <v>38.81</v>
       </c>
       <c r="L62" t="n">
-        <v>320.35</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:32:05</t>
+          <t>10:29:10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>6.66</v>
+        <v>6.34</v>
       </c>
       <c r="F63" t="n">
-        <v>14.85</v>
+        <v>14.15</v>
       </c>
       <c r="G63" t="n">
-        <v>277.3</v>
+        <v>280</v>
       </c>
       <c r="H63" t="n">
-        <v>98.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-48.87</v>
+        <v>107.71</v>
       </c>
       <c r="K63" t="n">
-        <v>35.38</v>
+        <v>463.3</v>
       </c>
       <c r="L63" t="n">
-        <v>60.33</v>
+        <v>475.65</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:33:08</t>
+          <t>10:29:49</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.36</v>
+        <v>6.57</v>
       </c>
       <c r="F64" t="n">
-        <v>14.53</v>
+        <v>14.82</v>
       </c>
       <c r="G64" t="n">
-        <v>296</v>
+        <v>283.6</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-47.85</v>
+        <v>-386.77</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.75</v>
+        <v>-179.79</v>
       </c>
       <c r="L64" t="n">
-        <v>48.19</v>
+        <v>426.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:38:48</t>
+          <t>10:34:55</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.64</v>
+        <v>6.43</v>
       </c>
       <c r="F65" t="n">
-        <v>14.74</v>
+        <v>14.42</v>
       </c>
       <c r="G65" t="n">
-        <v>288.8</v>
+        <v>285</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>142.34</v>
+        <v>-273.96</v>
       </c>
       <c r="K65" t="n">
-        <v>-210.42</v>
+        <v>56</v>
       </c>
       <c r="L65" t="n">
-        <v>254.04</v>
+        <v>279.63</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:40:18</t>
+          <t>10:36:21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>6.69</v>
+        <v>6.95</v>
       </c>
       <c r="F66" t="n">
-        <v>14.97</v>
+        <v>13.72</v>
       </c>
       <c r="G66" t="n">
-        <v>285.8</v>
+        <v>281.7</v>
       </c>
       <c r="H66" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I66" t="n">
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>440.99</v>
+        <v>148.1</v>
       </c>
       <c r="K66" t="n">
-        <v>204.59</v>
+        <v>552.86</v>
       </c>
       <c r="L66" t="n">
-        <v>486.14</v>
+        <v>572.35</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:41:30</t>
+          <t>10:37:29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.52</v>
+        <v>5.6</v>
       </c>
       <c r="F67" t="n">
-        <v>15.34</v>
+        <v>14.85</v>
       </c>
       <c r="G67" t="n">
-        <v>294.7</v>
+        <v>284.6</v>
       </c>
       <c r="H67" t="n">
-        <v>93.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-112.8</v>
+        <v>-0.24</v>
       </c>
       <c r="K67" t="n">
-        <v>361.14</v>
+        <v>-346.79</v>
       </c>
       <c r="L67" t="n">
-        <v>378.35</v>
+        <v>346.79</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:46:54</t>
+          <t>10:41:47</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.99</v>
+        <v>7.1</v>
       </c>
       <c r="F68" t="n">
-        <v>14.77</v>
+        <v>14.76</v>
       </c>
       <c r="G68" t="n">
-        <v>289.8</v>
+        <v>273.3</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>335.34</v>
+        <v>-538.51</v>
       </c>
       <c r="K68" t="n">
-        <v>-54.77</v>
+        <v>-224.27</v>
       </c>
       <c r="L68" t="n">
-        <v>339.78</v>
+        <v>583.35</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:48:26</t>
+          <t>10:44:05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.62</v>
+        <v>6.11</v>
       </c>
       <c r="F69" t="n">
-        <v>14.85</v>
+        <v>14.57</v>
       </c>
       <c r="G69" t="n">
-        <v>277.9</v>
+        <v>280.2</v>
       </c>
       <c r="H69" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-358.89</v>
+        <v>7.92</v>
       </c>
       <c r="K69" t="n">
-        <v>80.20999999999999</v>
+        <v>-310.97</v>
       </c>
       <c r="L69" t="n">
-        <v>367.74</v>
+        <v>311.07</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:49:13</t>
+          <t>10:45:45</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>7.13</v>
+        <v>6.97</v>
       </c>
       <c r="F70" t="n">
         <v>14.46</v>
       </c>
       <c r="G70" t="n">
-        <v>299.1</v>
+        <v>288.5</v>
       </c>
       <c r="H70" t="n">
-        <v>93.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>91.3</v>
+        <v>572.6799999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-108.13</v>
+        <v>-264.41</v>
       </c>
       <c r="L70" t="n">
-        <v>141.52</v>
+        <v>630.77</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:54:09</t>
+          <t>10:50:47</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.21</v>
+        <v>6.93</v>
       </c>
       <c r="F71" t="n">
-        <v>15.32</v>
+        <v>14.14</v>
       </c>
       <c r="G71" t="n">
-        <v>291.3</v>
+        <v>285.2</v>
       </c>
       <c r="H71" t="n">
-        <v>91.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-259.02</v>
+        <v>-732.88</v>
       </c>
       <c r="K71" t="n">
-        <v>297.35</v>
+        <v>-120.24</v>
       </c>
       <c r="L71" t="n">
-        <v>394.35</v>
+        <v>742.67</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:55:24</t>
+          <t>10:52:57</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>6.4</v>
+        <v>7.13</v>
       </c>
       <c r="F72" t="n">
-        <v>15.51</v>
+        <v>14.69</v>
       </c>
       <c r="G72" t="n">
-        <v>284.9</v>
+        <v>281</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>89.8</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-391.69</v>
+        <v>-585.27</v>
       </c>
       <c r="K72" t="n">
-        <v>331.44</v>
+        <v>-776.99</v>
       </c>
       <c r="L72" t="n">
-        <v>513.1</v>
+        <v>972.76</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:56:59</t>
+          <t>10:55:12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>7.23</v>
+        <v>6.48</v>
       </c>
       <c r="F73" t="n">
-        <v>14.9</v>
+        <v>14.56</v>
       </c>
       <c r="G73" t="n">
-        <v>287</v>
+        <v>297.2</v>
       </c>
       <c r="H73" t="n">
-        <v>87.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-52.56</v>
+        <v>-464.95</v>
       </c>
       <c r="K73" t="n">
-        <v>403.19</v>
+        <v>641.84</v>
       </c>
       <c r="L73" t="n">
-        <v>406.6</v>
+        <v>792.55</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11:07:05</t>
+          <t>11:07:02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>7.2</v>
+        <v>6.82</v>
       </c>
       <c r="F74" t="n">
-        <v>15.34</v>
+        <v>14.9</v>
       </c>
       <c r="G74" t="n">
-        <v>270.5</v>
+        <v>292</v>
       </c>
       <c r="H74" t="n">
-        <v>93.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-78.56999999999999</v>
+        <v>-7.96</v>
       </c>
       <c r="K74" t="n">
-        <v>-154.67</v>
+        <v>-46.12</v>
       </c>
       <c r="L74" t="n">
-        <v>173.48</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11:08:37</t>
+          <t>11:08:49</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>7.05</v>
+        <v>6.48</v>
       </c>
       <c r="F75" t="n">
-        <v>14.62</v>
+        <v>14.39</v>
       </c>
       <c r="G75" t="n">
-        <v>278.1</v>
+        <v>280.2</v>
       </c>
       <c r="H75" t="n">
-        <v>92.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-324.96</v>
+        <v>-305.98</v>
       </c>
       <c r="K75" t="n">
-        <v>-154.46</v>
+        <v>-120.56</v>
       </c>
       <c r="L75" t="n">
-        <v>359.8</v>
+        <v>328.87</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:10:35</t>
+          <t>11:09:44</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.55</v>
+        <v>6.65</v>
       </c>
       <c r="F76" t="n">
-        <v>14.76</v>
+        <v>14.74</v>
       </c>
       <c r="G76" t="n">
-        <v>283.2</v>
+        <v>296.2</v>
       </c>
       <c r="H76" t="n">
-        <v>98.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>254.61</v>
+        <v>159.59</v>
       </c>
       <c r="K76" t="n">
-        <v>-255.09</v>
+        <v>-264.6</v>
       </c>
       <c r="L76" t="n">
-        <v>360.41</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11:14:44</t>
+          <t>11:14:57</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>6.2</v>
+        <v>5.78</v>
       </c>
       <c r="F77" t="n">
-        <v>14.59</v>
+        <v>15.11</v>
       </c>
       <c r="G77" t="n">
-        <v>268.7</v>
+        <v>276.4</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>196.98</v>
+        <v>-34.07</v>
       </c>
       <c r="K77" t="n">
-        <v>-337.6</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>390.86</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11:16:38</t>
+          <t>11:16:51</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>7.3</v>
+        <v>6.75</v>
       </c>
       <c r="F78" t="n">
-        <v>14.54</v>
+        <v>14.43</v>
       </c>
       <c r="G78" t="n">
-        <v>270.3</v>
+        <v>285.8</v>
       </c>
       <c r="H78" t="n">
-        <v>96.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-175.65</v>
+        <v>57.06</v>
       </c>
       <c r="K78" t="n">
-        <v>245.51</v>
+        <v>227.93</v>
       </c>
       <c r="L78" t="n">
-        <v>301.87</v>
+        <v>234.96</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11:17:20</t>
+          <t>11:18:03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>7.29</v>
+        <v>7.09</v>
       </c>
       <c r="F79" t="n">
-        <v>14.66</v>
+        <v>13.75</v>
       </c>
       <c r="G79" t="n">
-        <v>290.9</v>
+        <v>283.8</v>
       </c>
       <c r="H79" t="n">
-        <v>97.3</v>
+        <v>99.5</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-319.84</v>
+        <v>-240.98</v>
       </c>
       <c r="K79" t="n">
-        <v>184.24</v>
+        <v>-273.5</v>
       </c>
       <c r="L79" t="n">
-        <v>369.11</v>
+        <v>364.52</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11:22:47</t>
+          <t>11:22:34</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
       <c r="F80" t="n">
-        <v>14.75</v>
+        <v>14.33</v>
       </c>
       <c r="G80" t="n">
-        <v>279.2</v>
+        <v>274.9</v>
       </c>
       <c r="H80" t="n">
-        <v>91.7</v>
+        <v>97.3</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-401.99</v>
+        <v>182.72</v>
       </c>
       <c r="K80" t="n">
-        <v>-285.93</v>
+        <v>135.79</v>
       </c>
       <c r="L80" t="n">
-        <v>493.31</v>
+        <v>227.66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11:23:39</t>
+          <t>11:23:19</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.11</v>
+        <v>6.17</v>
       </c>
       <c r="F81" t="n">
-        <v>15.11</v>
+        <v>14.3</v>
       </c>
       <c r="G81" t="n">
-        <v>296.9</v>
+        <v>283.7</v>
       </c>
       <c r="H81" t="n">
-        <v>91.5</v>
+        <v>99.7</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-38.2</v>
+        <v>92.37</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.07</v>
+        <v>-172.01</v>
       </c>
       <c r="L81" t="n">
-        <v>41.84</v>
+        <v>195.24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11:25:38</t>
+          <t>11:24:35</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.62</v>
+        <v>6.95</v>
       </c>
       <c r="F82" t="n">
-        <v>14.85</v>
+        <v>14.51</v>
       </c>
       <c r="G82" t="n">
-        <v>285.3</v>
+        <v>288.9</v>
       </c>
       <c r="H82" t="n">
-        <v>89.8</v>
+        <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-385.91</v>
+        <v>10.08</v>
       </c>
       <c r="K82" t="n">
-        <v>11.22</v>
+        <v>161.47</v>
       </c>
       <c r="L82" t="n">
-        <v>386.07</v>
+        <v>161.78</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:29:20</t>
+          <t>11:28:05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.01</v>
+        <v>6.64</v>
       </c>
       <c r="F83" t="n">
-        <v>14.84</v>
+        <v>15.28</v>
       </c>
       <c r="G83" t="n">
-        <v>290.7</v>
+        <v>288.7</v>
       </c>
       <c r="H83" t="n">
-        <v>94.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-443.24</v>
+        <v>143.05</v>
       </c>
       <c r="K83" t="n">
-        <v>-36.59</v>
+        <v>77.25</v>
       </c>
       <c r="L83" t="n">
-        <v>444.75</v>
+        <v>162.58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:31:33</t>
+          <t>11:29:23</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.59</v>
+        <v>6.87</v>
       </c>
       <c r="F84" t="n">
-        <v>13.92</v>
+        <v>15.24</v>
       </c>
       <c r="G84" t="n">
-        <v>274.6</v>
+        <v>276</v>
       </c>
       <c r="H84" t="n">
-        <v>99.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-52.59</v>
+        <v>320.29</v>
       </c>
       <c r="K84" t="n">
-        <v>-394.99</v>
+        <v>234.04</v>
       </c>
       <c r="L84" t="n">
-        <v>398.47</v>
+        <v>396.68</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:32:49</t>
+          <t>11:31:38</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>6.17</v>
+        <v>7.08</v>
       </c>
       <c r="F85" t="n">
-        <v>14.39</v>
+        <v>15.67</v>
       </c>
       <c r="G85" t="n">
-        <v>285.3</v>
+        <v>293.5</v>
       </c>
       <c r="H85" t="n">
-        <v>99.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-1132.26</v>
+        <v>-424.82</v>
       </c>
       <c r="K85" t="n">
-        <v>-489.05</v>
+        <v>-522.92</v>
       </c>
       <c r="L85" t="n">
-        <v>1233.36</v>
+        <v>673.73</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:37:45</t>
+          <t>11:35:44</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.92</v>
+        <v>6.21</v>
       </c>
       <c r="F86" t="n">
-        <v>14.85</v>
+        <v>14.89</v>
       </c>
       <c r="G86" t="n">
-        <v>288.5</v>
+        <v>277.8</v>
       </c>
       <c r="H86" t="n">
-        <v>88.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>214.81</v>
+        <v>-281.05</v>
       </c>
       <c r="K86" t="n">
-        <v>212.88</v>
+        <v>-881.5</v>
       </c>
       <c r="L86" t="n">
-        <v>302.43</v>
+        <v>925.21</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:40:04</t>
+          <t>11:37:18</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.49</v>
+        <v>7.13</v>
       </c>
       <c r="F87" t="n">
-        <v>15.16</v>
+        <v>14.77</v>
       </c>
       <c r="G87" t="n">
-        <v>287.5</v>
+        <v>279.3</v>
       </c>
       <c r="H87" t="n">
-        <v>94.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>413.91</v>
+        <v>-48.58</v>
       </c>
       <c r="K87" t="n">
-        <v>-325.45</v>
+        <v>643.79</v>
       </c>
       <c r="L87" t="n">
-        <v>526.53</v>
+        <v>645.62</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:42:02</t>
+          <t>11:39:14</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.99</v>
+        <v>6.72</v>
       </c>
       <c r="F88" t="n">
-        <v>15.13</v>
+        <v>14.79</v>
       </c>
       <c r="G88" t="n">
-        <v>282</v>
+        <v>273.4</v>
       </c>
       <c r="H88" t="n">
-        <v>90.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-703.79</v>
+        <v>238.53</v>
       </c>
       <c r="K88" t="n">
-        <v>634.12</v>
+        <v>129.63</v>
       </c>
       <c r="L88" t="n">
-        <v>947.33</v>
+        <v>271.48</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>185.3</v>
+        <v>226.9</v>
       </c>
       <c r="K14" t="n">
-        <v>349.21</v>
+        <v>427.6</v>
       </c>
       <c r="L14" t="n">
-        <v>395.32</v>
+        <v>484.08</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>190.01</v>
+        <v>238</v>
       </c>
       <c r="K15" t="n">
-        <v>27.86</v>
+        <v>34.9</v>
       </c>
       <c r="L15" t="n">
-        <v>192.04</v>
+        <v>240.55</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>28.54</v>
+        <v>37.1</v>
       </c>
       <c r="K16" t="n">
-        <v>181.82</v>
+        <v>236.39</v>
       </c>
       <c r="L16" t="n">
-        <v>184.05</v>
+        <v>239.29</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-165.3</v>
+        <v>-206.03</v>
       </c>
       <c r="K17" t="n">
-        <v>-182.51</v>
+        <v>-227.48</v>
       </c>
       <c r="L17" t="n">
-        <v>246.24</v>
+        <v>306.91</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>116.06</v>
+        <v>215.9</v>
       </c>
       <c r="K18" t="n">
-        <v>-40.53</v>
+        <v>-75.39</v>
       </c>
       <c r="L18" t="n">
-        <v>122.93</v>
+        <v>228.69</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>193.28</v>
+        <v>225.45</v>
       </c>
       <c r="K19" t="n">
-        <v>108.25</v>
+        <v>126.27</v>
       </c>
       <c r="L19" t="n">
-        <v>221.53</v>
+        <v>258.4</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>132.29</v>
+        <v>164.44</v>
       </c>
       <c r="K20" t="n">
-        <v>327.5</v>
+        <v>407.09</v>
       </c>
       <c r="L20" t="n">
-        <v>353.21</v>
+        <v>439.05</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-109.65</v>
+        <v>-215.27</v>
       </c>
       <c r="K21" t="n">
-        <v>-184.03</v>
+        <v>-361.28</v>
       </c>
       <c r="L21" t="n">
-        <v>214.22</v>
+        <v>420.56</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>139.76</v>
+        <v>192.95</v>
       </c>
       <c r="K22" t="n">
-        <v>-297.74</v>
+        <v>-411.06</v>
       </c>
       <c r="L22" t="n">
-        <v>328.91</v>
+        <v>454.09</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-77.63</v>
+        <v>-111.18</v>
       </c>
       <c r="K23" t="n">
-        <v>369.05</v>
+        <v>528.54</v>
       </c>
       <c r="L23" t="n">
-        <v>377.12</v>
+        <v>540.1</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-19.82</v>
+        <v>-51.45</v>
       </c>
       <c r="K24" t="n">
-        <v>-156.86</v>
+        <v>-407.21</v>
       </c>
       <c r="L24" t="n">
-        <v>158.11</v>
+        <v>410.44</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-238.03</v>
+        <v>-409.12</v>
       </c>
       <c r="K25" t="n">
-        <v>253.09</v>
+        <v>435</v>
       </c>
       <c r="L25" t="n">
-        <v>347.44</v>
+        <v>597.16</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-284.48</v>
+        <v>-648.83</v>
       </c>
       <c r="K26" t="n">
-        <v>37.88</v>
+        <v>86.38</v>
       </c>
       <c r="L26" t="n">
-        <v>286.99</v>
+        <v>654.5599999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-306.15</v>
+        <v>-479.4</v>
       </c>
       <c r="K27" t="n">
-        <v>556.46</v>
+        <v>871.36</v>
       </c>
       <c r="L27" t="n">
-        <v>635.12</v>
+        <v>994.53</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-92.31</v>
+        <v>-136.34</v>
       </c>
       <c r="K28" t="n">
-        <v>727.89</v>
+        <v>1075.07</v>
       </c>
       <c r="L28" t="n">
-        <v>733.72</v>
+        <v>1083.68</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="K29" t="n">
-        <v>275.44</v>
+        <v>368.73</v>
       </c>
       <c r="L29" t="n">
-        <v>275.45</v>
+        <v>368.74</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>364.07</v>
+        <v>397.47</v>
       </c>
       <c r="K30" t="n">
-        <v>188.66</v>
+        <v>205.96</v>
       </c>
       <c r="L30" t="n">
-        <v>410.05</v>
+        <v>447.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>241.36</v>
+        <v>295.52</v>
       </c>
       <c r="K31" t="n">
-        <v>-136.5</v>
+        <v>-167.13</v>
       </c>
       <c r="L31" t="n">
-        <v>277.29</v>
+        <v>339.5</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-231.17</v>
+        <v>-270.94</v>
       </c>
       <c r="K32" t="n">
-        <v>-223.25</v>
+        <v>-261.66</v>
       </c>
       <c r="L32" t="n">
-        <v>321.38</v>
+        <v>376.66</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-40.03</v>
+        <v>-75.88</v>
       </c>
       <c r="K33" t="n">
-        <v>119.92</v>
+        <v>227.31</v>
       </c>
       <c r="L33" t="n">
-        <v>126.42</v>
+        <v>239.64</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>44.03</v>
+        <v>69.34</v>
       </c>
       <c r="K34" t="n">
-        <v>-171.84</v>
+        <v>-270.63</v>
       </c>
       <c r="L34" t="n">
-        <v>177.39</v>
+        <v>279.37</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-536.28</v>
+        <v>-686.88</v>
       </c>
       <c r="K35" t="n">
-        <v>-458.08</v>
+        <v>-586.71</v>
       </c>
       <c r="L35" t="n">
-        <v>705.29</v>
+        <v>903.34</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-307.9</v>
+        <v>-454.73</v>
       </c>
       <c r="K36" t="n">
-        <v>266.76</v>
+        <v>393.97</v>
       </c>
       <c r="L36" t="n">
-        <v>407.39</v>
+        <v>601.65</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-38.82</v>
+        <v>-59.33</v>
       </c>
       <c r="K37" t="n">
-        <v>-254.69</v>
+        <v>-389.24</v>
       </c>
       <c r="L37" t="n">
-        <v>257.63</v>
+        <v>393.74</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-543.45</v>
+        <v>-698.59</v>
       </c>
       <c r="K38" t="n">
-        <v>728.25</v>
+        <v>936.15</v>
       </c>
       <c r="L38" t="n">
-        <v>908.67</v>
+        <v>1168.08</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-581.76</v>
+        <v>-831.49</v>
       </c>
       <c r="K39" t="n">
-        <v>-13.37</v>
+        <v>-19.12</v>
       </c>
       <c r="L39" t="n">
-        <v>581.91</v>
+        <v>831.71</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-250.25</v>
+        <v>-539.99</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.49</v>
+        <v>-3.2</v>
       </c>
       <c r="L40" t="n">
-        <v>250.26</v>
+        <v>540</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-1196.71</v>
+        <v>-1452.72</v>
       </c>
       <c r="K41" t="n">
-        <v>868.75</v>
+        <v>1054.6</v>
       </c>
       <c r="L41" t="n">
-        <v>1478.79</v>
+        <v>1795.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-227.24</v>
+        <v>-394.12</v>
       </c>
       <c r="K42" t="n">
-        <v>-291.21</v>
+        <v>-505.06</v>
       </c>
       <c r="L42" t="n">
-        <v>369.38</v>
+        <v>640.63</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-219.14</v>
+        <v>-290.74</v>
       </c>
       <c r="K43" t="n">
-        <v>977.84</v>
+        <v>1297.37</v>
       </c>
       <c r="L43" t="n">
-        <v>1002.09</v>
+        <v>1329.55</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-73.23</v>
+        <v>-126.54</v>
       </c>
       <c r="K44" t="n">
-        <v>-63.66</v>
+        <v>-110</v>
       </c>
       <c r="L44" t="n">
-        <v>97.04000000000001</v>
+        <v>167.67</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-317.78</v>
+        <v>-375.84</v>
       </c>
       <c r="K45" t="n">
-        <v>-527.15</v>
+        <v>-623.47</v>
       </c>
       <c r="L45" t="n">
-        <v>615.53</v>
+        <v>727.99</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>132.6</v>
+        <v>191.31</v>
       </c>
       <c r="K46" t="n">
-        <v>-115.08</v>
+        <v>-166.03</v>
       </c>
       <c r="L46" t="n">
-        <v>175.57</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-124.29</v>
+        <v>-259.95</v>
       </c>
       <c r="K47" t="n">
-        <v>-11.46</v>
+        <v>-23.97</v>
       </c>
       <c r="L47" t="n">
-        <v>124.82</v>
+        <v>261.05</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-44.21</v>
+        <v>-82.58</v>
       </c>
       <c r="K48" t="n">
-        <v>153.15</v>
+        <v>286.07</v>
       </c>
       <c r="L48" t="n">
-        <v>159.4</v>
+        <v>297.75</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>69.15000000000001</v>
+        <v>155.07</v>
       </c>
       <c r="K49" t="n">
-        <v>20.91</v>
+        <v>46.9</v>
       </c>
       <c r="L49" t="n">
-        <v>72.23999999999999</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-90.45999999999999</v>
+        <v>-111.89</v>
       </c>
       <c r="K50" t="n">
-        <v>760.7</v>
+        <v>940.95</v>
       </c>
       <c r="L50" t="n">
-        <v>766.0599999999999</v>
+        <v>947.58</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>477.07</v>
+        <v>675.78</v>
       </c>
       <c r="K51" t="n">
-        <v>-147.18</v>
+        <v>-208.48</v>
       </c>
       <c r="L51" t="n">
-        <v>499.25</v>
+        <v>707.21</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>220.31</v>
+        <v>443.38</v>
       </c>
       <c r="K52" t="n">
-        <v>101.95</v>
+        <v>205.17</v>
       </c>
       <c r="L52" t="n">
-        <v>242.75</v>
+        <v>488.55</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-962.37</v>
+        <v>-1123.37</v>
       </c>
       <c r="K53" t="n">
-        <v>-785.4299999999999</v>
+        <v>-916.83</v>
       </c>
       <c r="L53" t="n">
-        <v>1242.2</v>
+        <v>1450.01</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-423.68</v>
+        <v>-571.72</v>
       </c>
       <c r="K54" t="n">
-        <v>-522.51</v>
+        <v>-705.08</v>
       </c>
       <c r="L54" t="n">
-        <v>672.7</v>
+        <v>907.75</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-362.18</v>
+        <v>-557.59</v>
       </c>
       <c r="K55" t="n">
-        <v>266.93</v>
+        <v>410.94</v>
       </c>
       <c r="L55" t="n">
-        <v>449.92</v>
+        <v>692.66</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-375.37</v>
+        <v>-663.6799999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>-403.51</v>
+        <v>-713.4400000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>551.11</v>
+        <v>974.4</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>52.06</v>
+        <v>85.39</v>
       </c>
       <c r="K57" t="n">
-        <v>608.53</v>
+        <v>998.04</v>
       </c>
       <c r="L57" t="n">
-        <v>610.75</v>
+        <v>1001.69</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>841.86</v>
+        <v>1176.53</v>
       </c>
       <c r="K58" t="n">
-        <v>544.13</v>
+        <v>760.4400000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>1002.4</v>
+        <v>1400.88</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-336.63</v>
+        <v>-367.34</v>
       </c>
       <c r="K59" t="n">
-        <v>84.81</v>
+        <v>92.55</v>
       </c>
       <c r="L59" t="n">
-        <v>347.14</v>
+        <v>378.82</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-317.44</v>
+        <v>-370.52</v>
       </c>
       <c r="K60" t="n">
-        <v>89.39</v>
+        <v>104.34</v>
       </c>
       <c r="L60" t="n">
-        <v>329.79</v>
+        <v>384.93</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-140.16</v>
+        <v>-213.66</v>
       </c>
       <c r="K61" t="n">
-        <v>95.12</v>
+        <v>145.01</v>
       </c>
       <c r="L61" t="n">
-        <v>169.4</v>
+        <v>258.22</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-98.91</v>
+        <v>-243.38</v>
       </c>
       <c r="K62" t="n">
-        <v>38.81</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>106.25</v>
+        <v>261.45</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>107.71</v>
+        <v>133.97</v>
       </c>
       <c r="K63" t="n">
-        <v>463.3</v>
+        <v>576.26</v>
       </c>
       <c r="L63" t="n">
-        <v>475.65</v>
+        <v>591.63</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-386.77</v>
+        <v>-491.25</v>
       </c>
       <c r="K64" t="n">
-        <v>-179.79</v>
+        <v>-228.36</v>
       </c>
       <c r="L64" t="n">
-        <v>426.52</v>
+        <v>541.74</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-273.96</v>
+        <v>-401.19</v>
       </c>
       <c r="K65" t="n">
-        <v>56</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>279.63</v>
+        <v>409.49</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>148.1</v>
+        <v>206.12</v>
       </c>
       <c r="K66" t="n">
-        <v>552.86</v>
+        <v>769.4400000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>572.35</v>
+        <v>796.5599999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.24</v>
+        <v>-0.34</v>
       </c>
       <c r="K67" t="n">
-        <v>-346.79</v>
+        <v>-498.45</v>
       </c>
       <c r="L67" t="n">
-        <v>346.79</v>
+        <v>498.45</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-538.51</v>
+        <v>-906.1</v>
       </c>
       <c r="K68" t="n">
-        <v>-224.27</v>
+        <v>-377.36</v>
       </c>
       <c r="L68" t="n">
-        <v>583.35</v>
+        <v>981.54</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>7.92</v>
+        <v>13.9</v>
       </c>
       <c r="K69" t="n">
-        <v>-310.97</v>
+        <v>-545.77</v>
       </c>
       <c r="L69" t="n">
-        <v>311.07</v>
+        <v>545.95</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>572.6799999999999</v>
+        <v>787.03</v>
       </c>
       <c r="K70" t="n">
-        <v>-264.41</v>
+        <v>-363.37</v>
       </c>
       <c r="L70" t="n">
-        <v>630.77</v>
+        <v>866.86</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-732.88</v>
+        <v>-1094.61</v>
       </c>
       <c r="K71" t="n">
-        <v>-120.24</v>
+        <v>-179.59</v>
       </c>
       <c r="L71" t="n">
-        <v>742.67</v>
+        <v>1109.24</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-585.27</v>
+        <v>-954.55</v>
       </c>
       <c r="K72" t="n">
-        <v>-776.99</v>
+        <v>-1267.23</v>
       </c>
       <c r="L72" t="n">
-        <v>972.76</v>
+        <v>1586.52</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-464.95</v>
+        <v>-656.02</v>
       </c>
       <c r="K73" t="n">
-        <v>641.84</v>
+        <v>905.62</v>
       </c>
       <c r="L73" t="n">
-        <v>792.55</v>
+        <v>1118.27</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.96</v>
+        <v>-31.36</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.12</v>
+        <v>-181.64</v>
       </c>
       <c r="L74" t="n">
-        <v>46.8</v>
+        <v>184.33</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-305.98</v>
+        <v>-395.81</v>
       </c>
       <c r="K75" t="n">
-        <v>-120.56</v>
+        <v>-155.95</v>
       </c>
       <c r="L75" t="n">
-        <v>328.87</v>
+        <v>425.42</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>159.59</v>
+        <v>181.73</v>
       </c>
       <c r="K76" t="n">
-        <v>-264.6</v>
+        <v>-301.32</v>
       </c>
       <c r="L76" t="n">
-        <v>309</v>
+        <v>351.88</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-34.07</v>
+        <v>-82.38</v>
       </c>
       <c r="K77" t="n">
-        <v>72.04000000000001</v>
+        <v>174.18</v>
       </c>
       <c r="L77" t="n">
-        <v>79.7</v>
+        <v>192.68</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>57.06</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>227.93</v>
+        <v>341.93</v>
       </c>
       <c r="L78" t="n">
-        <v>234.96</v>
+        <v>352.49</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-240.98</v>
+        <v>-294.42</v>
       </c>
       <c r="K79" t="n">
-        <v>-273.5</v>
+        <v>-334.15</v>
       </c>
       <c r="L79" t="n">
-        <v>364.52</v>
+        <v>445.35</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>182.72</v>
+        <v>354.53</v>
       </c>
       <c r="K80" t="n">
-        <v>135.79</v>
+        <v>263.48</v>
       </c>
       <c r="L80" t="n">
-        <v>227.66</v>
+        <v>441.71</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>92.37</v>
+        <v>193.65</v>
       </c>
       <c r="K81" t="n">
-        <v>-172.01</v>
+        <v>-360.6</v>
       </c>
       <c r="L81" t="n">
-        <v>195.24</v>
+        <v>409.31</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>10.08</v>
+        <v>21.19</v>
       </c>
       <c r="K82" t="n">
-        <v>161.47</v>
+        <v>339.49</v>
       </c>
       <c r="L82" t="n">
-        <v>161.78</v>
+        <v>340.15</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>143.05</v>
+        <v>401.75</v>
       </c>
       <c r="K83" t="n">
-        <v>77.25</v>
+        <v>216.95</v>
       </c>
       <c r="L83" t="n">
-        <v>162.58</v>
+        <v>456.58</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>320.29</v>
+        <v>622.12</v>
       </c>
       <c r="K84" t="n">
-        <v>234.04</v>
+        <v>454.6</v>
       </c>
       <c r="L84" t="n">
-        <v>396.68</v>
+        <v>770.51</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-424.82</v>
+        <v>-618.52</v>
       </c>
       <c r="K85" t="n">
-        <v>-522.92</v>
+        <v>-761.34</v>
       </c>
       <c r="L85" t="n">
-        <v>673.73</v>
+        <v>980.9299999999999</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-281.05</v>
+        <v>-422.12</v>
       </c>
       <c r="K86" t="n">
-        <v>-881.5</v>
+        <v>-1323.96</v>
       </c>
       <c r="L86" t="n">
-        <v>925.21</v>
+        <v>1389.63</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-48.58</v>
+        <v>-94.48999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>643.79</v>
+        <v>1252.06</v>
       </c>
       <c r="L87" t="n">
-        <v>645.62</v>
+        <v>1255.62</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>238.53</v>
+        <v>700.1</v>
       </c>
       <c r="K88" t="n">
-        <v>129.63</v>
+        <v>380.47</v>
       </c>
       <c r="L88" t="n">
-        <v>271.48</v>
+        <v>796.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>226.9</v>
+        <v>143.34</v>
       </c>
       <c r="K14" t="n">
-        <v>427.6</v>
+        <v>270.13</v>
       </c>
       <c r="L14" t="n">
-        <v>484.08</v>
+        <v>305.81</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>238</v>
+        <v>165.29</v>
       </c>
       <c r="K15" t="n">
-        <v>34.9</v>
+        <v>24.24</v>
       </c>
       <c r="L15" t="n">
-        <v>240.55</v>
+        <v>167.06</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>37.1</v>
+        <v>26.98</v>
       </c>
       <c r="K16" t="n">
-        <v>236.39</v>
+        <v>171.9</v>
       </c>
       <c r="L16" t="n">
-        <v>239.29</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-206.03</v>
+        <v>-148.4</v>
       </c>
       <c r="K17" t="n">
-        <v>-227.48</v>
+        <v>-163.85</v>
       </c>
       <c r="L17" t="n">
-        <v>306.91</v>
+        <v>221.07</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>215.9</v>
+        <v>141.08</v>
       </c>
       <c r="K18" t="n">
-        <v>-75.39</v>
+        <v>-49.27</v>
       </c>
       <c r="L18" t="n">
-        <v>228.69</v>
+        <v>149.43</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>225.45</v>
+        <v>171.54</v>
       </c>
       <c r="K19" t="n">
-        <v>126.27</v>
+        <v>96.08</v>
       </c>
       <c r="L19" t="n">
-        <v>258.4</v>
+        <v>196.61</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>164.44</v>
+        <v>104.34</v>
       </c>
       <c r="K20" t="n">
-        <v>407.09</v>
+        <v>258.3</v>
       </c>
       <c r="L20" t="n">
-        <v>439.05</v>
+        <v>278.57</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-215.27</v>
+        <v>-114.26</v>
       </c>
       <c r="K21" t="n">
-        <v>-361.28</v>
+        <v>-191.76</v>
       </c>
       <c r="L21" t="n">
-        <v>420.56</v>
+        <v>223.22</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>192.95</v>
+        <v>120.12</v>
       </c>
       <c r="K22" t="n">
-        <v>-411.06</v>
+        <v>-255.89</v>
       </c>
       <c r="L22" t="n">
-        <v>454.09</v>
+        <v>282.68</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-111.18</v>
+        <v>-61.15</v>
       </c>
       <c r="K23" t="n">
-        <v>528.54</v>
+        <v>290.69</v>
       </c>
       <c r="L23" t="n">
-        <v>540.1</v>
+        <v>297.06</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-51.45</v>
+        <v>-26.08</v>
       </c>
       <c r="K24" t="n">
-        <v>-407.21</v>
+        <v>-206.38</v>
       </c>
       <c r="L24" t="n">
-        <v>410.44</v>
+        <v>208.02</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-409.12</v>
+        <v>-212.28</v>
       </c>
       <c r="K25" t="n">
-        <v>435</v>
+        <v>225.71</v>
       </c>
       <c r="L25" t="n">
-        <v>597.16</v>
+        <v>309.85</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-648.83</v>
+        <v>-297.27</v>
       </c>
       <c r="K26" t="n">
-        <v>86.38</v>
+        <v>39.58</v>
       </c>
       <c r="L26" t="n">
-        <v>654.5599999999999</v>
+        <v>299.89</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-479.4</v>
+        <v>-226.04</v>
       </c>
       <c r="K27" t="n">
-        <v>871.36</v>
+        <v>410.85</v>
       </c>
       <c r="L27" t="n">
-        <v>994.53</v>
+        <v>468.93</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-136.34</v>
+        <v>-68.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>1075.07</v>
+        <v>537</v>
       </c>
       <c r="L28" t="n">
-        <v>1083.68</v>
+        <v>541.3</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>3.54</v>
+        <v>2.29</v>
       </c>
       <c r="K29" t="n">
-        <v>368.73</v>
+        <v>239.27</v>
       </c>
       <c r="L29" t="n">
-        <v>368.74</v>
+        <v>239.28</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>397.47</v>
+        <v>269.71</v>
       </c>
       <c r="K30" t="n">
-        <v>205.96</v>
+        <v>139.76</v>
       </c>
       <c r="L30" t="n">
-        <v>447.66</v>
+        <v>303.77</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>295.52</v>
+        <v>205.21</v>
       </c>
       <c r="K31" t="n">
-        <v>-167.13</v>
+        <v>-116.06</v>
       </c>
       <c r="L31" t="n">
-        <v>339.5</v>
+        <v>235.76</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-270.94</v>
+        <v>-193.75</v>
       </c>
       <c r="K32" t="n">
-        <v>-261.66</v>
+        <v>-187.12</v>
       </c>
       <c r="L32" t="n">
-        <v>376.66</v>
+        <v>269.36</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-75.88</v>
+        <v>-50.51</v>
       </c>
       <c r="K33" t="n">
-        <v>227.31</v>
+        <v>151.32</v>
       </c>
       <c r="L33" t="n">
-        <v>239.64</v>
+        <v>159.53</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>69.34</v>
+        <v>46.26</v>
       </c>
       <c r="K34" t="n">
-        <v>-270.63</v>
+        <v>-180.58</v>
       </c>
       <c r="L34" t="n">
-        <v>279.37</v>
+        <v>186.41</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-686.88</v>
+        <v>-363.4</v>
       </c>
       <c r="K35" t="n">
-        <v>-586.71</v>
+        <v>-310.41</v>
       </c>
       <c r="L35" t="n">
-        <v>903.34</v>
+        <v>477.93</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-454.73</v>
+        <v>-241.64</v>
       </c>
       <c r="K36" t="n">
-        <v>393.97</v>
+        <v>209.35</v>
       </c>
       <c r="L36" t="n">
-        <v>601.65</v>
+        <v>319.71</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-59.33</v>
+        <v>-38.04</v>
       </c>
       <c r="K37" t="n">
-        <v>-389.24</v>
+        <v>-249.58</v>
       </c>
       <c r="L37" t="n">
-        <v>393.74</v>
+        <v>252.46</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-698.59</v>
+        <v>-359.41</v>
       </c>
       <c r="K38" t="n">
-        <v>936.15</v>
+        <v>481.63</v>
       </c>
       <c r="L38" t="n">
-        <v>1168.08</v>
+        <v>600.95</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-831.49</v>
+        <v>-454.56</v>
       </c>
       <c r="K39" t="n">
-        <v>-19.12</v>
+        <v>-10.45</v>
       </c>
       <c r="L39" t="n">
-        <v>831.71</v>
+        <v>454.68</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-539.99</v>
+        <v>-284.71</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.2</v>
+        <v>-1.69</v>
       </c>
       <c r="L40" t="n">
-        <v>540</v>
+        <v>284.72</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-1452.72</v>
+        <v>-728.03</v>
       </c>
       <c r="K41" t="n">
-        <v>1054.6</v>
+        <v>528.51</v>
       </c>
       <c r="L41" t="n">
-        <v>1795.16</v>
+        <v>899.64</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-394.12</v>
+        <v>-207.42</v>
       </c>
       <c r="K42" t="n">
-        <v>-505.06</v>
+        <v>-265.8</v>
       </c>
       <c r="L42" t="n">
-        <v>640.63</v>
+        <v>337.15</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-290.74</v>
+        <v>-145.65</v>
       </c>
       <c r="K43" t="n">
-        <v>1297.37</v>
+        <v>649.9299999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>1329.55</v>
+        <v>666.05</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-126.54</v>
+        <v>-94.97</v>
       </c>
       <c r="K44" t="n">
-        <v>-110</v>
+        <v>-82.56</v>
       </c>
       <c r="L44" t="n">
-        <v>167.67</v>
+        <v>125.84</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-375.84</v>
+        <v>-233.35</v>
       </c>
       <c r="K45" t="n">
-        <v>-623.47</v>
+        <v>-387.09</v>
       </c>
       <c r="L45" t="n">
-        <v>727.99</v>
+        <v>451.99</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>191.31</v>
+        <v>145.51</v>
       </c>
       <c r="K46" t="n">
-        <v>-166.03</v>
+        <v>-126.29</v>
       </c>
       <c r="L46" t="n">
-        <v>253.31</v>
+        <v>192.67</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-259.95</v>
+        <v>-158.5</v>
       </c>
       <c r="K47" t="n">
-        <v>-23.97</v>
+        <v>-14.61</v>
       </c>
       <c r="L47" t="n">
-        <v>261.05</v>
+        <v>159.17</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-82.58</v>
+        <v>-51.36</v>
       </c>
       <c r="K48" t="n">
-        <v>286.07</v>
+        <v>177.91</v>
       </c>
       <c r="L48" t="n">
-        <v>297.75</v>
+        <v>185.17</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>155.07</v>
+        <v>112.39</v>
       </c>
       <c r="K49" t="n">
-        <v>46.9</v>
+        <v>33.99</v>
       </c>
       <c r="L49" t="n">
-        <v>162</v>
+        <v>117.42</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-111.89</v>
+        <v>-60.75</v>
       </c>
       <c r="K50" t="n">
-        <v>940.95</v>
+        <v>510.83</v>
       </c>
       <c r="L50" t="n">
-        <v>947.58</v>
+        <v>514.4299999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>675.78</v>
+        <v>365.03</v>
       </c>
       <c r="K51" t="n">
-        <v>-208.48</v>
+        <v>-112.62</v>
       </c>
       <c r="L51" t="n">
-        <v>707.21</v>
+        <v>382.01</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>443.38</v>
+        <v>231.57</v>
       </c>
       <c r="K52" t="n">
-        <v>205.17</v>
+        <v>107.16</v>
       </c>
       <c r="L52" t="n">
-        <v>488.55</v>
+        <v>255.16</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-1123.37</v>
+        <v>-597.88</v>
       </c>
       <c r="K53" t="n">
-        <v>-916.83</v>
+        <v>-487.96</v>
       </c>
       <c r="L53" t="n">
-        <v>1450.01</v>
+        <v>771.73</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-571.72</v>
+        <v>-304.45</v>
       </c>
       <c r="K54" t="n">
-        <v>-705.08</v>
+        <v>-375.47</v>
       </c>
       <c r="L54" t="n">
-        <v>907.75</v>
+        <v>483.39</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-557.59</v>
+        <v>-315.93</v>
       </c>
       <c r="K55" t="n">
-        <v>410.94</v>
+        <v>232.84</v>
       </c>
       <c r="L55" t="n">
-        <v>692.66</v>
+        <v>392.47</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-663.6799999999999</v>
+        <v>-330.21</v>
       </c>
       <c r="K56" t="n">
-        <v>-713.4400000000001</v>
+        <v>-354.97</v>
       </c>
       <c r="L56" t="n">
-        <v>974.4</v>
+        <v>484.81</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>85.39</v>
+        <v>38.97</v>
       </c>
       <c r="K57" t="n">
-        <v>998.04</v>
+        <v>455.53</v>
       </c>
       <c r="L57" t="n">
-        <v>1001.69</v>
+        <v>457.2</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>1176.53</v>
+        <v>582.51</v>
       </c>
       <c r="K58" t="n">
-        <v>760.4400000000001</v>
+        <v>376.5</v>
       </c>
       <c r="L58" t="n">
-        <v>1400.88</v>
+        <v>693.6</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-367.34</v>
+        <v>-272.65</v>
       </c>
       <c r="K59" t="n">
-        <v>92.55</v>
+        <v>68.69</v>
       </c>
       <c r="L59" t="n">
-        <v>378.82</v>
+        <v>281.17</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-370.52</v>
+        <v>-271.83</v>
       </c>
       <c r="K60" t="n">
-        <v>104.34</v>
+        <v>76.55</v>
       </c>
       <c r="L60" t="n">
-        <v>384.93</v>
+        <v>282.4</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-213.66</v>
+        <v>-151.72</v>
       </c>
       <c r="K61" t="n">
-        <v>145.01</v>
+        <v>102.97</v>
       </c>
       <c r="L61" t="n">
-        <v>258.22</v>
+        <v>183.36</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-243.38</v>
+        <v>-154.29</v>
       </c>
       <c r="K62" t="n">
-        <v>95.48999999999999</v>
+        <v>60.54</v>
       </c>
       <c r="L62" t="n">
-        <v>261.45</v>
+        <v>165.74</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>133.97</v>
+        <v>81.14</v>
       </c>
       <c r="K63" t="n">
-        <v>576.26</v>
+        <v>349.03</v>
       </c>
       <c r="L63" t="n">
-        <v>591.63</v>
+        <v>358.34</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-491.25</v>
+        <v>-304.91</v>
       </c>
       <c r="K64" t="n">
-        <v>-228.36</v>
+        <v>-141.74</v>
       </c>
       <c r="L64" t="n">
-        <v>541.74</v>
+        <v>336.24</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-401.19</v>
+        <v>-257.71</v>
       </c>
       <c r="K65" t="n">
-        <v>82.01000000000001</v>
+        <v>52.68</v>
       </c>
       <c r="L65" t="n">
-        <v>409.49</v>
+        <v>263.04</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>206.12</v>
+        <v>110.73</v>
       </c>
       <c r="K66" t="n">
-        <v>769.4400000000001</v>
+        <v>413.34</v>
       </c>
       <c r="L66" t="n">
-        <v>796.5599999999999</v>
+        <v>427.92</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.34</v>
+        <v>-0.19</v>
       </c>
       <c r="K67" t="n">
-        <v>-498.45</v>
+        <v>-282.65</v>
       </c>
       <c r="L67" t="n">
-        <v>498.45</v>
+        <v>282.65</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-906.1</v>
+        <v>-431.3</v>
       </c>
       <c r="K68" t="n">
-        <v>-377.36</v>
+        <v>-179.62</v>
       </c>
       <c r="L68" t="n">
-        <v>981.54</v>
+        <v>467.21</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>13.9</v>
+        <v>7.67</v>
       </c>
       <c r="K69" t="n">
-        <v>-545.77</v>
+        <v>-301.17</v>
       </c>
       <c r="L69" t="n">
-        <v>545.95</v>
+        <v>301.27</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>787.03</v>
+        <v>445.15</v>
       </c>
       <c r="K70" t="n">
-        <v>-363.37</v>
+        <v>-205.53</v>
       </c>
       <c r="L70" t="n">
-        <v>866.86</v>
+        <v>490.31</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-1094.61</v>
+        <v>-562.35</v>
       </c>
       <c r="K71" t="n">
-        <v>-179.59</v>
+        <v>-92.26000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>1109.24</v>
+        <v>569.87</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-954.55</v>
+        <v>-412.29</v>
       </c>
       <c r="K72" t="n">
-        <v>-1267.23</v>
+        <v>-547.35</v>
       </c>
       <c r="L72" t="n">
-        <v>1586.52</v>
+        <v>685.26</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-656.02</v>
+        <v>-339.4</v>
       </c>
       <c r="K73" t="n">
-        <v>905.62</v>
+        <v>468.53</v>
       </c>
       <c r="L73" t="n">
-        <v>1118.27</v>
+        <v>578.54</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-31.36</v>
+        <v>-20.15</v>
       </c>
       <c r="K74" t="n">
-        <v>-181.64</v>
+        <v>-116.7</v>
       </c>
       <c r="L74" t="n">
-        <v>184.33</v>
+        <v>118.43</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-395.81</v>
+        <v>-255.65</v>
       </c>
       <c r="K75" t="n">
-        <v>-155.95</v>
+        <v>-100.73</v>
       </c>
       <c r="L75" t="n">
-        <v>425.42</v>
+        <v>274.78</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>181.73</v>
+        <v>138.84</v>
       </c>
       <c r="K76" t="n">
-        <v>-301.32</v>
+        <v>-230.21</v>
       </c>
       <c r="L76" t="n">
-        <v>351.88</v>
+        <v>268.84</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-82.38</v>
+        <v>-55.19</v>
       </c>
       <c r="K77" t="n">
-        <v>174.18</v>
+        <v>116.7</v>
       </c>
       <c r="L77" t="n">
-        <v>192.68</v>
+        <v>129.09</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>85.59999999999999</v>
+        <v>56.36</v>
       </c>
       <c r="K78" t="n">
-        <v>341.93</v>
+        <v>225.13</v>
       </c>
       <c r="L78" t="n">
-        <v>352.49</v>
+        <v>232.08</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-294.42</v>
+        <v>-206.89</v>
       </c>
       <c r="K79" t="n">
-        <v>-334.15</v>
+        <v>-234.82</v>
       </c>
       <c r="L79" t="n">
-        <v>445.35</v>
+        <v>312.96</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>354.53</v>
+        <v>199.05</v>
       </c>
       <c r="K80" t="n">
-        <v>263.48</v>
+        <v>147.93</v>
       </c>
       <c r="L80" t="n">
-        <v>441.71</v>
+        <v>248</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>193.65</v>
+        <v>102.41</v>
       </c>
       <c r="K81" t="n">
-        <v>-360.6</v>
+        <v>-190.71</v>
       </c>
       <c r="L81" t="n">
-        <v>409.31</v>
+        <v>216.47</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>21.19</v>
+        <v>12.99</v>
       </c>
       <c r="K82" t="n">
-        <v>339.49</v>
+        <v>208.09</v>
       </c>
       <c r="L82" t="n">
-        <v>340.15</v>
+        <v>208.5</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>401.75</v>
+        <v>211.89</v>
       </c>
       <c r="K83" t="n">
-        <v>216.95</v>
+        <v>114.42</v>
       </c>
       <c r="L83" t="n">
-        <v>456.58</v>
+        <v>240.81</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>622.12</v>
+        <v>297.11</v>
       </c>
       <c r="K84" t="n">
-        <v>454.6</v>
+        <v>217.1</v>
       </c>
       <c r="L84" t="n">
-        <v>770.51</v>
+        <v>367.98</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-618.52</v>
+        <v>-324.09</v>
       </c>
       <c r="K85" t="n">
-        <v>-761.34</v>
+        <v>-398.92</v>
       </c>
       <c r="L85" t="n">
-        <v>980.9299999999999</v>
+        <v>513.98</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-422.12</v>
+        <v>-190.62</v>
       </c>
       <c r="K86" t="n">
-        <v>-1323.96</v>
+        <v>-597.88</v>
       </c>
       <c r="L86" t="n">
-        <v>1389.63</v>
+        <v>627.53</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-94.48999999999999</v>
+        <v>-42.05</v>
       </c>
       <c r="K87" t="n">
-        <v>1252.06</v>
+        <v>557.26</v>
       </c>
       <c r="L87" t="n">
-        <v>1255.62</v>
+        <v>558.85</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>700.1</v>
+        <v>295.71</v>
       </c>
       <c r="K88" t="n">
-        <v>380.47</v>
+        <v>160.71</v>
       </c>
       <c r="L88" t="n">
-        <v>796.8</v>
+        <v>336.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>143.34</v>
+        <v>157.53</v>
       </c>
       <c r="K14" t="n">
-        <v>270.13</v>
+        <v>296.88</v>
       </c>
       <c r="L14" t="n">
-        <v>305.81</v>
+        <v>336.09</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>165.29</v>
+        <v>178.8</v>
       </c>
       <c r="K15" t="n">
-        <v>24.24</v>
+        <v>26.22</v>
       </c>
       <c r="L15" t="n">
-        <v>167.06</v>
+        <v>180.71</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>26.98</v>
+        <v>29.5</v>
       </c>
       <c r="K16" t="n">
-        <v>171.9</v>
+        <v>187.93</v>
       </c>
       <c r="L16" t="n">
-        <v>174</v>
+        <v>190.23</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-148.4</v>
+        <v>-160.18</v>
       </c>
       <c r="K17" t="n">
-        <v>-163.85</v>
+        <v>-176.85</v>
       </c>
       <c r="L17" t="n">
-        <v>221.07</v>
+        <v>238.61</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>141.08</v>
+        <v>155.66</v>
       </c>
       <c r="K18" t="n">
-        <v>-49.27</v>
+        <v>-54.36</v>
       </c>
       <c r="L18" t="n">
-        <v>149.43</v>
+        <v>164.87</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>171.54</v>
+        <v>184.54</v>
       </c>
       <c r="K19" t="n">
-        <v>96.08</v>
+        <v>103.36</v>
       </c>
       <c r="L19" t="n">
-        <v>196.61</v>
+        <v>211.51</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>104.34</v>
+        <v>116.64</v>
       </c>
       <c r="K20" t="n">
-        <v>258.3</v>
+        <v>288.74</v>
       </c>
       <c r="L20" t="n">
-        <v>278.57</v>
+        <v>311.41</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-114.26</v>
+        <v>-131.67</v>
       </c>
       <c r="K21" t="n">
-        <v>-191.76</v>
+        <v>-220.99</v>
       </c>
       <c r="L21" t="n">
-        <v>223.22</v>
+        <v>257.24</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>120.12</v>
+        <v>134.34</v>
       </c>
       <c r="K22" t="n">
-        <v>-255.89</v>
+        <v>-286.2</v>
       </c>
       <c r="L22" t="n">
-        <v>282.68</v>
+        <v>316.17</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-61.15</v>
+        <v>-71.06999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>290.69</v>
+        <v>337.86</v>
       </c>
       <c r="L23" t="n">
-        <v>297.06</v>
+        <v>345.25</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-26.08</v>
+        <v>-30.36</v>
       </c>
       <c r="K24" t="n">
-        <v>-206.38</v>
+        <v>-240.29</v>
       </c>
       <c r="L24" t="n">
-        <v>208.02</v>
+        <v>242.2</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-212.28</v>
+        <v>-248.12</v>
       </c>
       <c r="K25" t="n">
-        <v>225.71</v>
+        <v>263.82</v>
       </c>
       <c r="L25" t="n">
-        <v>309.85</v>
+        <v>362.16</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-297.27</v>
+        <v>-357.06</v>
       </c>
       <c r="K26" t="n">
-        <v>39.58</v>
+        <v>47.54</v>
       </c>
       <c r="L26" t="n">
-        <v>299.89</v>
+        <v>360.21</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-226.04</v>
+        <v>-268.45</v>
       </c>
       <c r="K27" t="n">
-        <v>410.85</v>
+        <v>487.93</v>
       </c>
       <c r="L27" t="n">
-        <v>468.93</v>
+        <v>556.91</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-68.09999999999999</v>
+        <v>-78.97</v>
       </c>
       <c r="K28" t="n">
-        <v>537</v>
+        <v>622.72</v>
       </c>
       <c r="L28" t="n">
-        <v>541.3</v>
+        <v>627.7</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="K29" t="n">
-        <v>239.27</v>
+        <v>267.31</v>
       </c>
       <c r="L29" t="n">
-        <v>239.28</v>
+        <v>267.32</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>269.71</v>
+        <v>294.12</v>
       </c>
       <c r="K30" t="n">
-        <v>139.76</v>
+        <v>152.41</v>
       </c>
       <c r="L30" t="n">
-        <v>303.77</v>
+        <v>331.26</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>205.21</v>
+        <v>226.34</v>
       </c>
       <c r="K31" t="n">
-        <v>-116.06</v>
+        <v>-128.01</v>
       </c>
       <c r="L31" t="n">
-        <v>235.76</v>
+        <v>260.03</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-193.75</v>
+        <v>-210.47</v>
       </c>
       <c r="K32" t="n">
-        <v>-187.12</v>
+        <v>-203.26</v>
       </c>
       <c r="L32" t="n">
-        <v>269.36</v>
+        <v>292.6</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-50.51</v>
+        <v>-55.25</v>
       </c>
       <c r="K33" t="n">
-        <v>151.32</v>
+        <v>165.51</v>
       </c>
       <c r="L33" t="n">
-        <v>159.53</v>
+        <v>174.49</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>46.26</v>
+        <v>50.74</v>
       </c>
       <c r="K34" t="n">
-        <v>-180.58</v>
+        <v>-198.05</v>
       </c>
       <c r="L34" t="n">
-        <v>186.41</v>
+        <v>204.45</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-363.4</v>
+        <v>-419.94</v>
       </c>
       <c r="K35" t="n">
-        <v>-310.41</v>
+        <v>-358.7</v>
       </c>
       <c r="L35" t="n">
-        <v>477.93</v>
+        <v>552.29</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-241.64</v>
+        <v>-279.23</v>
       </c>
       <c r="K36" t="n">
-        <v>209.35</v>
+        <v>241.92</v>
       </c>
       <c r="L36" t="n">
-        <v>319.71</v>
+        <v>369.45</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-38.04</v>
+        <v>-42.02</v>
       </c>
       <c r="K37" t="n">
-        <v>-249.58</v>
+        <v>-275.71</v>
       </c>
       <c r="L37" t="n">
-        <v>252.46</v>
+        <v>278.89</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-359.41</v>
+        <v>-418.76</v>
       </c>
       <c r="K38" t="n">
-        <v>481.63</v>
+        <v>561.16</v>
       </c>
       <c r="L38" t="n">
-        <v>600.95</v>
+        <v>700.1799999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-454.56</v>
+        <v>-522.83</v>
       </c>
       <c r="K39" t="n">
-        <v>-10.45</v>
+        <v>-12.02</v>
       </c>
       <c r="L39" t="n">
-        <v>454.68</v>
+        <v>522.96</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-284.71</v>
+        <v>-327.94</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.69</v>
+        <v>-1.95</v>
       </c>
       <c r="L40" t="n">
-        <v>284.72</v>
+        <v>327.95</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-728.03</v>
+        <v>-852.27</v>
       </c>
       <c r="K41" t="n">
-        <v>528.51</v>
+        <v>618.7</v>
       </c>
       <c r="L41" t="n">
-        <v>899.64</v>
+        <v>1053.17</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-207.42</v>
+        <v>-242.06</v>
       </c>
       <c r="K42" t="n">
-        <v>-265.8</v>
+        <v>-310.19</v>
       </c>
       <c r="L42" t="n">
-        <v>337.15</v>
+        <v>393.46</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-145.65</v>
+        <v>-170.07</v>
       </c>
       <c r="K43" t="n">
-        <v>649.9299999999999</v>
+        <v>758.91</v>
       </c>
       <c r="L43" t="n">
-        <v>666.05</v>
+        <v>777.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-94.97</v>
+        <v>-103.25</v>
       </c>
       <c r="K44" t="n">
-        <v>-82.56</v>
+        <v>-89.76000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>125.84</v>
+        <v>136.81</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-233.35</v>
+        <v>-263.32</v>
       </c>
       <c r="K45" t="n">
-        <v>-387.09</v>
+        <v>-436.81</v>
       </c>
       <c r="L45" t="n">
-        <v>451.99</v>
+        <v>510.04</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>145.51</v>
+        <v>158.65</v>
       </c>
       <c r="K46" t="n">
-        <v>-126.29</v>
+        <v>-137.69</v>
       </c>
       <c r="L46" t="n">
-        <v>192.67</v>
+        <v>210.07</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-158.5</v>
+        <v>-177.43</v>
       </c>
       <c r="K47" t="n">
-        <v>-14.61</v>
+        <v>-16.36</v>
       </c>
       <c r="L47" t="n">
-        <v>159.17</v>
+        <v>178.18</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-51.36</v>
+        <v>-57.29</v>
       </c>
       <c r="K48" t="n">
-        <v>177.91</v>
+        <v>198.47</v>
       </c>
       <c r="L48" t="n">
-        <v>185.17</v>
+        <v>206.57</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>112.39</v>
+        <v>122.48</v>
       </c>
       <c r="K49" t="n">
-        <v>33.99</v>
+        <v>37.05</v>
       </c>
       <c r="L49" t="n">
-        <v>117.42</v>
+        <v>127.96</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-60.75</v>
+        <v>-69.3</v>
       </c>
       <c r="K50" t="n">
-        <v>510.83</v>
+        <v>582.8099999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>514.4299999999999</v>
+        <v>586.91</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>365.03</v>
+        <v>418.97</v>
       </c>
       <c r="K51" t="n">
-        <v>-112.62</v>
+        <v>-129.26</v>
       </c>
       <c r="L51" t="n">
-        <v>382.01</v>
+        <v>438.46</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>231.57</v>
+        <v>261.34</v>
       </c>
       <c r="K52" t="n">
-        <v>107.16</v>
+        <v>120.93</v>
       </c>
       <c r="L52" t="n">
-        <v>255.16</v>
+        <v>287.96</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-597.88</v>
+        <v>-688.41</v>
       </c>
       <c r="K53" t="n">
-        <v>-487.96</v>
+        <v>-561.85</v>
       </c>
       <c r="L53" t="n">
-        <v>771.73</v>
+        <v>888.58</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-304.45</v>
+        <v>-350.74</v>
       </c>
       <c r="K54" t="n">
-        <v>-375.47</v>
+        <v>-432.55</v>
       </c>
       <c r="L54" t="n">
-        <v>483.39</v>
+        <v>556.88</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-315.93</v>
+        <v>-358.62</v>
       </c>
       <c r="K55" t="n">
-        <v>232.84</v>
+        <v>264.3</v>
       </c>
       <c r="L55" t="n">
-        <v>392.47</v>
+        <v>445.49</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-330.21</v>
+        <v>-381.37</v>
       </c>
       <c r="K56" t="n">
-        <v>-354.97</v>
+        <v>-409.97</v>
       </c>
       <c r="L56" t="n">
-        <v>484.81</v>
+        <v>559.92</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>38.97</v>
+        <v>46.8</v>
       </c>
       <c r="K57" t="n">
-        <v>455.53</v>
+        <v>547.03</v>
       </c>
       <c r="L57" t="n">
-        <v>457.2</v>
+        <v>549.03</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>582.51</v>
+        <v>681.4400000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>376.5</v>
+        <v>440.44</v>
       </c>
       <c r="L58" t="n">
-        <v>693.6</v>
+        <v>811.39</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-272.65</v>
+        <v>-298.46</v>
       </c>
       <c r="K59" t="n">
-        <v>68.69</v>
+        <v>75.19</v>
       </c>
       <c r="L59" t="n">
-        <v>281.17</v>
+        <v>307.79</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-271.83</v>
+        <v>-295.6</v>
       </c>
       <c r="K60" t="n">
-        <v>76.55</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>282.4</v>
+        <v>307.1</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-151.72</v>
+        <v>-165.79</v>
       </c>
       <c r="K61" t="n">
-        <v>102.97</v>
+        <v>112.51</v>
       </c>
       <c r="L61" t="n">
-        <v>183.36</v>
+        <v>200.36</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-154.29</v>
+        <v>-171.21</v>
       </c>
       <c r="K62" t="n">
-        <v>60.54</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>165.74</v>
+        <v>183.92</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>81.14</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>349.03</v>
+        <v>389.58</v>
       </c>
       <c r="L63" t="n">
-        <v>358.34</v>
+        <v>399.96</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-304.91</v>
+        <v>-338.38</v>
       </c>
       <c r="K64" t="n">
-        <v>-141.74</v>
+        <v>-157.3</v>
       </c>
       <c r="L64" t="n">
-        <v>336.24</v>
+        <v>373.16</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-257.71</v>
+        <v>-288</v>
       </c>
       <c r="K65" t="n">
-        <v>52.68</v>
+        <v>58.87</v>
       </c>
       <c r="L65" t="n">
-        <v>263.04</v>
+        <v>293.95</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>110.73</v>
+        <v>125.9</v>
       </c>
       <c r="K66" t="n">
-        <v>413.34</v>
+        <v>469.97</v>
       </c>
       <c r="L66" t="n">
-        <v>427.92</v>
+        <v>486.54</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="K67" t="n">
-        <v>-282.65</v>
+        <v>-319.06</v>
       </c>
       <c r="L67" t="n">
-        <v>282.65</v>
+        <v>319.06</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-431.3</v>
+        <v>-501.05</v>
       </c>
       <c r="K68" t="n">
-        <v>-179.62</v>
+        <v>-208.67</v>
       </c>
       <c r="L68" t="n">
-        <v>467.21</v>
+        <v>542.76</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>7.67</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-301.17</v>
+        <v>-347.77</v>
       </c>
       <c r="L69" t="n">
-        <v>301.27</v>
+        <v>347.88</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>445.15</v>
+        <v>503.94</v>
       </c>
       <c r="K70" t="n">
-        <v>-205.53</v>
+        <v>-232.67</v>
       </c>
       <c r="L70" t="n">
-        <v>490.31</v>
+        <v>555.0599999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-562.35</v>
+        <v>-652.21</v>
       </c>
       <c r="K71" t="n">
-        <v>-92.26000000000001</v>
+        <v>-107</v>
       </c>
       <c r="L71" t="n">
-        <v>569.87</v>
+        <v>660.9299999999999</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-412.29</v>
+        <v>-484.8</v>
       </c>
       <c r="K72" t="n">
-        <v>-547.35</v>
+        <v>-643.61</v>
       </c>
       <c r="L72" t="n">
-        <v>685.26</v>
+        <v>805.77</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-339.4</v>
+        <v>-392.41</v>
       </c>
       <c r="K73" t="n">
-        <v>468.53</v>
+        <v>541.71</v>
       </c>
       <c r="L73" t="n">
-        <v>578.54</v>
+        <v>668.91</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-20.15</v>
+        <v>-22.33</v>
       </c>
       <c r="K74" t="n">
-        <v>-116.7</v>
+        <v>-129.36</v>
       </c>
       <c r="L74" t="n">
-        <v>118.43</v>
+        <v>131.27</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-255.65</v>
+        <v>-282.73</v>
       </c>
       <c r="K75" t="n">
-        <v>-100.73</v>
+        <v>-111.39</v>
       </c>
       <c r="L75" t="n">
-        <v>274.78</v>
+        <v>303.88</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>138.84</v>
+        <v>151.48</v>
       </c>
       <c r="K76" t="n">
-        <v>-230.21</v>
+        <v>-251.16</v>
       </c>
       <c r="L76" t="n">
-        <v>268.84</v>
+        <v>293.31</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-55.19</v>
+        <v>-60.88</v>
       </c>
       <c r="K77" t="n">
-        <v>116.7</v>
+        <v>128.73</v>
       </c>
       <c r="L77" t="n">
-        <v>129.09</v>
+        <v>142.4</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>56.36</v>
+        <v>62.11</v>
       </c>
       <c r="K78" t="n">
-        <v>225.13</v>
+        <v>248.09</v>
       </c>
       <c r="L78" t="n">
-        <v>232.08</v>
+        <v>255.75</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-206.89</v>
+        <v>-227.74</v>
       </c>
       <c r="K79" t="n">
-        <v>-234.82</v>
+        <v>-258.48</v>
       </c>
       <c r="L79" t="n">
-        <v>312.96</v>
+        <v>344.5</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>199.05</v>
+        <v>227.15</v>
       </c>
       <c r="K80" t="n">
-        <v>147.93</v>
+        <v>168.81</v>
       </c>
       <c r="L80" t="n">
-        <v>248</v>
+        <v>283.01</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>102.41</v>
+        <v>118.3</v>
       </c>
       <c r="K81" t="n">
-        <v>-190.71</v>
+        <v>-220.3</v>
       </c>
       <c r="L81" t="n">
-        <v>216.47</v>
+        <v>250.05</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>12.99</v>
+        <v>14.66</v>
       </c>
       <c r="K82" t="n">
-        <v>208.09</v>
+        <v>234.82</v>
       </c>
       <c r="L82" t="n">
-        <v>208.5</v>
+        <v>235.27</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>211.89</v>
+        <v>242.78</v>
       </c>
       <c r="K83" t="n">
-        <v>114.42</v>
+        <v>131.1</v>
       </c>
       <c r="L83" t="n">
-        <v>240.81</v>
+        <v>275.91</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>297.11</v>
+        <v>345.67</v>
       </c>
       <c r="K84" t="n">
-        <v>217.1</v>
+        <v>252.59</v>
       </c>
       <c r="L84" t="n">
-        <v>367.98</v>
+        <v>428.13</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-324.09</v>
+        <v>-373.44</v>
       </c>
       <c r="K85" t="n">
-        <v>-398.92</v>
+        <v>-459.66</v>
       </c>
       <c r="L85" t="n">
-        <v>513.98</v>
+        <v>592.24</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-190.62</v>
+        <v>-222.97</v>
       </c>
       <c r="K86" t="n">
-        <v>-597.88</v>
+        <v>-699.34</v>
       </c>
       <c r="L86" t="n">
-        <v>627.53</v>
+        <v>734.02</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-42.05</v>
+        <v>-49.02</v>
       </c>
       <c r="K87" t="n">
-        <v>557.26</v>
+        <v>649.6</v>
       </c>
       <c r="L87" t="n">
-        <v>558.85</v>
+        <v>651.45</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>295.71</v>
+        <v>351.36</v>
       </c>
       <c r="K88" t="n">
-        <v>160.71</v>
+        <v>190.95</v>
       </c>
       <c r="L88" t="n">
-        <v>336.56</v>
+        <v>399.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>157.53</v>
+        <v>64.27</v>
       </c>
       <c r="K14" t="n">
-        <v>296.88</v>
+        <v>121.12</v>
       </c>
       <c r="L14" t="n">
-        <v>336.09</v>
+        <v>137.11</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>178.8</v>
+        <v>71.69</v>
       </c>
       <c r="K15" t="n">
-        <v>26.22</v>
+        <v>10.51</v>
       </c>
       <c r="L15" t="n">
-        <v>180.71</v>
+        <v>72.45999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>29.5</v>
+        <v>11.88</v>
       </c>
       <c r="K16" t="n">
-        <v>187.93</v>
+        <v>75.67</v>
       </c>
       <c r="L16" t="n">
-        <v>190.23</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-160.18</v>
+        <v>-68.83</v>
       </c>
       <c r="K17" t="n">
-        <v>-176.85</v>
+        <v>-75.98999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>238.61</v>
+        <v>102.53</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>155.66</v>
+        <v>66.44</v>
       </c>
       <c r="K18" t="n">
-        <v>-54.36</v>
+        <v>-23.2</v>
       </c>
       <c r="L18" t="n">
-        <v>164.87</v>
+        <v>70.37</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>184.54</v>
+        <v>77.42</v>
       </c>
       <c r="K19" t="n">
-        <v>103.36</v>
+        <v>43.36</v>
       </c>
       <c r="L19" t="n">
-        <v>211.51</v>
+        <v>88.73999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>116.64</v>
+        <v>55.73</v>
       </c>
       <c r="K20" t="n">
-        <v>288.74</v>
+        <v>137.97</v>
       </c>
       <c r="L20" t="n">
-        <v>311.41</v>
+        <v>148.8</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-131.67</v>
+        <v>-63.04</v>
       </c>
       <c r="K21" t="n">
-        <v>-220.99</v>
+        <v>-105.8</v>
       </c>
       <c r="L21" t="n">
-        <v>257.24</v>
+        <v>123.15</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>134.34</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-286.2</v>
+        <v>-137.03</v>
       </c>
       <c r="L22" t="n">
-        <v>316.17</v>
+        <v>151.38</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-71.06999999999999</v>
+        <v>-31.3</v>
       </c>
       <c r="K23" t="n">
-        <v>337.86</v>
+        <v>148.81</v>
       </c>
       <c r="L23" t="n">
-        <v>345.25</v>
+        <v>152.07</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-30.36</v>
+        <v>-13.66</v>
       </c>
       <c r="K24" t="n">
-        <v>-240.29</v>
+        <v>-108.09</v>
       </c>
       <c r="L24" t="n">
-        <v>242.2</v>
+        <v>108.94</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-248.12</v>
+        <v>-113.7</v>
       </c>
       <c r="K25" t="n">
-        <v>263.82</v>
+        <v>120.9</v>
       </c>
       <c r="L25" t="n">
-        <v>362.16</v>
+        <v>165.97</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-357.06</v>
+        <v>-193.03</v>
       </c>
       <c r="K26" t="n">
-        <v>47.54</v>
+        <v>25.7</v>
       </c>
       <c r="L26" t="n">
-        <v>360.21</v>
+        <v>194.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-268.45</v>
+        <v>-145.68</v>
       </c>
       <c r="K27" t="n">
-        <v>487.93</v>
+        <v>264.78</v>
       </c>
       <c r="L27" t="n">
-        <v>556.91</v>
+        <v>302.21</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-78.97</v>
+        <v>-43.51</v>
       </c>
       <c r="K28" t="n">
-        <v>622.72</v>
+        <v>343.1</v>
       </c>
       <c r="L28" t="n">
-        <v>627.7</v>
+        <v>345.85</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>2.56</v>
+        <v>1.05</v>
       </c>
       <c r="K29" t="n">
-        <v>267.31</v>
+        <v>109.18</v>
       </c>
       <c r="L29" t="n">
-        <v>267.32</v>
+        <v>109.18</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>294.12</v>
+        <v>118.75</v>
       </c>
       <c r="K30" t="n">
-        <v>152.41</v>
+        <v>61.53</v>
       </c>
       <c r="L30" t="n">
-        <v>331.26</v>
+        <v>133.74</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>226.34</v>
+        <v>92.02</v>
       </c>
       <c r="K31" t="n">
-        <v>-128.01</v>
+        <v>-52.04</v>
       </c>
       <c r="L31" t="n">
-        <v>260.03</v>
+        <v>105.71</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-210.47</v>
+        <v>-91.40000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-203.26</v>
+        <v>-88.27</v>
       </c>
       <c r="L32" t="n">
-        <v>292.6</v>
+        <v>127.06</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-55.25</v>
+        <v>-24.05</v>
       </c>
       <c r="K33" t="n">
-        <v>165.51</v>
+        <v>72.03</v>
       </c>
       <c r="L33" t="n">
-        <v>174.49</v>
+        <v>75.94</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>50.74</v>
+        <v>22.01</v>
       </c>
       <c r="K34" t="n">
-        <v>-198.05</v>
+        <v>-85.91</v>
       </c>
       <c r="L34" t="n">
-        <v>204.45</v>
+        <v>88.68000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-419.94</v>
+        <v>-201.12</v>
       </c>
       <c r="K35" t="n">
-        <v>-358.7</v>
+        <v>-171.79</v>
       </c>
       <c r="L35" t="n">
-        <v>552.29</v>
+        <v>264.5</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-279.23</v>
+        <v>-133.67</v>
       </c>
       <c r="K36" t="n">
-        <v>241.92</v>
+        <v>115.81</v>
       </c>
       <c r="L36" t="n">
-        <v>369.45</v>
+        <v>176.85</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-42.02</v>
+        <v>-20.14</v>
       </c>
       <c r="K37" t="n">
-        <v>-275.71</v>
+        <v>-132.14</v>
       </c>
       <c r="L37" t="n">
-        <v>278.89</v>
+        <v>133.66</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-418.76</v>
+        <v>-195.55</v>
       </c>
       <c r="K38" t="n">
-        <v>561.16</v>
+        <v>262.05</v>
       </c>
       <c r="L38" t="n">
-        <v>700.1799999999999</v>
+        <v>326.97</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-522.83</v>
+        <v>-249.25</v>
       </c>
       <c r="K39" t="n">
-        <v>-12.02</v>
+        <v>-5.73</v>
       </c>
       <c r="L39" t="n">
-        <v>522.96</v>
+        <v>249.31</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-327.94</v>
+        <v>-156.34</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.95</v>
+        <v>-0.93</v>
       </c>
       <c r="L40" t="n">
-        <v>327.95</v>
+        <v>156.34</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-852.27</v>
+        <v>-467.68</v>
       </c>
       <c r="K41" t="n">
-        <v>618.7</v>
+        <v>339.51</v>
       </c>
       <c r="L41" t="n">
-        <v>1053.17</v>
+        <v>577.9299999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-242.06</v>
+        <v>-131.18</v>
       </c>
       <c r="K42" t="n">
-        <v>-310.19</v>
+        <v>-168.1</v>
       </c>
       <c r="L42" t="n">
-        <v>393.46</v>
+        <v>213.23</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-170.07</v>
+        <v>-93.37</v>
       </c>
       <c r="K43" t="n">
-        <v>758.91</v>
+        <v>416.65</v>
       </c>
       <c r="L43" t="n">
-        <v>777.74</v>
+        <v>426.98</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-103.25</v>
+        <v>-41.73</v>
       </c>
       <c r="K44" t="n">
-        <v>-89.76000000000001</v>
+        <v>-36.27</v>
       </c>
       <c r="L44" t="n">
-        <v>136.81</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-263.32</v>
+        <v>-108.89</v>
       </c>
       <c r="K45" t="n">
-        <v>-436.81</v>
+        <v>-180.63</v>
       </c>
       <c r="L45" t="n">
-        <v>510.04</v>
+        <v>210.91</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>158.65</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-137.69</v>
+        <v>-56.76</v>
       </c>
       <c r="L46" t="n">
-        <v>210.07</v>
+        <v>86.59</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-177.43</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-16.36</v>
+        <v>-7.1</v>
       </c>
       <c r="L47" t="n">
-        <v>178.18</v>
+        <v>77.29000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-57.29</v>
+        <v>-25.16</v>
       </c>
       <c r="K48" t="n">
-        <v>198.47</v>
+        <v>87.16</v>
       </c>
       <c r="L48" t="n">
-        <v>206.57</v>
+        <v>90.72</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>122.48</v>
+        <v>50.36</v>
       </c>
       <c r="K49" t="n">
-        <v>37.05</v>
+        <v>15.23</v>
       </c>
       <c r="L49" t="n">
-        <v>127.96</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-69.3</v>
+        <v>-33.2</v>
       </c>
       <c r="K50" t="n">
-        <v>582.8099999999999</v>
+        <v>279.19</v>
       </c>
       <c r="L50" t="n">
-        <v>586.91</v>
+        <v>281.16</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>418.97</v>
+        <v>200.81</v>
       </c>
       <c r="K51" t="n">
-        <v>-129.26</v>
+        <v>-61.95</v>
       </c>
       <c r="L51" t="n">
-        <v>438.46</v>
+        <v>210.15</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>261.34</v>
+        <v>125.33</v>
       </c>
       <c r="K52" t="n">
-        <v>120.93</v>
+        <v>58</v>
       </c>
       <c r="L52" t="n">
-        <v>287.96</v>
+        <v>138.1</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-688.41</v>
+        <v>-321.48</v>
       </c>
       <c r="K53" t="n">
-        <v>-561.85</v>
+        <v>-262.37</v>
       </c>
       <c r="L53" t="n">
-        <v>888.58</v>
+        <v>414.95</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-350.74</v>
+        <v>-163.59</v>
       </c>
       <c r="K54" t="n">
-        <v>-432.55</v>
+        <v>-201.75</v>
       </c>
       <c r="L54" t="n">
-        <v>556.88</v>
+        <v>259.74</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-358.62</v>
+        <v>-172.06</v>
       </c>
       <c r="K55" t="n">
-        <v>264.3</v>
+        <v>126.81</v>
       </c>
       <c r="L55" t="n">
-        <v>445.49</v>
+        <v>213.74</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-381.37</v>
+        <v>-211.15</v>
       </c>
       <c r="K56" t="n">
-        <v>-409.97</v>
+        <v>-226.98</v>
       </c>
       <c r="L56" t="n">
-        <v>559.92</v>
+        <v>310.01</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>46.8</v>
+        <v>25.42</v>
       </c>
       <c r="K57" t="n">
-        <v>547.03</v>
+        <v>297.09</v>
       </c>
       <c r="L57" t="n">
-        <v>549.03</v>
+        <v>298.17</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>681.4400000000001</v>
+        <v>379.58</v>
       </c>
       <c r="K58" t="n">
-        <v>440.44</v>
+        <v>245.33</v>
       </c>
       <c r="L58" t="n">
-        <v>811.39</v>
+        <v>451.96</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-298.46</v>
+        <v>-121.67</v>
       </c>
       <c r="K59" t="n">
-        <v>75.19</v>
+        <v>30.65</v>
       </c>
       <c r="L59" t="n">
-        <v>307.79</v>
+        <v>125.48</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-295.6</v>
+        <v>-121.61</v>
       </c>
       <c r="K60" t="n">
-        <v>83.23999999999999</v>
+        <v>34.24</v>
       </c>
       <c r="L60" t="n">
-        <v>307.1</v>
+        <v>126.34</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-165.79</v>
+        <v>-68.01000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>112.51</v>
+        <v>46.16</v>
       </c>
       <c r="L61" t="n">
-        <v>200.36</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-171.21</v>
+        <v>-76.37</v>
       </c>
       <c r="K62" t="n">
-        <v>67.18000000000001</v>
+        <v>29.97</v>
       </c>
       <c r="L62" t="n">
-        <v>183.92</v>
+        <v>82.04000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>90.56999999999999</v>
+        <v>39.67</v>
       </c>
       <c r="K63" t="n">
-        <v>389.58</v>
+        <v>170.62</v>
       </c>
       <c r="L63" t="n">
-        <v>399.96</v>
+        <v>175.17</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-338.38</v>
+        <v>-149.03</v>
       </c>
       <c r="K64" t="n">
-        <v>-157.3</v>
+        <v>-69.28</v>
       </c>
       <c r="L64" t="n">
-        <v>373.16</v>
+        <v>164.35</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-288</v>
+        <v>-138</v>
       </c>
       <c r="K65" t="n">
-        <v>58.87</v>
+        <v>28.21</v>
       </c>
       <c r="L65" t="n">
-        <v>293.95</v>
+        <v>140.85</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>125.9</v>
+        <v>60.38</v>
       </c>
       <c r="K66" t="n">
-        <v>469.97</v>
+        <v>225.39</v>
       </c>
       <c r="L66" t="n">
-        <v>486.54</v>
+        <v>233.34</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="K67" t="n">
-        <v>-319.06</v>
+        <v>-152.62</v>
       </c>
       <c r="L67" t="n">
-        <v>319.06</v>
+        <v>152.62</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-501.05</v>
+        <v>-242.3</v>
       </c>
       <c r="K68" t="n">
-        <v>-208.67</v>
+        <v>-100.91</v>
       </c>
       <c r="L68" t="n">
-        <v>542.76</v>
+        <v>262.47</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>8.859999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="K69" t="n">
-        <v>-347.77</v>
+        <v>-162.4</v>
       </c>
       <c r="L69" t="n">
-        <v>347.88</v>
+        <v>162.46</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>503.94</v>
+        <v>242.71</v>
       </c>
       <c r="K70" t="n">
-        <v>-232.67</v>
+        <v>-112.06</v>
       </c>
       <c r="L70" t="n">
-        <v>555.0599999999999</v>
+        <v>267.34</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-652.21</v>
+        <v>-364.09</v>
       </c>
       <c r="K71" t="n">
-        <v>-107</v>
+        <v>-59.74</v>
       </c>
       <c r="L71" t="n">
-        <v>660.9299999999999</v>
+        <v>368.96</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-484.8</v>
+        <v>-271.6</v>
       </c>
       <c r="K72" t="n">
-        <v>-643.61</v>
+        <v>-360.56</v>
       </c>
       <c r="L72" t="n">
-        <v>805.77</v>
+        <v>451.41</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-392.41</v>
+        <v>-217.17</v>
       </c>
       <c r="K73" t="n">
-        <v>541.71</v>
+        <v>299.8</v>
       </c>
       <c r="L73" t="n">
-        <v>668.91</v>
+        <v>370.19</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-22.33</v>
+        <v>-1.34</v>
       </c>
       <c r="K74" t="n">
-        <v>-129.36</v>
+        <v>-7.76</v>
       </c>
       <c r="L74" t="n">
-        <v>131.27</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-282.73</v>
+        <v>-115.9</v>
       </c>
       <c r="K75" t="n">
-        <v>-111.39</v>
+        <v>-45.66</v>
       </c>
       <c r="L75" t="n">
-        <v>303.88</v>
+        <v>124.57</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>151.48</v>
+        <v>62.23</v>
       </c>
       <c r="K76" t="n">
-        <v>-251.16</v>
+        <v>-103.18</v>
       </c>
       <c r="L76" t="n">
-        <v>293.31</v>
+        <v>120.49</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-60.88</v>
+        <v>-24.6</v>
       </c>
       <c r="K77" t="n">
-        <v>128.73</v>
+        <v>52.01</v>
       </c>
       <c r="L77" t="n">
-        <v>142.4</v>
+        <v>57.53</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>62.11</v>
+        <v>27.46</v>
       </c>
       <c r="K78" t="n">
-        <v>248.09</v>
+        <v>109.71</v>
       </c>
       <c r="L78" t="n">
-        <v>255.75</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-227.74</v>
+        <v>-101.43</v>
       </c>
       <c r="K79" t="n">
-        <v>-258.48</v>
+        <v>-115.12</v>
       </c>
       <c r="L79" t="n">
-        <v>344.5</v>
+        <v>153.43</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>227.15</v>
+        <v>108.77</v>
       </c>
       <c r="K80" t="n">
-        <v>168.81</v>
+        <v>80.84</v>
       </c>
       <c r="L80" t="n">
-        <v>283.01</v>
+        <v>135.52</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>118.3</v>
+        <v>56.66</v>
       </c>
       <c r="K81" t="n">
-        <v>-220.3</v>
+        <v>-105.51</v>
       </c>
       <c r="L81" t="n">
-        <v>250.05</v>
+        <v>119.76</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>14.66</v>
+        <v>7.03</v>
       </c>
       <c r="K82" t="n">
-        <v>234.82</v>
+        <v>112.61</v>
       </c>
       <c r="L82" t="n">
-        <v>235.27</v>
+        <v>112.83</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>242.78</v>
+        <v>106.2</v>
       </c>
       <c r="K83" t="n">
-        <v>131.1</v>
+        <v>57.35</v>
       </c>
       <c r="L83" t="n">
-        <v>275.91</v>
+        <v>120.7</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>345.67</v>
+        <v>165.96</v>
       </c>
       <c r="K84" t="n">
-        <v>252.59</v>
+        <v>121.27</v>
       </c>
       <c r="L84" t="n">
-        <v>428.13</v>
+        <v>205.54</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-373.44</v>
+        <v>-180.48</v>
       </c>
       <c r="K85" t="n">
-        <v>-459.66</v>
+        <v>-222.15</v>
       </c>
       <c r="L85" t="n">
-        <v>592.24</v>
+        <v>286.22</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-222.97</v>
+        <v>-122.69</v>
       </c>
       <c r="K86" t="n">
-        <v>-699.34</v>
+        <v>-384.81</v>
       </c>
       <c r="L86" t="n">
-        <v>734.02</v>
+        <v>403.89</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-49.02</v>
+        <v>-27.46</v>
       </c>
       <c r="K87" t="n">
-        <v>649.6</v>
+        <v>363.92</v>
       </c>
       <c r="L87" t="n">
-        <v>651.45</v>
+        <v>364.95</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>351.36</v>
+        <v>195.38</v>
       </c>
       <c r="K88" t="n">
-        <v>190.95</v>
+        <v>106.18</v>
       </c>
       <c r="L88" t="n">
-        <v>399.9</v>
+        <v>222.37</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>64.27</v>
+        <v>48.55</v>
       </c>
       <c r="K14" t="n">
-        <v>121.12</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>137.11</v>
+        <v>103.57</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>71.69</v>
+        <v>68.95</v>
       </c>
       <c r="K15" t="n">
-        <v>10.51</v>
+        <v>10.11</v>
       </c>
       <c r="L15" t="n">
-        <v>72.45999999999999</v>
+        <v>69.69</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>11.88</v>
+        <v>10.19</v>
       </c>
       <c r="K16" t="n">
-        <v>75.67</v>
+        <v>64.95</v>
       </c>
       <c r="L16" t="n">
-        <v>76.59999999999999</v>
+        <v>65.73999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-68.83</v>
+        <v>-58.4</v>
       </c>
       <c r="K17" t="n">
-        <v>-75.98999999999999</v>
+        <v>-64.48</v>
       </c>
       <c r="L17" t="n">
-        <v>102.53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>66.44</v>
+        <v>60.39</v>
       </c>
       <c r="K18" t="n">
-        <v>-23.2</v>
+        <v>-21.09</v>
       </c>
       <c r="L18" t="n">
-        <v>70.37</v>
+        <v>63.96</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>77.42</v>
+        <v>70.67</v>
       </c>
       <c r="K19" t="n">
-        <v>43.36</v>
+        <v>39.58</v>
       </c>
       <c r="L19" t="n">
-        <v>88.73999999999999</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>55.73</v>
+        <v>54.06</v>
       </c>
       <c r="K20" t="n">
-        <v>137.97</v>
+        <v>133.82</v>
       </c>
       <c r="L20" t="n">
-        <v>148.8</v>
+        <v>144.33</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-63.04</v>
+        <v>-64.55</v>
       </c>
       <c r="K21" t="n">
-        <v>-105.8</v>
+        <v>-108.33</v>
       </c>
       <c r="L21" t="n">
-        <v>123.15</v>
+        <v>126.1</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>64.31999999999999</v>
+        <v>62.94</v>
       </c>
       <c r="K22" t="n">
-        <v>-137.03</v>
+        <v>-134.09</v>
       </c>
       <c r="L22" t="n">
-        <v>151.38</v>
+        <v>148.13</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-31.3</v>
+        <v>-32.87</v>
       </c>
       <c r="K23" t="n">
-        <v>148.81</v>
+        <v>156.26</v>
       </c>
       <c r="L23" t="n">
-        <v>152.07</v>
+        <v>159.68</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-13.66</v>
+        <v>-16.05</v>
       </c>
       <c r="K24" t="n">
-        <v>-108.09</v>
+        <v>-127.04</v>
       </c>
       <c r="L24" t="n">
-        <v>108.94</v>
+        <v>128.05</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-113.7</v>
+        <v>-126.58</v>
       </c>
       <c r="K25" t="n">
-        <v>120.9</v>
+        <v>134.58</v>
       </c>
       <c r="L25" t="n">
-        <v>165.97</v>
+        <v>184.76</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-193.03</v>
+        <v>-240.5</v>
       </c>
       <c r="K26" t="n">
-        <v>25.7</v>
+        <v>32.02</v>
       </c>
       <c r="L26" t="n">
-        <v>194.73</v>
+        <v>242.62</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-145.68</v>
+        <v>-170.85</v>
       </c>
       <c r="K27" t="n">
-        <v>264.78</v>
+        <v>310.54</v>
       </c>
       <c r="L27" t="n">
-        <v>302.21</v>
+        <v>354.44</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-43.51</v>
+        <v>-51.65</v>
       </c>
       <c r="K28" t="n">
-        <v>343.1</v>
+        <v>407.26</v>
       </c>
       <c r="L28" t="n">
-        <v>345.85</v>
+        <v>410.52</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>1.05</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>109.18</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>109.18</v>
+        <v>84.25</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>118.75</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>61.53</v>
+        <v>48.69</v>
       </c>
       <c r="L30" t="n">
-        <v>133.74</v>
+        <v>105.83</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>92.02</v>
+        <v>71.44</v>
       </c>
       <c r="K31" t="n">
-        <v>-52.04</v>
+        <v>-40.4</v>
       </c>
       <c r="L31" t="n">
-        <v>105.71</v>
+        <v>82.06999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-91.40000000000001</v>
+        <v>-75.2</v>
       </c>
       <c r="K32" t="n">
-        <v>-88.27</v>
+        <v>-72.62</v>
       </c>
       <c r="L32" t="n">
-        <v>127.06</v>
+        <v>104.54</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-24.05</v>
+        <v>-21.4</v>
       </c>
       <c r="K33" t="n">
-        <v>72.03</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>75.94</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>22.01</v>
+        <v>19.09</v>
       </c>
       <c r="K34" t="n">
-        <v>-85.91</v>
+        <v>-74.53</v>
       </c>
       <c r="L34" t="n">
-        <v>88.68000000000001</v>
+        <v>76.94</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-201.12</v>
+        <v>-187.37</v>
       </c>
       <c r="K35" t="n">
-        <v>-171.79</v>
+        <v>-160.05</v>
       </c>
       <c r="L35" t="n">
-        <v>264.5</v>
+        <v>246.42</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-133.67</v>
+        <v>-129.54</v>
       </c>
       <c r="K36" t="n">
-        <v>115.81</v>
+        <v>112.23</v>
       </c>
       <c r="L36" t="n">
-        <v>176.85</v>
+        <v>171.4</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-20.14</v>
+        <v>-20.08</v>
       </c>
       <c r="K37" t="n">
-        <v>-132.14</v>
+        <v>-131.71</v>
       </c>
       <c r="L37" t="n">
-        <v>133.66</v>
+        <v>133.23</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-195.55</v>
+        <v>-204.04</v>
       </c>
       <c r="K38" t="n">
-        <v>262.05</v>
+        <v>273.43</v>
       </c>
       <c r="L38" t="n">
-        <v>326.97</v>
+        <v>341.17</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-249.25</v>
+        <v>-271</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.73</v>
+        <v>-6.23</v>
       </c>
       <c r="L39" t="n">
-        <v>249.31</v>
+        <v>271.07</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-156.34</v>
+        <v>-182.56</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.93</v>
+        <v>-1.08</v>
       </c>
       <c r="L40" t="n">
-        <v>156.34</v>
+        <v>182.56</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-467.68</v>
+        <v>-524.65</v>
       </c>
       <c r="K41" t="n">
-        <v>339.51</v>
+        <v>380.87</v>
       </c>
       <c r="L41" t="n">
-        <v>577.9299999999999</v>
+        <v>648.3200000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-131.18</v>
+        <v>-159.18</v>
       </c>
       <c r="K42" t="n">
-        <v>-168.1</v>
+        <v>-203.99</v>
       </c>
       <c r="L42" t="n">
-        <v>213.23</v>
+        <v>258.75</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-93.37</v>
+        <v>-107.45</v>
       </c>
       <c r="K43" t="n">
-        <v>416.65</v>
+        <v>479.45</v>
       </c>
       <c r="L43" t="n">
-        <v>426.98</v>
+        <v>491.34</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-41.73</v>
+        <v>-36.48</v>
       </c>
       <c r="K44" t="n">
-        <v>-36.27</v>
+        <v>-31.71</v>
       </c>
       <c r="L44" t="n">
-        <v>55.29</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-108.89</v>
+        <v>-77.34999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-180.63</v>
+        <v>-128.31</v>
       </c>
       <c r="L45" t="n">
-        <v>210.91</v>
+        <v>149.83</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>65.40000000000001</v>
+        <v>50.86</v>
       </c>
       <c r="K46" t="n">
-        <v>-56.76</v>
+        <v>-44.14</v>
       </c>
       <c r="L46" t="n">
-        <v>86.59</v>
+        <v>67.34</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-76.95999999999999</v>
+        <v>-69.16</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.1</v>
+        <v>-6.38</v>
       </c>
       <c r="L47" t="n">
-        <v>77.29000000000001</v>
+        <v>69.45999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-25.16</v>
+        <v>-21.92</v>
       </c>
       <c r="K48" t="n">
-        <v>87.16</v>
+        <v>75.95</v>
       </c>
       <c r="L48" t="n">
-        <v>90.72</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>50.36</v>
+        <v>41.98</v>
       </c>
       <c r="K49" t="n">
-        <v>15.23</v>
+        <v>12.7</v>
       </c>
       <c r="L49" t="n">
-        <v>52.62</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-33.2</v>
+        <v>-30.74</v>
       </c>
       <c r="K50" t="n">
-        <v>279.19</v>
+        <v>258.54</v>
       </c>
       <c r="L50" t="n">
-        <v>281.16</v>
+        <v>260.37</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>200.81</v>
+        <v>191.83</v>
       </c>
       <c r="K51" t="n">
-        <v>-61.95</v>
+        <v>-59.18</v>
       </c>
       <c r="L51" t="n">
-        <v>210.15</v>
+        <v>200.75</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>125.33</v>
+        <v>127.41</v>
       </c>
       <c r="K52" t="n">
-        <v>58</v>
+        <v>58.96</v>
       </c>
       <c r="L52" t="n">
-        <v>138.1</v>
+        <v>140.39</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-321.48</v>
+        <v>-328.69</v>
       </c>
       <c r="K53" t="n">
-        <v>-262.37</v>
+        <v>-268.26</v>
       </c>
       <c r="L53" t="n">
-        <v>414.95</v>
+        <v>424.27</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-163.59</v>
+        <v>-174.02</v>
       </c>
       <c r="K54" t="n">
-        <v>-201.75</v>
+        <v>-214.61</v>
       </c>
       <c r="L54" t="n">
-        <v>259.74</v>
+        <v>276.3</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-172.06</v>
+        <v>-191.5</v>
       </c>
       <c r="K55" t="n">
-        <v>126.81</v>
+        <v>141.14</v>
       </c>
       <c r="L55" t="n">
-        <v>213.74</v>
+        <v>237.89</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-211.15</v>
+        <v>-219.43</v>
       </c>
       <c r="K56" t="n">
-        <v>-226.98</v>
+        <v>-235.88</v>
       </c>
       <c r="L56" t="n">
-        <v>310.01</v>
+        <v>322.16</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>25.42</v>
+        <v>29.97</v>
       </c>
       <c r="K57" t="n">
-        <v>297.09</v>
+        <v>350.31</v>
       </c>
       <c r="L57" t="n">
-        <v>298.17</v>
+        <v>351.59</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>379.58</v>
+        <v>448.32</v>
       </c>
       <c r="K58" t="n">
-        <v>245.33</v>
+        <v>289.77</v>
       </c>
       <c r="L58" t="n">
-        <v>451.96</v>
+        <v>533.8099999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-121.67</v>
+        <v>-92.04000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>30.65</v>
+        <v>23.19</v>
       </c>
       <c r="L59" t="n">
-        <v>125.48</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-121.61</v>
+        <v>-90.48</v>
       </c>
       <c r="K60" t="n">
-        <v>34.24</v>
+        <v>25.48</v>
       </c>
       <c r="L60" t="n">
-        <v>126.34</v>
+        <v>93.98999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-68.01000000000001</v>
+        <v>-53.82</v>
       </c>
       <c r="K61" t="n">
-        <v>46.16</v>
+        <v>36.52</v>
       </c>
       <c r="L61" t="n">
-        <v>82.2</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-76.37</v>
+        <v>-67.08</v>
       </c>
       <c r="K62" t="n">
-        <v>29.97</v>
+        <v>26.32</v>
       </c>
       <c r="L62" t="n">
-        <v>82.04000000000001</v>
+        <v>72.05</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>39.67</v>
+        <v>31.8</v>
       </c>
       <c r="K63" t="n">
-        <v>170.62</v>
+        <v>136.78</v>
       </c>
       <c r="L63" t="n">
-        <v>175.17</v>
+        <v>140.42</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-149.03</v>
+        <v>-119.69</v>
       </c>
       <c r="K64" t="n">
-        <v>-69.28</v>
+        <v>-55.64</v>
       </c>
       <c r="L64" t="n">
-        <v>164.35</v>
+        <v>131.99</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-138</v>
+        <v>-136.65</v>
       </c>
       <c r="K65" t="n">
-        <v>28.21</v>
+        <v>27.93</v>
       </c>
       <c r="L65" t="n">
-        <v>140.85</v>
+        <v>139.48</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>60.38</v>
+        <v>57.17</v>
       </c>
       <c r="K66" t="n">
-        <v>225.39</v>
+        <v>213.4</v>
       </c>
       <c r="L66" t="n">
-        <v>233.34</v>
+        <v>220.92</v>
       </c>
     </row>
     <row r="67">
@@ -2869,10 +2869,10 @@
         <v>-0.1</v>
       </c>
       <c r="K67" t="n">
-        <v>-152.62</v>
+        <v>-149.19</v>
       </c>
       <c r="L67" t="n">
-        <v>152.62</v>
+        <v>149.19</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-242.3</v>
+        <v>-268.09</v>
       </c>
       <c r="K68" t="n">
-        <v>-100.91</v>
+        <v>-111.65</v>
       </c>
       <c r="L68" t="n">
-        <v>262.47</v>
+        <v>290.42</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>4.14</v>
+        <v>4.68</v>
       </c>
       <c r="K69" t="n">
-        <v>-162.4</v>
+        <v>-183.61</v>
       </c>
       <c r="L69" t="n">
-        <v>162.46</v>
+        <v>183.67</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>242.71</v>
+        <v>263.59</v>
       </c>
       <c r="K70" t="n">
-        <v>-112.06</v>
+        <v>-121.7</v>
       </c>
       <c r="L70" t="n">
-        <v>267.34</v>
+        <v>290.33</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-364.09</v>
+        <v>-440.84</v>
       </c>
       <c r="K71" t="n">
-        <v>-59.74</v>
+        <v>-72.33</v>
       </c>
       <c r="L71" t="n">
-        <v>368.96</v>
+        <v>446.74</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-271.6</v>
+        <v>-327.24</v>
       </c>
       <c r="K72" t="n">
-        <v>-360.56</v>
+        <v>-434.43</v>
       </c>
       <c r="L72" t="n">
-        <v>451.41</v>
+        <v>543.89</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-217.17</v>
+        <v>-257.53</v>
       </c>
       <c r="K73" t="n">
-        <v>299.8</v>
+        <v>355.51</v>
       </c>
       <c r="L73" t="n">
-        <v>370.19</v>
+        <v>438.99</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.34</v>
+        <v>-1</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.76</v>
+        <v>-5.79</v>
       </c>
       <c r="L74" t="n">
-        <v>7.88</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-115.9</v>
+        <v>-87.59</v>
       </c>
       <c r="K75" t="n">
-        <v>-45.66</v>
+        <v>-34.51</v>
       </c>
       <c r="L75" t="n">
-        <v>124.57</v>
+        <v>94.14</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>62.23</v>
+        <v>46.59</v>
       </c>
       <c r="K76" t="n">
-        <v>-103.18</v>
+        <v>-77.26000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>120.49</v>
+        <v>90.22</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-24.6</v>
+        <v>-20.18</v>
       </c>
       <c r="K77" t="n">
-        <v>52.01</v>
+        <v>42.67</v>
       </c>
       <c r="L77" t="n">
-        <v>57.53</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>27.46</v>
+        <v>22.98</v>
       </c>
       <c r="K78" t="n">
-        <v>109.71</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>113.1</v>
+        <v>94.63</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-101.43</v>
+        <v>-81.2</v>
       </c>
       <c r="K79" t="n">
-        <v>-115.12</v>
+        <v>-92.15000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>153.43</v>
+        <v>122.82</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>108.77</v>
+        <v>104.91</v>
       </c>
       <c r="K80" t="n">
-        <v>80.84</v>
+        <v>77.97</v>
       </c>
       <c r="L80" t="n">
-        <v>135.52</v>
+        <v>130.71</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>56.66</v>
+        <v>58.46</v>
       </c>
       <c r="K81" t="n">
-        <v>-105.51</v>
+        <v>-108.87</v>
       </c>
       <c r="L81" t="n">
-        <v>119.76</v>
+        <v>123.57</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>7.03</v>
+        <v>7.32</v>
       </c>
       <c r="K82" t="n">
-        <v>112.61</v>
+        <v>117.22</v>
       </c>
       <c r="L82" t="n">
-        <v>112.83</v>
+        <v>117.44</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>106.2</v>
+        <v>113.13</v>
       </c>
       <c r="K83" t="n">
-        <v>57.35</v>
+        <v>61.09</v>
       </c>
       <c r="L83" t="n">
-        <v>120.7</v>
+        <v>128.58</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>165.96</v>
+        <v>188.74</v>
       </c>
       <c r="K84" t="n">
-        <v>121.27</v>
+        <v>137.92</v>
       </c>
       <c r="L84" t="n">
-        <v>205.54</v>
+        <v>233.76</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-180.48</v>
+        <v>-196.27</v>
       </c>
       <c r="K85" t="n">
-        <v>-222.15</v>
+        <v>-241.59</v>
       </c>
       <c r="L85" t="n">
-        <v>286.22</v>
+        <v>311.27</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-122.69</v>
+        <v>-143.45</v>
       </c>
       <c r="K86" t="n">
-        <v>-384.81</v>
+        <v>-449.92</v>
       </c>
       <c r="L86" t="n">
-        <v>403.89</v>
+        <v>472.24</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-27.46</v>
+        <v>-32.46</v>
       </c>
       <c r="K87" t="n">
-        <v>363.92</v>
+        <v>430.14</v>
       </c>
       <c r="L87" t="n">
-        <v>364.95</v>
+        <v>431.37</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>195.38</v>
+        <v>258</v>
       </c>
       <c r="K88" t="n">
-        <v>106.18</v>
+        <v>140.21</v>
       </c>
       <c r="L88" t="n">
-        <v>222.37</v>
+        <v>293.63</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>48.55</v>
+        <v>45.63</v>
       </c>
       <c r="K14" t="n">
-        <v>91.48999999999999</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>103.57</v>
+        <v>97.34999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>68.95</v>
+        <v>69.02</v>
       </c>
       <c r="K15" t="n">
-        <v>10.11</v>
+        <v>10.12</v>
       </c>
       <c r="L15" t="n">
-        <v>69.69</v>
+        <v>69.76000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>10.19</v>
+        <v>10.29</v>
       </c>
       <c r="K16" t="n">
-        <v>64.95</v>
+        <v>65.58</v>
       </c>
       <c r="L16" t="n">
-        <v>65.73999999999999</v>
+        <v>66.38</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-58.4</v>
+        <v>-57.65</v>
       </c>
       <c r="K17" t="n">
-        <v>-64.48</v>
+        <v>-63.65</v>
       </c>
       <c r="L17" t="n">
-        <v>87</v>
+        <v>85.88</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>60.39</v>
+        <v>63.94</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.09</v>
+        <v>-22.33</v>
       </c>
       <c r="L18" t="n">
-        <v>63.96</v>
+        <v>67.73</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>70.67</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>39.58</v>
+        <v>39.51</v>
       </c>
       <c r="L19" t="n">
-        <v>81</v>
+        <v>80.84999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>54.06</v>
+        <v>53.5</v>
       </c>
       <c r="K20" t="n">
-        <v>133.82</v>
+        <v>132.45</v>
       </c>
       <c r="L20" t="n">
-        <v>144.33</v>
+        <v>142.85</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-64.55</v>
+        <v>-68.18000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-108.33</v>
+        <v>-114.42</v>
       </c>
       <c r="L21" t="n">
-        <v>126.1</v>
+        <v>133.19</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>62.94</v>
+        <v>63.34</v>
       </c>
       <c r="K22" t="n">
-        <v>-134.09</v>
+        <v>-134.94</v>
       </c>
       <c r="L22" t="n">
-        <v>148.13</v>
+        <v>149.07</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-32.87</v>
+        <v>-33.39</v>
       </c>
       <c r="K23" t="n">
-        <v>156.26</v>
+        <v>158.75</v>
       </c>
       <c r="L23" t="n">
-        <v>159.68</v>
+        <v>162.22</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-16.05</v>
+        <v>-17.79</v>
       </c>
       <c r="K24" t="n">
-        <v>-127.04</v>
+        <v>-140.83</v>
       </c>
       <c r="L24" t="n">
-        <v>128.05</v>
+        <v>141.95</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-126.58</v>
+        <v>-132.1</v>
       </c>
       <c r="K25" t="n">
-        <v>134.58</v>
+        <v>140.46</v>
       </c>
       <c r="L25" t="n">
-        <v>184.76</v>
+        <v>192.82</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-240.5</v>
+        <v>-261.96</v>
       </c>
       <c r="K26" t="n">
-        <v>32.02</v>
+        <v>34.88</v>
       </c>
       <c r="L26" t="n">
-        <v>242.62</v>
+        <v>264.27</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-170.85</v>
+        <v>-173.62</v>
       </c>
       <c r="K27" t="n">
-        <v>310.54</v>
+        <v>315.58</v>
       </c>
       <c r="L27" t="n">
-        <v>354.44</v>
+        <v>360.19</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-51.65</v>
+        <v>-52.11</v>
       </c>
       <c r="K28" t="n">
-        <v>407.26</v>
+        <v>410.94</v>
       </c>
       <c r="L28" t="n">
-        <v>410.52</v>
+        <v>414.23</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="K29" t="n">
-        <v>84.23999999999999</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>84.25</v>
+        <v>81.48999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>93.95999999999999</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>48.69</v>
+        <v>45.99</v>
       </c>
       <c r="L30" t="n">
-        <v>105.83</v>
+        <v>99.97</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>71.44</v>
+        <v>68.8</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.4</v>
+        <v>-38.91</v>
       </c>
       <c r="L31" t="n">
-        <v>82.06999999999999</v>
+        <v>79.04000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-75.2</v>
+        <v>-72.54000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-72.62</v>
+        <v>-70.06</v>
       </c>
       <c r="L32" t="n">
-        <v>104.54</v>
+        <v>100.85</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-21.4</v>
+        <v>-22.53</v>
       </c>
       <c r="K33" t="n">
-        <v>64.09999999999999</v>
+        <v>67.48</v>
       </c>
       <c r="L33" t="n">
-        <v>67.58</v>
+        <v>71.15000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>19.09</v>
+        <v>19.52</v>
       </c>
       <c r="K34" t="n">
-        <v>-74.53</v>
+        <v>-76.18000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>76.94</v>
+        <v>78.64</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-187.37</v>
+        <v>-178.08</v>
       </c>
       <c r="K35" t="n">
-        <v>-160.05</v>
+        <v>-152.11</v>
       </c>
       <c r="L35" t="n">
-        <v>246.42</v>
+        <v>234.2</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-129.54</v>
+        <v>-128.86</v>
       </c>
       <c r="K36" t="n">
-        <v>112.23</v>
+        <v>111.64</v>
       </c>
       <c r="L36" t="n">
-        <v>171.4</v>
+        <v>170.49</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-20.08</v>
+        <v>-20.68</v>
       </c>
       <c r="K37" t="n">
-        <v>-131.71</v>
+        <v>-135.68</v>
       </c>
       <c r="L37" t="n">
-        <v>133.23</v>
+        <v>137.25</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-204.04</v>
+        <v>-196.33</v>
       </c>
       <c r="K38" t="n">
-        <v>273.43</v>
+        <v>263.09</v>
       </c>
       <c r="L38" t="n">
-        <v>341.17</v>
+        <v>328.27</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-271</v>
+        <v>-271.95</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.23</v>
+        <v>-6.25</v>
       </c>
       <c r="L39" t="n">
-        <v>271.07</v>
+        <v>272.03</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-182.56</v>
+        <v>-197.76</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.08</v>
+        <v>-1.17</v>
       </c>
       <c r="L40" t="n">
-        <v>182.56</v>
+        <v>197.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-524.65</v>
+        <v>-496.89</v>
       </c>
       <c r="K41" t="n">
-        <v>380.87</v>
+        <v>360.71</v>
       </c>
       <c r="L41" t="n">
-        <v>648.3200000000001</v>
+        <v>614.01</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-159.18</v>
+        <v>-168.23</v>
       </c>
       <c r="K42" t="n">
-        <v>-203.99</v>
+        <v>-215.59</v>
       </c>
       <c r="L42" t="n">
-        <v>258.75</v>
+        <v>273.46</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-107.45</v>
+        <v>-105.01</v>
       </c>
       <c r="K43" t="n">
-        <v>479.45</v>
+        <v>468.57</v>
       </c>
       <c r="L43" t="n">
-        <v>491.34</v>
+        <v>480.2</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-36.48</v>
+        <v>-38.9</v>
       </c>
       <c r="K44" t="n">
-        <v>-31.71</v>
+        <v>-33.82</v>
       </c>
       <c r="L44" t="n">
-        <v>48.34</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-77.34999999999999</v>
+        <v>-70.52</v>
       </c>
       <c r="K45" t="n">
-        <v>-128.31</v>
+        <v>-116.98</v>
       </c>
       <c r="L45" t="n">
-        <v>149.83</v>
+        <v>136.59</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>50.86</v>
+        <v>51</v>
       </c>
       <c r="K46" t="n">
-        <v>-44.14</v>
+        <v>-44.26</v>
       </c>
       <c r="L46" t="n">
-        <v>67.34</v>
+        <v>67.53</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-69.16</v>
+        <v>-73.28</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.38</v>
+        <v>-6.76</v>
       </c>
       <c r="L47" t="n">
-        <v>69.45999999999999</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-21.92</v>
+        <v>-22.81</v>
       </c>
       <c r="K48" t="n">
-        <v>75.95</v>
+        <v>79.02</v>
       </c>
       <c r="L48" t="n">
-        <v>79.05</v>
+        <v>82.25</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>41.98</v>
+        <v>45.84</v>
       </c>
       <c r="K49" t="n">
-        <v>12.7</v>
+        <v>13.86</v>
       </c>
       <c r="L49" t="n">
-        <v>43.86</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-30.74</v>
+        <v>-29.03</v>
       </c>
       <c r="K50" t="n">
-        <v>258.54</v>
+        <v>244.11</v>
       </c>
       <c r="L50" t="n">
-        <v>260.37</v>
+        <v>245.82</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>191.83</v>
+        <v>188.45</v>
       </c>
       <c r="K51" t="n">
-        <v>-59.18</v>
+        <v>-58.14</v>
       </c>
       <c r="L51" t="n">
-        <v>200.75</v>
+        <v>197.21</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>127.41</v>
+        <v>134.26</v>
       </c>
       <c r="K52" t="n">
-        <v>58.96</v>
+        <v>62.13</v>
       </c>
       <c r="L52" t="n">
-        <v>140.39</v>
+        <v>147.94</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-328.69</v>
+        <v>-308.2</v>
       </c>
       <c r="K53" t="n">
-        <v>-268.26</v>
+        <v>-251.54</v>
       </c>
       <c r="L53" t="n">
-        <v>424.27</v>
+        <v>397.82</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-174.02</v>
+        <v>-171.51</v>
       </c>
       <c r="K54" t="n">
-        <v>-214.61</v>
+        <v>-211.52</v>
       </c>
       <c r="L54" t="n">
-        <v>276.3</v>
+        <v>272.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-191.5</v>
+        <v>-196.9</v>
       </c>
       <c r="K55" t="n">
-        <v>141.14</v>
+        <v>145.12</v>
       </c>
       <c r="L55" t="n">
-        <v>237.89</v>
+        <v>244.6</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-219.43</v>
+        <v>-232.38</v>
       </c>
       <c r="K56" t="n">
-        <v>-235.88</v>
+        <v>-249.8</v>
       </c>
       <c r="L56" t="n">
-        <v>322.16</v>
+        <v>341.17</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>29.97</v>
+        <v>30.61</v>
       </c>
       <c r="K57" t="n">
-        <v>350.31</v>
+        <v>357.78</v>
       </c>
       <c r="L57" t="n">
-        <v>351.59</v>
+        <v>359.09</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>448.32</v>
+        <v>443.01</v>
       </c>
       <c r="K58" t="n">
-        <v>289.77</v>
+        <v>286.33</v>
       </c>
       <c r="L58" t="n">
-        <v>533.8099999999999</v>
+        <v>527.49</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-92.04000000000001</v>
+        <v>-86.44</v>
       </c>
       <c r="K59" t="n">
-        <v>23.19</v>
+        <v>21.78</v>
       </c>
       <c r="L59" t="n">
-        <v>94.92</v>
+        <v>89.14</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-90.48</v>
+        <v>-85.8</v>
       </c>
       <c r="K60" t="n">
-        <v>25.48</v>
+        <v>24.16</v>
       </c>
       <c r="L60" t="n">
-        <v>93.98999999999999</v>
+        <v>89.13</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-53.82</v>
+        <v>-54.22</v>
       </c>
       <c r="K61" t="n">
-        <v>36.52</v>
+        <v>36.8</v>
       </c>
       <c r="L61" t="n">
-        <v>65.04000000000001</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-67.08</v>
+        <v>-72.17</v>
       </c>
       <c r="K62" t="n">
-        <v>26.32</v>
+        <v>28.32</v>
       </c>
       <c r="L62" t="n">
-        <v>72.05</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>31.8</v>
+        <v>30.05</v>
       </c>
       <c r="K63" t="n">
-        <v>136.78</v>
+        <v>129.28</v>
       </c>
       <c r="L63" t="n">
-        <v>140.42</v>
+        <v>132.73</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-119.69</v>
+        <v>-114.2</v>
       </c>
       <c r="K64" t="n">
-        <v>-55.64</v>
+        <v>-53.09</v>
       </c>
       <c r="L64" t="n">
-        <v>131.99</v>
+        <v>125.93</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-136.65</v>
+        <v>-139.69</v>
       </c>
       <c r="K65" t="n">
-        <v>27.93</v>
+        <v>28.55</v>
       </c>
       <c r="L65" t="n">
-        <v>139.48</v>
+        <v>142.57</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>57.17</v>
+        <v>55.68</v>
       </c>
       <c r="K66" t="n">
-        <v>213.4</v>
+        <v>207.86</v>
       </c>
       <c r="L66" t="n">
-        <v>220.92</v>
+        <v>215.19</v>
       </c>
     </row>
     <row r="67">
@@ -2869,10 +2869,10 @@
         <v>-0.1</v>
       </c>
       <c r="K67" t="n">
-        <v>-149.19</v>
+        <v>-149.52</v>
       </c>
       <c r="L67" t="n">
-        <v>149.19</v>
+        <v>149.52</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-268.09</v>
+        <v>-273.16</v>
       </c>
       <c r="K68" t="n">
-        <v>-111.65</v>
+        <v>-113.76</v>
       </c>
       <c r="L68" t="n">
-        <v>290.42</v>
+        <v>295.9</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>4.68</v>
+        <v>4.93</v>
       </c>
       <c r="K69" t="n">
-        <v>-183.61</v>
+        <v>-193.63</v>
       </c>
       <c r="L69" t="n">
-        <v>183.67</v>
+        <v>193.69</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>263.59</v>
+        <v>263.26</v>
       </c>
       <c r="K70" t="n">
-        <v>-121.7</v>
+        <v>-121.55</v>
       </c>
       <c r="L70" t="n">
-        <v>290.33</v>
+        <v>289.96</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-440.84</v>
+        <v>-447.2</v>
       </c>
       <c r="K71" t="n">
-        <v>-72.33</v>
+        <v>-73.37</v>
       </c>
       <c r="L71" t="n">
-        <v>446.74</v>
+        <v>453.18</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-327.24</v>
+        <v>-328.53</v>
       </c>
       <c r="K72" t="n">
-        <v>-434.43</v>
+        <v>-436.15</v>
       </c>
       <c r="L72" t="n">
-        <v>543.89</v>
+        <v>546.04</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-257.53</v>
+        <v>-257.98</v>
       </c>
       <c r="K73" t="n">
-        <v>355.51</v>
+        <v>356.14</v>
       </c>
       <c r="L73" t="n">
-        <v>438.99</v>
+        <v>439.76</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-1</v>
+        <v>-1.02</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.79</v>
+        <v>-5.88</v>
       </c>
       <c r="L74" t="n">
-        <v>5.88</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-87.59</v>
+        <v>-83.65000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-34.51</v>
+        <v>-32.96</v>
       </c>
       <c r="L75" t="n">
-        <v>94.14</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>46.59</v>
+        <v>44.32</v>
       </c>
       <c r="K76" t="n">
-        <v>-77.26000000000001</v>
+        <v>-73.48</v>
       </c>
       <c r="L76" t="n">
-        <v>90.22</v>
+        <v>85.81</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-20.18</v>
+        <v>-21.74</v>
       </c>
       <c r="K77" t="n">
-        <v>42.67</v>
+        <v>45.98</v>
       </c>
       <c r="L77" t="n">
-        <v>47.2</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>22.98</v>
+        <v>23.08</v>
       </c>
       <c r="K78" t="n">
-        <v>91.79000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="L78" t="n">
-        <v>94.63</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-81.2</v>
+        <v>-78.23999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-92.15000000000001</v>
+        <v>-88.8</v>
       </c>
       <c r="L79" t="n">
-        <v>122.82</v>
+        <v>118.35</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>104.91</v>
+        <v>111.92</v>
       </c>
       <c r="K80" t="n">
-        <v>77.97</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>130.71</v>
+        <v>139.44</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>58.46</v>
+        <v>62.3</v>
       </c>
       <c r="K81" t="n">
-        <v>-108.87</v>
+        <v>-116.01</v>
       </c>
       <c r="L81" t="n">
-        <v>123.57</v>
+        <v>131.68</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>7.32</v>
+        <v>7.89</v>
       </c>
       <c r="K82" t="n">
-        <v>117.22</v>
+        <v>126.47</v>
       </c>
       <c r="L82" t="n">
-        <v>117.44</v>
+        <v>126.72</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>113.13</v>
+        <v>125.24</v>
       </c>
       <c r="K83" t="n">
-        <v>61.09</v>
+        <v>67.63</v>
       </c>
       <c r="L83" t="n">
-        <v>128.58</v>
+        <v>142.33</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>188.74</v>
+        <v>198.59</v>
       </c>
       <c r="K84" t="n">
-        <v>137.92</v>
+        <v>145.11</v>
       </c>
       <c r="L84" t="n">
-        <v>233.76</v>
+        <v>245.96</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-196.27</v>
+        <v>-196.12</v>
       </c>
       <c r="K85" t="n">
-        <v>-241.59</v>
+        <v>-241.4</v>
       </c>
       <c r="L85" t="n">
-        <v>311.27</v>
+        <v>311.02</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-143.45</v>
+        <v>-142.46</v>
       </c>
       <c r="K86" t="n">
-        <v>-449.92</v>
+        <v>-446.82</v>
       </c>
       <c r="L86" t="n">
-        <v>472.24</v>
+        <v>468.99</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-32.46</v>
+        <v>-34.45</v>
       </c>
       <c r="K87" t="n">
-        <v>430.14</v>
+        <v>456.46</v>
       </c>
       <c r="L87" t="n">
-        <v>431.37</v>
+        <v>457.76</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>258</v>
+        <v>287.93</v>
       </c>
       <c r="K88" t="n">
-        <v>140.21</v>
+        <v>156.47</v>
       </c>
       <c r="L88" t="n">
-        <v>293.63</v>
+        <v>327.7</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>6.13</v>
+        <v>5.12</v>
       </c>
       <c r="F14" t="n">
-        <v>14.98</v>
+        <v>14.78</v>
       </c>
       <c r="G14" t="n">
-        <v>287.1</v>
+        <v>261.4</v>
       </c>
       <c r="H14" t="n">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>45.63</v>
+        <v>81.23</v>
       </c>
       <c r="K14" t="n">
-        <v>85.98999999999999</v>
+        <v>-20.62</v>
       </c>
       <c r="L14" t="n">
-        <v>97.34999999999999</v>
+        <v>83.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:07:16</t>
+          <t>08:07:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.69</v>
+        <v>5.76</v>
       </c>
       <c r="F15" t="n">
-        <v>14.42</v>
+        <v>11.6</v>
       </c>
       <c r="G15" t="n">
-        <v>282.3</v>
+        <v>273.3</v>
       </c>
       <c r="H15" t="n">
-        <v>90.5</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>69.02</v>
+        <v>-38.25</v>
       </c>
       <c r="K15" t="n">
-        <v>10.12</v>
+        <v>77.34</v>
       </c>
       <c r="L15" t="n">
-        <v>69.76000000000001</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:08:38</t>
+          <t>08:09:16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.36</v>
+        <v>5.9</v>
       </c>
       <c r="F16" t="n">
-        <v>14.54</v>
+        <v>14.09</v>
       </c>
       <c r="G16" t="n">
-        <v>280.4</v>
+        <v>294.6</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>10.29</v>
+        <v>-17.41</v>
       </c>
       <c r="K16" t="n">
-        <v>65.58</v>
+        <v>82.64</v>
       </c>
       <c r="L16" t="n">
-        <v>66.38</v>
+        <v>84.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:13:51</t>
+          <t>08:14:16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.67</v>
+        <v>5.49</v>
       </c>
       <c r="F17" t="n">
-        <v>15.03</v>
+        <v>14.05</v>
       </c>
       <c r="G17" t="n">
-        <v>282</v>
+        <v>274.2</v>
       </c>
       <c r="H17" t="n">
-        <v>91</v>
+        <v>96.7</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-57.65</v>
+        <v>85.89</v>
       </c>
       <c r="K17" t="n">
-        <v>-63.65</v>
+        <v>-80.56999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>85.88</v>
+        <v>117.77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:15:26</t>
+          <t>08:16:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.47</v>
+        <v>5.08</v>
       </c>
       <c r="F18" t="n">
-        <v>14.86</v>
+        <v>12.42</v>
       </c>
       <c r="G18" t="n">
-        <v>265.8</v>
+        <v>287.6</v>
       </c>
       <c r="H18" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>63.94</v>
+        <v>67.34</v>
       </c>
       <c r="K18" t="n">
-        <v>-22.33</v>
+        <v>-51.53</v>
       </c>
       <c r="L18" t="n">
-        <v>67.73</v>
+        <v>84.79000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:17:09</t>
+          <t>08:18:09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.02</v>
+        <v>5.67</v>
       </c>
       <c r="F19" t="n">
-        <v>14.15</v>
+        <v>12.33</v>
       </c>
       <c r="G19" t="n">
-        <v>276.1</v>
+        <v>285.7</v>
       </c>
       <c r="H19" t="n">
-        <v>96.7</v>
+        <v>93.7</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>70.54000000000001</v>
+        <v>-102.77</v>
       </c>
       <c r="K19" t="n">
-        <v>39.51</v>
+        <v>62.78</v>
       </c>
       <c r="L19" t="n">
-        <v>80.84999999999999</v>
+        <v>120.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:22:16</t>
+          <t>08:22:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.16</v>
+        <v>5.99</v>
       </c>
       <c r="F20" t="n">
-        <v>14.27</v>
+        <v>13.49</v>
       </c>
       <c r="G20" t="n">
-        <v>290.3</v>
+        <v>277.7</v>
       </c>
       <c r="H20" t="n">
-        <v>92.8</v>
+        <v>92.5</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>53.5</v>
+        <v>-171.94</v>
       </c>
       <c r="K20" t="n">
-        <v>132.45</v>
+        <v>134.83</v>
       </c>
       <c r="L20" t="n">
-        <v>142.85</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:24:17</t>
+          <t>08:24:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.98</v>
+        <v>5.78</v>
       </c>
       <c r="F21" t="n">
-        <v>14.45</v>
+        <v>15.58</v>
       </c>
       <c r="G21" t="n">
-        <v>284.1</v>
+        <v>288.1</v>
       </c>
       <c r="H21" t="n">
-        <v>97.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-68.18000000000001</v>
+        <v>-95.33</v>
       </c>
       <c r="K21" t="n">
-        <v>-114.42</v>
+        <v>197.37</v>
       </c>
       <c r="L21" t="n">
-        <v>133.19</v>
+        <v>219.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:25:59</t>
+          <t>08:26:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>6.02</v>
+        <v>5.43</v>
       </c>
       <c r="F22" t="n">
-        <v>14.27</v>
+        <v>14.85</v>
       </c>
       <c r="G22" t="n">
-        <v>274.2</v>
+        <v>278.6</v>
       </c>
       <c r="H22" t="n">
-        <v>93.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>63.34</v>
+        <v>-172.03</v>
       </c>
       <c r="K22" t="n">
-        <v>-134.94</v>
+        <v>-102.33</v>
       </c>
       <c r="L22" t="n">
-        <v>149.07</v>
+        <v>200.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:31:09</t>
+          <t>08:30:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.67</v>
+        <v>5.83</v>
       </c>
       <c r="F23" t="n">
-        <v>14.63</v>
+        <v>11.39</v>
       </c>
       <c r="G23" t="n">
-        <v>293.5</v>
+        <v>283.1</v>
       </c>
       <c r="H23" t="n">
-        <v>95.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-33.39</v>
+        <v>-60.7</v>
       </c>
       <c r="K23" t="n">
-        <v>158.75</v>
+        <v>305.43</v>
       </c>
       <c r="L23" t="n">
-        <v>162.22</v>
+        <v>311.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:33:30</t>
+          <t>08:32:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5.31</v>
+        <v>5.53</v>
       </c>
       <c r="F24" t="n">
-        <v>14.51</v>
+        <v>12.67</v>
       </c>
       <c r="G24" t="n">
-        <v>276.7</v>
+        <v>275.7</v>
       </c>
       <c r="H24" t="n">
-        <v>91.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-17.79</v>
+        <v>-121.74</v>
       </c>
       <c r="K24" t="n">
-        <v>-140.83</v>
+        <v>-251.97</v>
       </c>
       <c r="L24" t="n">
-        <v>141.95</v>
+        <v>279.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:34:49</t>
+          <t>08:35:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.68</v>
+        <v>5.65</v>
       </c>
       <c r="F25" t="n">
-        <v>15.36</v>
+        <v>14.17</v>
       </c>
       <c r="G25" t="n">
-        <v>295.1</v>
+        <v>296.8</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-132.1</v>
+        <v>296.86</v>
       </c>
       <c r="K25" t="n">
-        <v>140.46</v>
+        <v>42.75</v>
       </c>
       <c r="L25" t="n">
-        <v>192.82</v>
+        <v>299.92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:38:56</t>
+          <t>08:39:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="F26" t="n">
-        <v>14.01</v>
+        <v>13.04</v>
       </c>
       <c r="G26" t="n">
-        <v>281.3</v>
+        <v>289.8</v>
       </c>
       <c r="H26" t="n">
-        <v>98.8</v>
+        <v>88.5</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-261.96</v>
+        <v>-480.69</v>
       </c>
       <c r="K26" t="n">
-        <v>34.88</v>
+        <v>-97.19</v>
       </c>
       <c r="L26" t="n">
-        <v>264.27</v>
+        <v>490.41</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:40:49</t>
+          <t>08:41:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.64</v>
+        <v>5.54</v>
       </c>
       <c r="F27" t="n">
-        <v>15.1</v>
+        <v>13.68</v>
       </c>
       <c r="G27" t="n">
-        <v>276.2</v>
+        <v>282</v>
       </c>
       <c r="H27" t="n">
-        <v>94.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="I27" t="n">
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-173.62</v>
+        <v>325.27</v>
       </c>
       <c r="K27" t="n">
-        <v>315.58</v>
+        <v>-179.87</v>
       </c>
       <c r="L27" t="n">
-        <v>360.19</v>
+        <v>371.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:43:22</t>
+          <t>08:43:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>6.27</v>
+        <v>5.49</v>
       </c>
       <c r="F28" t="n">
-        <v>14.71</v>
+        <v>15.54</v>
       </c>
       <c r="G28" t="n">
-        <v>287.1</v>
+        <v>270.1</v>
       </c>
       <c r="H28" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>-52.11</v>
+        <v>-110.36</v>
       </c>
       <c r="K28" t="n">
-        <v>410.94</v>
+        <v>-42.93</v>
       </c>
       <c r="L28" t="n">
-        <v>414.23</v>
+        <v>118.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:53:01</t>
+          <t>08:55:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>6.21</v>
+        <v>5.78</v>
       </c>
       <c r="F29" t="n">
-        <v>13.95</v>
+        <v>15.99</v>
       </c>
       <c r="G29" t="n">
-        <v>280</v>
+        <v>301.4</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>0.78</v>
+        <v>-113.47</v>
       </c>
       <c r="K29" t="n">
-        <v>81.48999999999999</v>
+        <v>-15.3</v>
       </c>
       <c r="L29" t="n">
-        <v>81.48999999999999</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:54:33</t>
+          <t>08:56:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.5</v>
+        <v>5.79</v>
       </c>
       <c r="F30" t="n">
-        <v>14.63</v>
+        <v>13.7</v>
       </c>
       <c r="G30" t="n">
-        <v>291.9</v>
+        <v>271.4</v>
       </c>
       <c r="H30" t="n">
-        <v>89.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>88.76000000000001</v>
+        <v>-1.38</v>
       </c>
       <c r="K30" t="n">
-        <v>45.99</v>
+        <v>-62.38</v>
       </c>
       <c r="L30" t="n">
-        <v>99.97</v>
+        <v>62.39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:56:31</t>
+          <t>08:58:29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.9</v>
+        <v>6.77</v>
       </c>
       <c r="F31" t="n">
-        <v>15.13</v>
+        <v>15.38</v>
       </c>
       <c r="G31" t="n">
-        <v>268.4</v>
+        <v>299</v>
       </c>
       <c r="H31" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>68.8</v>
+        <v>-118.98</v>
       </c>
       <c r="K31" t="n">
-        <v>-38.91</v>
+        <v>85.03</v>
       </c>
       <c r="L31" t="n">
-        <v>79.04000000000001</v>
+        <v>146.24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09:00:12</t>
+          <t>09:02:42</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.02</v>
+        <v>5.51</v>
       </c>
       <c r="F32" t="n">
-        <v>14.07</v>
+        <v>12.75</v>
       </c>
       <c r="G32" t="n">
-        <v>288.2</v>
+        <v>278.1</v>
       </c>
       <c r="H32" t="n">
-        <v>94</v>
+        <v>97.5</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-72.54000000000001</v>
+        <v>43.04</v>
       </c>
       <c r="K32" t="n">
-        <v>-70.06</v>
+        <v>-115.11</v>
       </c>
       <c r="L32" t="n">
-        <v>100.85</v>
+        <v>122.89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09:02:12</t>
+          <t>09:04:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6.1</v>
+        <v>6.93</v>
       </c>
       <c r="F33" t="n">
-        <v>14.19</v>
+        <v>15.81</v>
       </c>
       <c r="G33" t="n">
-        <v>275.8</v>
+        <v>280.6</v>
       </c>
       <c r="H33" t="n">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-22.53</v>
+        <v>-116.02</v>
       </c>
       <c r="K33" t="n">
-        <v>67.48</v>
+        <v>-105.99</v>
       </c>
       <c r="L33" t="n">
-        <v>71.15000000000001</v>
+        <v>157.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09:03:07</t>
+          <t>09:06:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1468,31 +1468,31 @@
         <v>5.98</v>
       </c>
       <c r="F34" t="n">
-        <v>14.66</v>
+        <v>15.72</v>
       </c>
       <c r="G34" t="n">
-        <v>277.3</v>
+        <v>289.8</v>
       </c>
       <c r="H34" t="n">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="I34" t="n">
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>19.52</v>
+        <v>-102.64</v>
       </c>
       <c r="K34" t="n">
-        <v>-76.18000000000001</v>
+        <v>24.17</v>
       </c>
       <c r="L34" t="n">
-        <v>78.64</v>
+        <v>105.45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09:07:12</t>
+          <t>09:09:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>6.15</v>
+        <v>5.84</v>
       </c>
       <c r="F35" t="n">
-        <v>15.02</v>
+        <v>13.69</v>
       </c>
       <c r="G35" t="n">
-        <v>274.1</v>
+        <v>279.7</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>90.8</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-178.08</v>
+        <v>-181.86</v>
       </c>
       <c r="K35" t="n">
-        <v>-152.11</v>
+        <v>135.98</v>
       </c>
       <c r="L35" t="n">
-        <v>234.2</v>
+        <v>227.07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09:09:24</t>
+          <t>09:11:33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.92</v>
+        <v>5.22</v>
       </c>
       <c r="F36" t="n">
-        <v>14.95</v>
+        <v>10.97</v>
       </c>
       <c r="G36" t="n">
-        <v>292.9</v>
+        <v>289</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-128.86</v>
+        <v>127.48</v>
       </c>
       <c r="K36" t="n">
-        <v>111.64</v>
+        <v>135.64</v>
       </c>
       <c r="L36" t="n">
-        <v>170.49</v>
+        <v>186.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09:10:33</t>
+          <t>09:13:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>6.54</v>
+        <v>5.51</v>
       </c>
       <c r="F37" t="n">
-        <v>14.56</v>
+        <v>15.17</v>
       </c>
       <c r="G37" t="n">
-        <v>286.3</v>
+        <v>293.6</v>
       </c>
       <c r="H37" t="n">
-        <v>87.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-20.68</v>
+        <v>23.23</v>
       </c>
       <c r="K37" t="n">
-        <v>-135.68</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>137.25</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:14:43</t>
+          <t>09:17:06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.11</v>
+        <v>6.62</v>
       </c>
       <c r="F38" t="n">
-        <v>14.65</v>
+        <v>16.79</v>
       </c>
       <c r="G38" t="n">
-        <v>295.9</v>
+        <v>290.7</v>
       </c>
       <c r="H38" t="n">
-        <v>99.2</v>
+        <v>95.7</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-196.33</v>
+        <v>-99.54000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>263.09</v>
+        <v>-272.67</v>
       </c>
       <c r="L38" t="n">
-        <v>328.27</v>
+        <v>290.27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:17:03</t>
+          <t>09:18:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6.66</v>
+        <v>5.4</v>
       </c>
       <c r="F39" t="n">
-        <v>14.35</v>
+        <v>16.13</v>
       </c>
       <c r="G39" t="n">
-        <v>293.6</v>
+        <v>289.7</v>
       </c>
       <c r="H39" t="n">
-        <v>98.8</v>
+        <v>95.7</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-271.95</v>
+        <v>-246.18</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.25</v>
+        <v>40.75</v>
       </c>
       <c r="L39" t="n">
-        <v>272.03</v>
+        <v>249.53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:18:40</t>
+          <t>09:20:49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>6.66</v>
+        <v>5.43</v>
       </c>
       <c r="F40" t="n">
-        <v>14.34</v>
+        <v>16.19</v>
       </c>
       <c r="G40" t="n">
-        <v>261.7</v>
+        <v>284.3</v>
       </c>
       <c r="H40" t="n">
-        <v>96</v>
+        <v>99.8</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-197.76</v>
+        <v>-247.49</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.17</v>
+        <v>47.73</v>
       </c>
       <c r="L40" t="n">
-        <v>197.76</v>
+        <v>252.05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:23:50</t>
+          <t>09:26:08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>6.09</v>
+        <v>5.89</v>
       </c>
       <c r="F41" t="n">
-        <v>15.34</v>
+        <v>15.47</v>
       </c>
       <c r="G41" t="n">
-        <v>277.6</v>
+        <v>282</v>
       </c>
       <c r="H41" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-496.89</v>
+        <v>509.79</v>
       </c>
       <c r="K41" t="n">
-        <v>360.71</v>
+        <v>-137.79</v>
       </c>
       <c r="L41" t="n">
-        <v>614.01</v>
+        <v>528.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09:24:54</t>
+          <t>09:27:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.59</v>
+        <v>4.95</v>
       </c>
       <c r="F42" t="n">
-        <v>14.58</v>
+        <v>11.44</v>
       </c>
       <c r="G42" t="n">
-        <v>287.8</v>
+        <v>277.8</v>
       </c>
       <c r="H42" t="n">
-        <v>92.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>-168.23</v>
+        <v>-137.29</v>
       </c>
       <c r="K42" t="n">
-        <v>-215.59</v>
+        <v>325.77</v>
       </c>
       <c r="L42" t="n">
-        <v>273.46</v>
+        <v>353.52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09:26:33</t>
+          <t>09:28:37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>6.11</v>
+        <v>5.91</v>
       </c>
       <c r="F43" t="n">
-        <v>13.87</v>
+        <v>15.58</v>
       </c>
       <c r="G43" t="n">
-        <v>306.2</v>
+        <v>278.4</v>
       </c>
       <c r="H43" t="n">
-        <v>93.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>-105.01</v>
+        <v>-648.41</v>
       </c>
       <c r="K43" t="n">
-        <v>468.57</v>
+        <v>87.59</v>
       </c>
       <c r="L43" t="n">
-        <v>480.2</v>
+        <v>654.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:37:21</t>
+          <t>09:37:58</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.55</v>
+        <v>5.96</v>
       </c>
       <c r="F44" t="n">
-        <v>14.29</v>
+        <v>13.76</v>
       </c>
       <c r="G44" t="n">
-        <v>281.8</v>
+        <v>288.7</v>
       </c>
       <c r="H44" t="n">
-        <v>98.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-38.9</v>
+        <v>-84.06999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>-33.82</v>
+        <v>0.24</v>
       </c>
       <c r="L44" t="n">
-        <v>51.54</v>
+        <v>84.06999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:39:00</t>
+          <t>09:39:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>7.25</v>
+        <v>5.95</v>
       </c>
       <c r="F45" t="n">
-        <v>14.49</v>
+        <v>16.79</v>
       </c>
       <c r="G45" t="n">
-        <v>293.6</v>
+        <v>285.8</v>
       </c>
       <c r="H45" t="n">
-        <v>99.3</v>
+        <v>97.7</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-70.52</v>
+        <v>100.03</v>
       </c>
       <c r="K45" t="n">
-        <v>-116.98</v>
+        <v>-21.61</v>
       </c>
       <c r="L45" t="n">
-        <v>136.59</v>
+        <v>102.34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:41:13</t>
+          <t>09:41:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.95</v>
+        <v>6.48</v>
       </c>
       <c r="F46" t="n">
-        <v>14.09</v>
+        <v>13.43</v>
       </c>
       <c r="G46" t="n">
-        <v>273.4</v>
+        <v>280.5</v>
       </c>
       <c r="H46" t="n">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>51</v>
+        <v>-86.69</v>
       </c>
       <c r="K46" t="n">
-        <v>-44.26</v>
+        <v>-83.31</v>
       </c>
       <c r="L46" t="n">
-        <v>67.53</v>
+        <v>120.23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:46:37</t>
+          <t>09:46:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.98</v>
+        <v>5.8</v>
       </c>
       <c r="F47" t="n">
-        <v>14.87</v>
+        <v>14.34</v>
       </c>
       <c r="G47" t="n">
-        <v>279.3</v>
+        <v>292.5</v>
       </c>
       <c r="H47" t="n">
-        <v>99</v>
+        <v>92.5</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-73.28</v>
+        <v>-71.55</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.76</v>
+        <v>85.62</v>
       </c>
       <c r="L47" t="n">
-        <v>73.59</v>
+        <v>111.58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:48:05</t>
+          <t>09:47:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>6.45</v>
+        <v>6.03</v>
       </c>
       <c r="F48" t="n">
-        <v>14.67</v>
+        <v>15.66</v>
       </c>
       <c r="G48" t="n">
-        <v>303.2</v>
+        <v>276.1</v>
       </c>
       <c r="H48" t="n">
-        <v>97.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J48" t="n">
-        <v>-22.81</v>
+        <v>173.46</v>
       </c>
       <c r="K48" t="n">
-        <v>79.02</v>
+        <v>14.71</v>
       </c>
       <c r="L48" t="n">
-        <v>82.25</v>
+        <v>174.08</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:49:24</t>
+          <t>09:49:20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.4</v>
+        <v>6.94</v>
       </c>
       <c r="F49" t="n">
-        <v>14.61</v>
+        <v>15.7</v>
       </c>
       <c r="G49" t="n">
         <v>278</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>45.84</v>
+        <v>-105.38</v>
       </c>
       <c r="K49" t="n">
-        <v>13.86</v>
+        <v>46.74</v>
       </c>
       <c r="L49" t="n">
-        <v>47.89</v>
+        <v>115.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:53:29</t>
+          <t>09:53:18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,10 +2137,10 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>6.29</v>
+        <v>6.21</v>
       </c>
       <c r="F50" t="n">
-        <v>14.39</v>
+        <v>14.72</v>
       </c>
       <c r="G50" t="n">
         <v>292.4</v>
@@ -2149,22 +2149,22 @@
         <v>93.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-29.03</v>
+        <v>-296</v>
       </c>
       <c r="K50" t="n">
-        <v>244.11</v>
+        <v>-0.49</v>
       </c>
       <c r="L50" t="n">
-        <v>245.82</v>
+        <v>296</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:54:44</t>
+          <t>09:55:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,10 +2179,10 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.59</v>
+        <v>7.32</v>
       </c>
       <c r="F51" t="n">
-        <v>14.26</v>
+        <v>16.79</v>
       </c>
       <c r="G51" t="n">
         <v>269.1</v>
@@ -2191,22 +2191,22 @@
         <v>98.2</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>188.45</v>
+        <v>-0.27</v>
       </c>
       <c r="K51" t="n">
-        <v>-58.14</v>
+        <v>272.22</v>
       </c>
       <c r="L51" t="n">
-        <v>197.21</v>
+        <v>272.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:56:55</t>
+          <t>09:56:16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,10 +2221,10 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>6.94</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
-        <v>14.82</v>
+        <v>14.62</v>
       </c>
       <c r="G52" t="n">
         <v>289.2</v>
@@ -2233,22 +2233,22 @@
         <v>82</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>134.26</v>
+        <v>80.64</v>
       </c>
       <c r="K52" t="n">
-        <v>62.13</v>
+        <v>170.33</v>
       </c>
       <c r="L52" t="n">
-        <v>147.94</v>
+        <v>188.46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10:01:01</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,10 +2263,10 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6.11</v>
+        <v>6.32</v>
       </c>
       <c r="F53" t="n">
-        <v>14.11</v>
+        <v>16.32</v>
       </c>
       <c r="G53" t="n">
         <v>268.7</v>
@@ -2275,22 +2275,22 @@
         <v>93.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-308.2</v>
+        <v>-102.9</v>
       </c>
       <c r="K53" t="n">
-        <v>-251.54</v>
+        <v>-411</v>
       </c>
       <c r="L53" t="n">
-        <v>397.82</v>
+        <v>423.69</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10:02:11</t>
+          <t>10:03:38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,10 +2305,10 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.08</v>
+        <v>5.31</v>
       </c>
       <c r="F54" t="n">
-        <v>15.22</v>
+        <v>13.82</v>
       </c>
       <c r="G54" t="n">
         <v>264.2</v>
@@ -2317,22 +2317,22 @@
         <v>94.2</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-171.51</v>
+        <v>-285.45</v>
       </c>
       <c r="K54" t="n">
-        <v>-211.52</v>
+        <v>-133.62</v>
       </c>
       <c r="L54" t="n">
-        <v>272.31</v>
+        <v>315.17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10:03:37</t>
+          <t>10:04:48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,10 +2347,10 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>6.85</v>
+        <v>5.66</v>
       </c>
       <c r="F55" t="n">
-        <v>14.1</v>
+        <v>15.58</v>
       </c>
       <c r="G55" t="n">
         <v>284.6</v>
@@ -2359,22 +2359,22 @@
         <v>93.3</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-196.9</v>
+        <v>-2.94</v>
       </c>
       <c r="K55" t="n">
-        <v>145.12</v>
+        <v>-207.41</v>
       </c>
       <c r="L55" t="n">
-        <v>244.6</v>
+        <v>207.43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10:07:09</t>
+          <t>10:08:55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,10 +2389,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>6.5</v>
+        <v>6.52</v>
       </c>
       <c r="F56" t="n">
-        <v>14.02</v>
+        <v>16.37</v>
       </c>
       <c r="G56" t="n">
         <v>281.2</v>
@@ -2401,22 +2401,22 @@
         <v>87.3</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-232.38</v>
+        <v>-336.55</v>
       </c>
       <c r="K56" t="n">
-        <v>-249.8</v>
+        <v>-191.88</v>
       </c>
       <c r="L56" t="n">
-        <v>341.17</v>
+        <v>387.41</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10:08:35</t>
+          <t>10:10:26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,10 +2431,10 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.67</v>
+        <v>6.01</v>
       </c>
       <c r="F57" t="n">
-        <v>14.74</v>
+        <v>16.79</v>
       </c>
       <c r="G57" t="n">
         <v>283.5</v>
@@ -2443,22 +2443,22 @@
         <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>30.61</v>
+        <v>-259.38</v>
       </c>
       <c r="K57" t="n">
-        <v>357.78</v>
+        <v>322.57</v>
       </c>
       <c r="L57" t="n">
-        <v>359.09</v>
+        <v>413.92</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10:10:59</t>
+          <t>10:11:51</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2476,7 +2476,7 @@
         <v>6.81</v>
       </c>
       <c r="F58" t="n">
-        <v>14.61</v>
+        <v>15.4</v>
       </c>
       <c r="G58" t="n">
         <v>287.2</v>
@@ -2485,22 +2485,22 @@
         <v>98.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>443.01</v>
+        <v>418.89</v>
       </c>
       <c r="K58" t="n">
-        <v>286.33</v>
+        <v>589.1</v>
       </c>
       <c r="L58" t="n">
-        <v>527.49</v>
+        <v>722.85</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10:19:16</t>
+          <t>10:20:44</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6.08</v>
+        <v>6.77</v>
       </c>
       <c r="F59" t="n">
-        <v>15.03</v>
+        <v>16.26</v>
       </c>
       <c r="G59" t="n">
         <v>267</v>
@@ -2527,22 +2527,22 @@
         <v>100</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-86.44</v>
+        <v>-21.61</v>
       </c>
       <c r="K59" t="n">
-        <v>21.78</v>
+        <v>-114.65</v>
       </c>
       <c r="L59" t="n">
-        <v>89.14</v>
+        <v>116.67</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10:20:22</t>
+          <t>10:22:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,10 +2557,10 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.77</v>
+        <v>6.57</v>
       </c>
       <c r="F60" t="n">
-        <v>14.33</v>
+        <v>16.79</v>
       </c>
       <c r="G60" t="n">
         <v>296.9</v>
@@ -2569,22 +2569,22 @@
         <v>91.3</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-85.8</v>
+        <v>67.2</v>
       </c>
       <c r="K60" t="n">
-        <v>24.16</v>
+        <v>-91.42</v>
       </c>
       <c r="L60" t="n">
-        <v>89.13</v>
+        <v>113.46</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:22:24</t>
+          <t>10:23:20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>6.54</v>
+        <v>7.07</v>
       </c>
       <c r="F61" t="n">
-        <v>14.05</v>
+        <v>16.79</v>
       </c>
       <c r="G61" t="n">
-        <v>287.4</v>
+        <v>272.3</v>
       </c>
       <c r="H61" t="n">
-        <v>92.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-54.22</v>
+        <v>-78.22</v>
       </c>
       <c r="K61" t="n">
-        <v>36.8</v>
+        <v>48.27</v>
       </c>
       <c r="L61" t="n">
-        <v>65.53</v>
+        <v>91.91</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:27:59</t>
+          <t>10:28:14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2644,31 +2644,31 @@
         <v>7.17</v>
       </c>
       <c r="F62" t="n">
-        <v>14.98</v>
+        <v>16.79</v>
       </c>
       <c r="G62" t="n">
-        <v>285.6</v>
+        <v>290.7</v>
       </c>
       <c r="H62" t="n">
-        <v>94.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="I62" t="n">
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-72.17</v>
+        <v>-92.55</v>
       </c>
       <c r="K62" t="n">
-        <v>28.32</v>
+        <v>38.29</v>
       </c>
       <c r="L62" t="n">
-        <v>77.52</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:29:10</t>
+          <t>10:30:06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2686,31 +2686,31 @@
         <v>6.34</v>
       </c>
       <c r="F63" t="n">
-        <v>14.15</v>
+        <v>16.49</v>
       </c>
       <c r="G63" t="n">
-        <v>280</v>
+        <v>274.1</v>
       </c>
       <c r="H63" t="n">
-        <v>95</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>30.05</v>
+        <v>27.99</v>
       </c>
       <c r="K63" t="n">
-        <v>129.28</v>
+        <v>147.53</v>
       </c>
       <c r="L63" t="n">
-        <v>132.73</v>
+        <v>150.17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:29:49</t>
+          <t>10:31:17</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2728,31 +2728,31 @@
         <v>6.57</v>
       </c>
       <c r="F64" t="n">
-        <v>14.82</v>
+        <v>16.69</v>
       </c>
       <c r="G64" t="n">
-        <v>283.6</v>
+        <v>287.6</v>
       </c>
       <c r="H64" t="n">
-        <v>93</v>
+        <v>95.7</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-114.2</v>
+        <v>-132.01</v>
       </c>
       <c r="K64" t="n">
-        <v>-53.09</v>
+        <v>-55.94</v>
       </c>
       <c r="L64" t="n">
-        <v>125.93</v>
+        <v>143.37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:34:55</t>
+          <t>10:34:23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2770,31 +2770,31 @@
         <v>6.43</v>
       </c>
       <c r="F65" t="n">
-        <v>14.42</v>
+        <v>15.04</v>
       </c>
       <c r="G65" t="n">
-        <v>285</v>
+        <v>279.6</v>
       </c>
       <c r="H65" t="n">
-        <v>96.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-139.69</v>
+        <v>-192.62</v>
       </c>
       <c r="K65" t="n">
-        <v>28.55</v>
+        <v>35.36</v>
       </c>
       <c r="L65" t="n">
-        <v>142.57</v>
+        <v>195.84</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:36:21</t>
+          <t>10:35:29</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2812,31 +2812,31 @@
         <v>6.95</v>
       </c>
       <c r="F66" t="n">
-        <v>13.72</v>
+        <v>16.79</v>
       </c>
       <c r="G66" t="n">
-        <v>281.7</v>
+        <v>265.7</v>
       </c>
       <c r="H66" t="n">
-        <v>91</v>
+        <v>94.8</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>55.68</v>
+        <v>30.32</v>
       </c>
       <c r="K66" t="n">
-        <v>207.86</v>
+        <v>235.04</v>
       </c>
       <c r="L66" t="n">
-        <v>215.19</v>
+        <v>236.98</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:37:29</t>
+          <t>10:36:56</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2854,31 +2854,31 @@
         <v>5.6</v>
       </c>
       <c r="F67" t="n">
-        <v>14.85</v>
+        <v>15.29</v>
       </c>
       <c r="G67" t="n">
-        <v>284.6</v>
+        <v>288.2</v>
       </c>
       <c r="H67" t="n">
-        <v>89</v>
+        <v>96.2</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.1</v>
+        <v>-32.22</v>
       </c>
       <c r="K67" t="n">
-        <v>-149.52</v>
+        <v>-182.7</v>
       </c>
       <c r="L67" t="n">
-        <v>149.52</v>
+        <v>185.51</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:41:47</t>
+          <t>10:40:37</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="F68" t="n">
-        <v>14.76</v>
+        <v>16.79</v>
       </c>
       <c r="G68" t="n">
-        <v>273.3</v>
+        <v>286.3</v>
       </c>
       <c r="H68" t="n">
-        <v>92.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-273.16</v>
+        <v>-366.42</v>
       </c>
       <c r="K68" t="n">
-        <v>-113.76</v>
+        <v>-103.82</v>
       </c>
       <c r="L68" t="n">
-        <v>295.9</v>
+        <v>380.84</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:44:05</t>
+          <t>10:41:38</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="F69" t="n">
-        <v>14.57</v>
+        <v>13.58</v>
       </c>
       <c r="G69" t="n">
-        <v>280.2</v>
+        <v>282.6</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>4.93</v>
+        <v>-59.39</v>
       </c>
       <c r="K69" t="n">
-        <v>-193.63</v>
+        <v>-253.09</v>
       </c>
       <c r="L69" t="n">
-        <v>193.69</v>
+        <v>259.96</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:45:45</t>
+          <t>10:43:56</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.97</v>
+        <v>6.96</v>
       </c>
       <c r="F70" t="n">
-        <v>14.46</v>
+        <v>16.79</v>
       </c>
       <c r="G70" t="n">
-        <v>288.5</v>
+        <v>280.3</v>
       </c>
       <c r="H70" t="n">
-        <v>91.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>263.26</v>
+        <v>317.02</v>
       </c>
       <c r="K70" t="n">
-        <v>-121.55</v>
+        <v>-168.8</v>
       </c>
       <c r="L70" t="n">
-        <v>289.96</v>
+        <v>359.16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:50:47</t>
+          <t>10:47:57</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.93</v>
+        <v>6.91</v>
       </c>
       <c r="F71" t="n">
-        <v>14.14</v>
+        <v>16.79</v>
       </c>
       <c r="G71" t="n">
-        <v>285.2</v>
+        <v>273.9</v>
       </c>
       <c r="H71" t="n">
-        <v>97</v>
+        <v>96.5</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-447.2</v>
+        <v>-587.87</v>
       </c>
       <c r="K71" t="n">
-        <v>-73.37</v>
+        <v>-101.52</v>
       </c>
       <c r="L71" t="n">
-        <v>453.18</v>
+        <v>596.5700000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:52:57</t>
+          <t>10:50:05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>7.13</v>
+        <v>7.12</v>
       </c>
       <c r="F72" t="n">
-        <v>14.69</v>
+        <v>16.79</v>
       </c>
       <c r="G72" t="n">
-        <v>281</v>
+        <v>285.1</v>
       </c>
       <c r="H72" t="n">
-        <v>89.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-328.53</v>
+        <v>-447.51</v>
       </c>
       <c r="K72" t="n">
-        <v>-436.15</v>
+        <v>-489.06</v>
       </c>
       <c r="L72" t="n">
-        <v>546.04</v>
+        <v>662.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:55:12</t>
+          <t>10:52:15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="F73" t="n">
-        <v>14.56</v>
+        <v>16.79</v>
       </c>
       <c r="G73" t="n">
-        <v>297.2</v>
+        <v>282.4</v>
       </c>
       <c r="H73" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-257.98</v>
+        <v>-404.02</v>
       </c>
       <c r="K73" t="n">
-        <v>356.14</v>
+        <v>457.67</v>
       </c>
       <c r="L73" t="n">
-        <v>439.76</v>
+        <v>610.49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11:07:02</t>
+          <t>11:04:57</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3148,31 +3148,31 @@
         <v>6.82</v>
       </c>
       <c r="F74" t="n">
-        <v>14.9</v>
+        <v>16.79</v>
       </c>
       <c r="G74" t="n">
-        <v>292</v>
+        <v>289.3</v>
       </c>
       <c r="H74" t="n">
-        <v>90.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.02</v>
+        <v>-6.05</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.88</v>
+        <v>-6.06</v>
       </c>
       <c r="L74" t="n">
-        <v>5.97</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11:08:49</t>
+          <t>11:06:53</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="F75" t="n">
-        <v>14.39</v>
+        <v>16.79</v>
       </c>
       <c r="G75" t="n">
-        <v>280.2</v>
+        <v>278.9</v>
       </c>
       <c r="H75" t="n">
-        <v>90.8</v>
+        <v>94</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>-83.65000000000001</v>
+        <v>-107.6</v>
       </c>
       <c r="K75" t="n">
-        <v>-32.96</v>
+        <v>-41.03</v>
       </c>
       <c r="L75" t="n">
-        <v>89.91</v>
+        <v>115.15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:09:44</t>
+          <t>11:08:39</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3232,31 +3232,31 @@
         <v>6.65</v>
       </c>
       <c r="F76" t="n">
-        <v>14.74</v>
+        <v>16.79</v>
       </c>
       <c r="G76" t="n">
-        <v>296.2</v>
+        <v>286</v>
       </c>
       <c r="H76" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>44.32</v>
+        <v>59.13</v>
       </c>
       <c r="K76" t="n">
-        <v>-73.48</v>
+        <v>-102.73</v>
       </c>
       <c r="L76" t="n">
-        <v>85.81</v>
+        <v>118.53</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11:14:57</t>
+          <t>11:12:19</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.78</v>
+        <v>5.77</v>
       </c>
       <c r="F77" t="n">
-        <v>15.11</v>
+        <v>16.09</v>
       </c>
       <c r="G77" t="n">
-        <v>276.4</v>
+        <v>293.5</v>
       </c>
       <c r="H77" t="n">
-        <v>99.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>-21.74</v>
+        <v>-47.66</v>
       </c>
       <c r="K77" t="n">
-        <v>45.98</v>
+        <v>77.27</v>
       </c>
       <c r="L77" t="n">
-        <v>50.86</v>
+        <v>90.78</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11:16:51</t>
+          <t>11:15:04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.75</v>
+        <v>6.74</v>
       </c>
       <c r="F78" t="n">
-        <v>14.43</v>
+        <v>16.79</v>
       </c>
       <c r="G78" t="n">
-        <v>285.8</v>
+        <v>279.8</v>
       </c>
       <c r="H78" t="n">
-        <v>94</v>
+        <v>96.8</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>23.08</v>
+        <v>17.08</v>
       </c>
       <c r="K78" t="n">
-        <v>92.2</v>
+        <v>114.59</v>
       </c>
       <c r="L78" t="n">
-        <v>95.05</v>
+        <v>115.86</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11:18:03</t>
+          <t>11:16:57</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3358,31 +3358,31 @@
         <v>7.09</v>
       </c>
       <c r="F79" t="n">
-        <v>13.75</v>
+        <v>16.79</v>
       </c>
       <c r="G79" t="n">
-        <v>283.8</v>
+        <v>266.2</v>
       </c>
       <c r="H79" t="n">
-        <v>99.5</v>
+        <v>95.8</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>-78.23999999999999</v>
+        <v>-108.75</v>
       </c>
       <c r="K79" t="n">
-        <v>-88.8</v>
+        <v>-116.12</v>
       </c>
       <c r="L79" t="n">
-        <v>118.35</v>
+        <v>159.09</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11:22:34</t>
+          <t>11:20:45</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="F80" t="n">
-        <v>14.33</v>
+        <v>16.79</v>
       </c>
       <c r="G80" t="n">
-        <v>274.9</v>
+        <v>277.7</v>
       </c>
       <c r="H80" t="n">
-        <v>97.3</v>
+        <v>91.3</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>111.92</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>83.18000000000001</v>
+        <v>149.74</v>
       </c>
       <c r="L80" t="n">
-        <v>139.44</v>
+        <v>168.85</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11:23:19</t>
+          <t>11:22:48</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3442,31 +3442,31 @@
         <v>6.17</v>
       </c>
       <c r="F81" t="n">
-        <v>14.3</v>
+        <v>16</v>
       </c>
       <c r="G81" t="n">
-        <v>283.7</v>
+        <v>277.1</v>
       </c>
       <c r="H81" t="n">
-        <v>99.7</v>
+        <v>95.7</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>62.3</v>
+        <v>2.51</v>
       </c>
       <c r="K81" t="n">
-        <v>-116.01</v>
+        <v>-166.36</v>
       </c>
       <c r="L81" t="n">
-        <v>131.68</v>
+        <v>166.37</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11:24:35</t>
+          <t>11:23:32</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3484,31 +3484,31 @@
         <v>6.95</v>
       </c>
       <c r="F82" t="n">
-        <v>14.51</v>
+        <v>16.79</v>
       </c>
       <c r="G82" t="n">
-        <v>288.9</v>
+        <v>281.5</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>7.89</v>
+        <v>-81.12</v>
       </c>
       <c r="K82" t="n">
-        <v>126.47</v>
+        <v>166.55</v>
       </c>
       <c r="L82" t="n">
-        <v>126.72</v>
+        <v>185.26</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:28:05</t>
+          <t>11:27:31</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,31 +3526,31 @@
         <v>6.64</v>
       </c>
       <c r="F83" t="n">
-        <v>15.28</v>
+        <v>16.79</v>
       </c>
       <c r="G83" t="n">
-        <v>288.7</v>
+        <v>296.8</v>
       </c>
       <c r="H83" t="n">
-        <v>91.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>125.24</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>67.63</v>
+        <v>173.34</v>
       </c>
       <c r="L83" t="n">
-        <v>142.33</v>
+        <v>185.56</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:29:23</t>
+          <t>11:29:04</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3568,31 +3568,31 @@
         <v>6.87</v>
       </c>
       <c r="F84" t="n">
-        <v>15.24</v>
+        <v>16.79</v>
       </c>
       <c r="G84" t="n">
-        <v>276</v>
+        <v>295.9</v>
       </c>
       <c r="H84" t="n">
-        <v>93.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I84" t="n">
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>198.59</v>
+        <v>188.64</v>
       </c>
       <c r="K84" t="n">
-        <v>145.11</v>
+        <v>229.96</v>
       </c>
       <c r="L84" t="n">
-        <v>245.96</v>
+        <v>297.43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:31:38</t>
+          <t>11:30:23</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3610,31 +3610,31 @@
         <v>7.08</v>
       </c>
       <c r="F85" t="n">
-        <v>15.67</v>
+        <v>16.79</v>
       </c>
       <c r="G85" t="n">
-        <v>293.5</v>
+        <v>304.6</v>
       </c>
       <c r="H85" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-196.12</v>
+        <v>-266.54</v>
       </c>
       <c r="K85" t="n">
-        <v>-241.4</v>
+        <v>-260.66</v>
       </c>
       <c r="L85" t="n">
-        <v>311.02</v>
+        <v>372.81</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:35:44</t>
+          <t>11:35:01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3652,31 +3652,31 @@
         <v>6.21</v>
       </c>
       <c r="F86" t="n">
-        <v>14.89</v>
+        <v>12.71</v>
       </c>
       <c r="G86" t="n">
-        <v>277.8</v>
+        <v>288.9</v>
       </c>
       <c r="H86" t="n">
-        <v>83.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-142.46</v>
+        <v>-216.86</v>
       </c>
       <c r="K86" t="n">
-        <v>-446.82</v>
+        <v>-508.01</v>
       </c>
       <c r="L86" t="n">
-        <v>468.99</v>
+        <v>552.36</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:37:18</t>
+          <t>11:36:38</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3694,31 +3694,31 @@
         <v>7.13</v>
       </c>
       <c r="F87" t="n">
-        <v>14.77</v>
+        <v>16.79</v>
       </c>
       <c r="G87" t="n">
-        <v>279.3</v>
+        <v>286.7</v>
       </c>
       <c r="H87" t="n">
-        <v>86.7</v>
+        <v>93.5</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-34.45</v>
+        <v>-144.92</v>
       </c>
       <c r="K87" t="n">
-        <v>456.46</v>
+        <v>606.67</v>
       </c>
       <c r="L87" t="n">
-        <v>457.76</v>
+        <v>623.74</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:39:14</t>
+          <t>11:38:12</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.72</v>
+        <v>6.71</v>
       </c>
       <c r="F88" t="n">
-        <v>14.79</v>
+        <v>16.79</v>
       </c>
       <c r="G88" t="n">
-        <v>273.4</v>
+        <v>287</v>
       </c>
       <c r="H88" t="n">
-        <v>92.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>287.93</v>
+        <v>182.78</v>
       </c>
       <c r="K88" t="n">
-        <v>156.47</v>
+        <v>332.92</v>
       </c>
       <c r="L88" t="n">
-        <v>327.7</v>
+        <v>379.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>81.23</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-20.62</v>
+        <v>-22.31</v>
       </c>
       <c r="L14" t="n">
-        <v>83.81</v>
+        <v>90.64</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>-38.25</v>
+        <v>-41.26</v>
       </c>
       <c r="K15" t="n">
-        <v>77.34</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>86.29000000000001</v>
+        <v>93.06999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.41</v>
+        <v>-18.77</v>
       </c>
       <c r="K16" t="n">
-        <v>82.64</v>
+        <v>89.09</v>
       </c>
       <c r="L16" t="n">
-        <v>84.45</v>
+        <v>91.04000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>85.89</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-80.56999999999999</v>
+        <v>-89.58</v>
       </c>
       <c r="L17" t="n">
-        <v>117.77</v>
+        <v>130.93</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>67.34</v>
+        <v>69.36</v>
       </c>
       <c r="K18" t="n">
-        <v>-51.53</v>
+        <v>-53.07</v>
       </c>
       <c r="L18" t="n">
-        <v>84.79000000000001</v>
+        <v>87.33</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>-102.77</v>
+        <v>-110.67</v>
       </c>
       <c r="K19" t="n">
-        <v>62.78</v>
+        <v>67.61</v>
       </c>
       <c r="L19" t="n">
-        <v>120.43</v>
+        <v>129.69</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-171.94</v>
+        <v>-192.18</v>
       </c>
       <c r="K20" t="n">
-        <v>134.83</v>
+        <v>150.7</v>
       </c>
       <c r="L20" t="n">
-        <v>218.5</v>
+        <v>244.22</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-95.33</v>
+        <v>-103.55</v>
       </c>
       <c r="K21" t="n">
-        <v>197.37</v>
+        <v>214.38</v>
       </c>
       <c r="L21" t="n">
-        <v>219.19</v>
+        <v>238.07</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>-172.03</v>
+        <v>-192.4</v>
       </c>
       <c r="K22" t="n">
-        <v>-102.33</v>
+        <v>-114.45</v>
       </c>
       <c r="L22" t="n">
-        <v>200.17</v>
+        <v>223.86</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-60.7</v>
+        <v>-67.95</v>
       </c>
       <c r="K23" t="n">
-        <v>305.43</v>
+        <v>341.91</v>
       </c>
       <c r="L23" t="n">
-        <v>311.41</v>
+        <v>348.6</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-121.74</v>
+        <v>-134.19</v>
       </c>
       <c r="K24" t="n">
-        <v>-251.97</v>
+        <v>-277.74</v>
       </c>
       <c r="L24" t="n">
-        <v>279.83</v>
+        <v>308.46</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>296.86</v>
+        <v>322.26</v>
       </c>
       <c r="K25" t="n">
-        <v>42.75</v>
+        <v>46.41</v>
       </c>
       <c r="L25" t="n">
-        <v>299.92</v>
+        <v>325.59</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-480.69</v>
+        <v>-527</v>
       </c>
       <c r="K26" t="n">
-        <v>-97.19</v>
+        <v>-106.56</v>
       </c>
       <c r="L26" t="n">
-        <v>490.41</v>
+        <v>537.67</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>325.27</v>
+        <v>338.67</v>
       </c>
       <c r="K27" t="n">
-        <v>-179.87</v>
+        <v>-187.28</v>
       </c>
       <c r="L27" t="n">
-        <v>371.69</v>
+        <v>387</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>-110.36</v>
+        <v>-126.51</v>
       </c>
       <c r="K28" t="n">
-        <v>-42.93</v>
+        <v>-49.22</v>
       </c>
       <c r="L28" t="n">
-        <v>118.42</v>
+        <v>135.75</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-113.47</v>
+        <v>-125.97</v>
       </c>
       <c r="K29" t="n">
-        <v>-15.3</v>
+        <v>-16.99</v>
       </c>
       <c r="L29" t="n">
-        <v>114.5</v>
+        <v>127.11</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.38</v>
+        <v>-1.39</v>
       </c>
       <c r="K30" t="n">
-        <v>-62.38</v>
+        <v>-62.88</v>
       </c>
       <c r="L30" t="n">
-        <v>62.39</v>
+        <v>62.89</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-118.98</v>
+        <v>-126.96</v>
       </c>
       <c r="K31" t="n">
-        <v>85.03</v>
+        <v>90.73</v>
       </c>
       <c r="L31" t="n">
-        <v>146.24</v>
+        <v>156.05</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>43.04</v>
+        <v>47.84</v>
       </c>
       <c r="K32" t="n">
-        <v>-115.11</v>
+        <v>-127.97</v>
       </c>
       <c r="L32" t="n">
-        <v>122.89</v>
+        <v>136.62</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-116.02</v>
+        <v>-125.66</v>
       </c>
       <c r="K33" t="n">
-        <v>-105.99</v>
+        <v>-114.79</v>
       </c>
       <c r="L33" t="n">
-        <v>157.14</v>
+        <v>170.2</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-102.64</v>
+        <v>-101.49</v>
       </c>
       <c r="K34" t="n">
-        <v>24.17</v>
+        <v>23.9</v>
       </c>
       <c r="L34" t="n">
-        <v>105.45</v>
+        <v>104.27</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-181.86</v>
+        <v>-191.31</v>
       </c>
       <c r="K35" t="n">
-        <v>135.98</v>
+        <v>143.05</v>
       </c>
       <c r="L35" t="n">
-        <v>227.07</v>
+        <v>238.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>127.48</v>
+        <v>140.62</v>
       </c>
       <c r="K36" t="n">
-        <v>135.64</v>
+        <v>149.61</v>
       </c>
       <c r="L36" t="n">
-        <v>186.14</v>
+        <v>205.33</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>23.23</v>
+        <v>25.62</v>
       </c>
       <c r="K37" t="n">
-        <v>9.369999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="L37" t="n">
-        <v>25.05</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-99.54000000000001</v>
+        <v>-106.48</v>
       </c>
       <c r="K38" t="n">
-        <v>-272.67</v>
+        <v>-291.69</v>
       </c>
       <c r="L38" t="n">
-        <v>290.27</v>
+        <v>310.52</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-246.18</v>
+        <v>-258.24</v>
       </c>
       <c r="K39" t="n">
-        <v>40.75</v>
+        <v>42.75</v>
       </c>
       <c r="L39" t="n">
-        <v>249.53</v>
+        <v>261.76</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-247.49</v>
+        <v>-254.92</v>
       </c>
       <c r="K40" t="n">
-        <v>47.73</v>
+        <v>49.16</v>
       </c>
       <c r="L40" t="n">
-        <v>252.05</v>
+        <v>259.62</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>509.79</v>
+        <v>559.95</v>
       </c>
       <c r="K41" t="n">
-        <v>-137.79</v>
+        <v>-151.35</v>
       </c>
       <c r="L41" t="n">
-        <v>528.08</v>
+        <v>580.04</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>-137.29</v>
+        <v>-145.15</v>
       </c>
       <c r="K42" t="n">
-        <v>325.77</v>
+        <v>344.42</v>
       </c>
       <c r="L42" t="n">
-        <v>353.52</v>
+        <v>373.76</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>-648.41</v>
+        <v>-734.1900000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>87.59</v>
+        <v>99.17</v>
       </c>
       <c r="L43" t="n">
-        <v>654.29</v>
+        <v>740.86</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-84.06999999999999</v>
+        <v>-91.65000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="L44" t="n">
-        <v>84.06999999999999</v>
+        <v>91.65000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>100.03</v>
+        <v>110.72</v>
       </c>
       <c r="K45" t="n">
-        <v>-21.61</v>
+        <v>-23.92</v>
       </c>
       <c r="L45" t="n">
-        <v>102.34</v>
+        <v>113.27</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-86.69</v>
+        <v>-92.72</v>
       </c>
       <c r="K46" t="n">
-        <v>-83.31</v>
+        <v>-89.09999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>120.23</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-71.55</v>
+        <v>-76.92</v>
       </c>
       <c r="K47" t="n">
-        <v>85.62</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>111.58</v>
+        <v>119.95</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>17</v>
       </c>
       <c r="J48" t="n">
-        <v>173.46</v>
+        <v>188.82</v>
       </c>
       <c r="K48" t="n">
-        <v>14.71</v>
+        <v>16.01</v>
       </c>
       <c r="L48" t="n">
-        <v>174.08</v>
+        <v>189.49</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-105.38</v>
+        <v>-105.56</v>
       </c>
       <c r="K49" t="n">
-        <v>46.74</v>
+        <v>46.82</v>
       </c>
       <c r="L49" t="n">
-        <v>115.28</v>
+        <v>115.47</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-296</v>
+        <v>-300.37</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="L50" t="n">
-        <v>296</v>
+        <v>300.37</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="K51" t="n">
-        <v>272.22</v>
+        <v>299.68</v>
       </c>
       <c r="L51" t="n">
-        <v>272.22</v>
+        <v>299.68</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>80.64</v>
+        <v>90.13</v>
       </c>
       <c r="K52" t="n">
-        <v>170.33</v>
+        <v>190.38</v>
       </c>
       <c r="L52" t="n">
-        <v>188.46</v>
+        <v>210.64</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-102.9</v>
+        <v>-110.03</v>
       </c>
       <c r="K53" t="n">
-        <v>-411</v>
+        <v>-439.47</v>
       </c>
       <c r="L53" t="n">
-        <v>423.69</v>
+        <v>453.04</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-285.45</v>
+        <v>-304.59</v>
       </c>
       <c r="K54" t="n">
-        <v>-133.62</v>
+        <v>-142.58</v>
       </c>
       <c r="L54" t="n">
-        <v>315.17</v>
+        <v>336.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.94</v>
+        <v>-3.03</v>
       </c>
       <c r="K55" t="n">
-        <v>-207.41</v>
+        <v>-213.75</v>
       </c>
       <c r="L55" t="n">
-        <v>207.43</v>
+        <v>213.77</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-336.55</v>
+        <v>-358.17</v>
       </c>
       <c r="K56" t="n">
-        <v>-191.88</v>
+        <v>-204.21</v>
       </c>
       <c r="L56" t="n">
-        <v>387.41</v>
+        <v>412.29</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-259.38</v>
+        <v>-289.49</v>
       </c>
       <c r="K57" t="n">
-        <v>322.57</v>
+        <v>360.03</v>
       </c>
       <c r="L57" t="n">
-        <v>413.92</v>
+        <v>461.98</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>418.89</v>
+        <v>446.17</v>
       </c>
       <c r="K58" t="n">
-        <v>589.1</v>
+        <v>627.47</v>
       </c>
       <c r="L58" t="n">
-        <v>722.85</v>
+        <v>769.92</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-21.61</v>
+        <v>-21.33</v>
       </c>
       <c r="K59" t="n">
-        <v>-114.65</v>
+        <v>-113.15</v>
       </c>
       <c r="L59" t="n">
-        <v>116.67</v>
+        <v>115.14</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>67.2</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-91.42</v>
+        <v>-90.37</v>
       </c>
       <c r="L60" t="n">
-        <v>113.46</v>
+        <v>112.16</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-78.22</v>
+        <v>-79.65000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>48.27</v>
+        <v>49.16</v>
       </c>
       <c r="L61" t="n">
-        <v>91.91</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-92.55</v>
+        <v>-92.61</v>
       </c>
       <c r="K62" t="n">
-        <v>38.29</v>
+        <v>38.31</v>
       </c>
       <c r="L62" t="n">
-        <v>100.16</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>27.99</v>
+        <v>28.62</v>
       </c>
       <c r="K63" t="n">
-        <v>147.53</v>
+        <v>150.85</v>
       </c>
       <c r="L63" t="n">
-        <v>150.17</v>
+        <v>153.54</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-132.01</v>
+        <v>-130.08</v>
       </c>
       <c r="K64" t="n">
-        <v>-55.94</v>
+        <v>-55.12</v>
       </c>
       <c r="L64" t="n">
-        <v>143.37</v>
+        <v>141.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-192.62</v>
+        <v>-199.03</v>
       </c>
       <c r="K65" t="n">
-        <v>35.36</v>
+        <v>36.54</v>
       </c>
       <c r="L65" t="n">
-        <v>195.84</v>
+        <v>202.36</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>30.32</v>
+        <v>31.31</v>
       </c>
       <c r="K66" t="n">
-        <v>235.04</v>
+        <v>242.76</v>
       </c>
       <c r="L66" t="n">
-        <v>236.98</v>
+        <v>244.77</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-32.22</v>
+        <v>-34.46</v>
       </c>
       <c r="K67" t="n">
-        <v>-182.7</v>
+        <v>-195.42</v>
       </c>
       <c r="L67" t="n">
-        <v>185.51</v>
+        <v>198.43</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-366.42</v>
+        <v>-416.81</v>
       </c>
       <c r="K68" t="n">
-        <v>-103.82</v>
+        <v>-118.1</v>
       </c>
       <c r="L68" t="n">
-        <v>380.84</v>
+        <v>433.22</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-59.39</v>
+        <v>-67.45</v>
       </c>
       <c r="K69" t="n">
-        <v>-253.09</v>
+        <v>-287.47</v>
       </c>
       <c r="L69" t="n">
-        <v>259.96</v>
+        <v>295.28</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>317.02</v>
+        <v>339.3</v>
       </c>
       <c r="K70" t="n">
-        <v>-168.8</v>
+        <v>-180.66</v>
       </c>
       <c r="L70" t="n">
-        <v>359.16</v>
+        <v>384.4</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-587.87</v>
+        <v>-626.3200000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-101.52</v>
+        <v>-108.16</v>
       </c>
       <c r="L71" t="n">
-        <v>596.5700000000001</v>
+        <v>635.59</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-447.51</v>
+        <v>-495.28</v>
       </c>
       <c r="K72" t="n">
-        <v>-489.06</v>
+        <v>-541.26</v>
       </c>
       <c r="L72" t="n">
-        <v>662.9</v>
+        <v>733.66</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-404.02</v>
+        <v>-451.63</v>
       </c>
       <c r="K73" t="n">
-        <v>457.67</v>
+        <v>511.59</v>
       </c>
       <c r="L73" t="n">
-        <v>610.49</v>
+        <v>682.42</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.05</v>
+        <v>-5.97</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.06</v>
+        <v>-5.98</v>
       </c>
       <c r="L74" t="n">
-        <v>8.56</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>-107.6</v>
+        <v>-115.09</v>
       </c>
       <c r="K75" t="n">
-        <v>-41.03</v>
+        <v>-43.89</v>
       </c>
       <c r="L75" t="n">
-        <v>115.15</v>
+        <v>123.18</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>59.13</v>
+        <v>63.15</v>
       </c>
       <c r="K76" t="n">
-        <v>-102.73</v>
+        <v>-109.72</v>
       </c>
       <c r="L76" t="n">
-        <v>118.53</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>-47.66</v>
+        <v>-51.97</v>
       </c>
       <c r="K77" t="n">
-        <v>77.27</v>
+        <v>84.25</v>
       </c>
       <c r="L77" t="n">
-        <v>90.78</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>17.08</v>
+        <v>17.13</v>
       </c>
       <c r="K78" t="n">
-        <v>114.59</v>
+        <v>114.9</v>
       </c>
       <c r="L78" t="n">
-        <v>115.86</v>
+        <v>116.17</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>-108.75</v>
+        <v>-116.06</v>
       </c>
       <c r="K79" t="n">
-        <v>-116.12</v>
+        <v>-123.92</v>
       </c>
       <c r="L79" t="n">
-        <v>159.09</v>
+        <v>169.78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>78.01000000000001</v>
+        <v>82.05</v>
       </c>
       <c r="K80" t="n">
-        <v>149.74</v>
+        <v>157.49</v>
       </c>
       <c r="L80" t="n">
-        <v>168.85</v>
+        <v>177.58</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>2.51</v>
+        <v>2.81</v>
       </c>
       <c r="K81" t="n">
-        <v>-166.36</v>
+        <v>-185.9</v>
       </c>
       <c r="L81" t="n">
-        <v>166.37</v>
+        <v>185.92</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-81.12</v>
+        <v>-90.59</v>
       </c>
       <c r="K82" t="n">
-        <v>166.55</v>
+        <v>186</v>
       </c>
       <c r="L82" t="n">
-        <v>185.26</v>
+        <v>206.89</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>66.23999999999999</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>173.34</v>
+        <v>188.5</v>
       </c>
       <c r="L83" t="n">
-        <v>185.56</v>
+        <v>201.8</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>188.64</v>
+        <v>201.88</v>
       </c>
       <c r="K84" t="n">
-        <v>229.96</v>
+        <v>246.09</v>
       </c>
       <c r="L84" t="n">
-        <v>297.43</v>
+        <v>318.3</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-266.54</v>
+        <v>-280.42</v>
       </c>
       <c r="K85" t="n">
-        <v>-260.66</v>
+        <v>-274.23</v>
       </c>
       <c r="L85" t="n">
-        <v>372.81</v>
+        <v>392.22</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-216.86</v>
+        <v>-242.2</v>
       </c>
       <c r="K86" t="n">
-        <v>-508.01</v>
+        <v>-567.39</v>
       </c>
       <c r="L86" t="n">
-        <v>552.36</v>
+        <v>616.92</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-144.92</v>
+        <v>-164.8</v>
       </c>
       <c r="K87" t="n">
-        <v>606.67</v>
+        <v>689.92</v>
       </c>
       <c r="L87" t="n">
-        <v>623.74</v>
+        <v>709.33</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>182.78</v>
+        <v>191.1</v>
       </c>
       <c r="K88" t="n">
-        <v>332.92</v>
+        <v>348.06</v>
       </c>
       <c r="L88" t="n">
-        <v>379.79</v>
+        <v>397.07</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -628,31 +628,31 @@
         <v>5.12</v>
       </c>
       <c r="F14" t="n">
-        <v>14.78</v>
+        <v>14.15</v>
       </c>
       <c r="G14" t="n">
-        <v>261.4</v>
+        <v>282.5</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>54.1</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>87.84999999999999</v>
+        <v>-49.54</v>
       </c>
       <c r="K14" t="n">
-        <v>-22.31</v>
+        <v>86.58</v>
       </c>
       <c r="L14" t="n">
-        <v>90.64</v>
+        <v>99.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:07:00</t>
+          <t>08:06:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.76</v>
+        <v>4.42</v>
       </c>
       <c r="F15" t="n">
-        <v>11.6</v>
+        <v>11.12</v>
       </c>
       <c r="G15" t="n">
-        <v>273.3</v>
+        <v>282.2</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>47.2</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-41.26</v>
+        <v>47.26</v>
       </c>
       <c r="K15" t="n">
-        <v>83.43000000000001</v>
+        <v>61.16</v>
       </c>
       <c r="L15" t="n">
-        <v>93.06999999999999</v>
+        <v>77.29000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:09:16</t>
+          <t>08:08:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,28 +709,28 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9</v>
+        <v>5.25</v>
       </c>
       <c r="F16" t="n">
-        <v>14.09</v>
+        <v>10.2</v>
       </c>
       <c r="G16" t="n">
-        <v>294.6</v>
+        <v>272.9</v>
       </c>
       <c r="H16" t="n">
-        <v>88.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.77</v>
+        <v>22.9</v>
       </c>
       <c r="K16" t="n">
-        <v>89.09</v>
+        <v>115.08</v>
       </c>
       <c r="L16" t="n">
-        <v>91.04000000000001</v>
+        <v>117.34</v>
       </c>
     </row>
     <row r="17">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.49</v>
+        <v>6.73</v>
       </c>
       <c r="F17" t="n">
-        <v>14.05</v>
+        <v>15.94</v>
       </c>
       <c r="G17" t="n">
-        <v>274.2</v>
+        <v>284.4</v>
       </c>
       <c r="H17" t="n">
-        <v>96.7</v>
+        <v>49.9</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>95.48999999999999</v>
+        <v>-324.35</v>
       </c>
       <c r="K17" t="n">
-        <v>-89.58</v>
+        <v>0.53</v>
       </c>
       <c r="L17" t="n">
-        <v>130.93</v>
+        <v>324.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:16:34</t>
+          <t>08:15:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.08</v>
+        <v>5.05</v>
       </c>
       <c r="F18" t="n">
-        <v>12.42</v>
+        <v>12.3</v>
       </c>
       <c r="G18" t="n">
-        <v>287.6</v>
+        <v>283.2</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>52.5</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>69.36</v>
+        <v>-51.88</v>
       </c>
       <c r="K18" t="n">
-        <v>-53.07</v>
+        <v>187.29</v>
       </c>
       <c r="L18" t="n">
-        <v>87.33</v>
+        <v>194.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:18:09</t>
+          <t>08:16:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.67</v>
+        <v>5.37</v>
       </c>
       <c r="F19" t="n">
-        <v>12.33</v>
+        <v>12.73</v>
       </c>
       <c r="G19" t="n">
-        <v>285.7</v>
+        <v>265.5</v>
       </c>
       <c r="H19" t="n">
-        <v>93.7</v>
+        <v>84.3</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J19" t="n">
-        <v>-110.67</v>
+        <v>19.88</v>
       </c>
       <c r="K19" t="n">
-        <v>67.61</v>
+        <v>-121.43</v>
       </c>
       <c r="L19" t="n">
-        <v>129.69</v>
+        <v>123.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:22:58</t>
+          <t>08:20:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.99</v>
+        <v>5.91</v>
       </c>
       <c r="F20" t="n">
-        <v>13.49</v>
+        <v>12.65</v>
       </c>
       <c r="G20" t="n">
-        <v>277.7</v>
+        <v>292.9</v>
       </c>
       <c r="H20" t="n">
-        <v>92.5</v>
+        <v>79.2</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-192.18</v>
+        <v>-216.95</v>
       </c>
       <c r="K20" t="n">
-        <v>150.7</v>
+        <v>18.98</v>
       </c>
       <c r="L20" t="n">
-        <v>244.22</v>
+        <v>217.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:24:14</t>
+          <t>08:22:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.78</v>
+        <v>5.95</v>
       </c>
       <c r="F21" t="n">
-        <v>15.58</v>
+        <v>13.43</v>
       </c>
       <c r="G21" t="n">
-        <v>288.1</v>
+        <v>272.5</v>
       </c>
       <c r="H21" t="n">
-        <v>89.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-103.55</v>
+        <v>-114.31</v>
       </c>
       <c r="K21" t="n">
-        <v>214.38</v>
+        <v>237.53</v>
       </c>
       <c r="L21" t="n">
-        <v>238.07</v>
+        <v>263.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:26:15</t>
+          <t>08:23:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.43</v>
+        <v>5.34</v>
       </c>
       <c r="F22" t="n">
-        <v>14.85</v>
+        <v>14.13</v>
       </c>
       <c r="G22" t="n">
-        <v>278.6</v>
+        <v>285.5</v>
       </c>
       <c r="H22" t="n">
-        <v>93.90000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-192.4</v>
+        <v>178.01</v>
       </c>
       <c r="K22" t="n">
-        <v>-114.45</v>
+        <v>-49.62</v>
       </c>
       <c r="L22" t="n">
-        <v>223.86</v>
+        <v>184.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:30:21</t>
+          <t>08:29:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.83</v>
+        <v>5.63</v>
       </c>
       <c r="F23" t="n">
-        <v>11.39</v>
+        <v>13.76</v>
       </c>
       <c r="G23" t="n">
-        <v>283.1</v>
+        <v>281.8</v>
       </c>
       <c r="H23" t="n">
-        <v>93</v>
+        <v>27.1</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-67.95</v>
+        <v>-87.59</v>
       </c>
       <c r="K23" t="n">
-        <v>341.91</v>
+        <v>238.08</v>
       </c>
       <c r="L23" t="n">
-        <v>348.6</v>
+        <v>253.68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:32:45</t>
+          <t>08:30:41</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5.53</v>
+        <v>6.11</v>
       </c>
       <c r="F24" t="n">
-        <v>12.67</v>
+        <v>16.79</v>
       </c>
       <c r="G24" t="n">
-        <v>275.7</v>
+        <v>294.3</v>
       </c>
       <c r="H24" t="n">
-        <v>95.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-134.19</v>
+        <v>-216</v>
       </c>
       <c r="K24" t="n">
-        <v>-277.74</v>
+        <v>276.8</v>
       </c>
       <c r="L24" t="n">
-        <v>308.46</v>
+        <v>351.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:35:07</t>
+          <t>08:32:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.65</v>
+        <v>4.9</v>
       </c>
       <c r="F25" t="n">
-        <v>14.17</v>
+        <v>14.42</v>
       </c>
       <c r="G25" t="n">
-        <v>296.8</v>
+        <v>279.9</v>
       </c>
       <c r="H25" t="n">
-        <v>98.3</v>
+        <v>91</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>322.26</v>
+        <v>-260.36</v>
       </c>
       <c r="K25" t="n">
-        <v>46.41</v>
+        <v>-183.47</v>
       </c>
       <c r="L25" t="n">
-        <v>325.59</v>
+        <v>318.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:39:56</t>
+          <t>08:37:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.45</v>
+        <v>6.12</v>
       </c>
       <c r="F26" t="n">
-        <v>13.04</v>
+        <v>14.75</v>
       </c>
       <c r="G26" t="n">
-        <v>289.8</v>
+        <v>279.9</v>
       </c>
       <c r="H26" t="n">
-        <v>88.5</v>
+        <v>49.4</v>
       </c>
       <c r="I26" t="n">
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-527</v>
+        <v>-450.32</v>
       </c>
       <c r="K26" t="n">
-        <v>-106.56</v>
+        <v>-91.09</v>
       </c>
       <c r="L26" t="n">
-        <v>537.67</v>
+        <v>459.44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:41:55</t>
+          <t>08:39:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.54</v>
+        <v>6.24</v>
       </c>
       <c r="F27" t="n">
-        <v>13.68</v>
+        <v>14.52</v>
       </c>
       <c r="G27" t="n">
-        <v>282</v>
+        <v>279.4</v>
       </c>
       <c r="H27" t="n">
-        <v>90.3</v>
+        <v>68.3</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>338.67</v>
+        <v>-537.9</v>
       </c>
       <c r="K27" t="n">
-        <v>-187.28</v>
+        <v>-322.44</v>
       </c>
       <c r="L27" t="n">
-        <v>387</v>
+        <v>627.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:43:47</t>
+          <t>08:40:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.49</v>
+        <v>6.42</v>
       </c>
       <c r="F28" t="n">
-        <v>15.54</v>
+        <v>15.86</v>
       </c>
       <c r="G28" t="n">
-        <v>270.1</v>
+        <v>292.1</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>24.7</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>-126.51</v>
+        <v>94.05</v>
       </c>
       <c r="K28" t="n">
-        <v>-49.22</v>
+        <v>-349.77</v>
       </c>
       <c r="L28" t="n">
-        <v>135.75</v>
+        <v>362.19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:55:39</t>
+          <t>08:51:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.78</v>
+        <v>6.01</v>
       </c>
       <c r="F29" t="n">
-        <v>15.99</v>
+        <v>16.79</v>
       </c>
       <c r="G29" t="n">
-        <v>301.4</v>
+        <v>293.1</v>
       </c>
       <c r="H29" t="n">
-        <v>96.3</v>
+        <v>80</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-125.97</v>
+        <v>-107.68</v>
       </c>
       <c r="K29" t="n">
-        <v>-16.99</v>
+        <v>16.01</v>
       </c>
       <c r="L29" t="n">
-        <v>127.11</v>
+        <v>108.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:56:57</t>
+          <t>08:52:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.79</v>
+        <v>5.23</v>
       </c>
       <c r="F30" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="G30" t="n">
-        <v>271.4</v>
+        <v>287.1</v>
       </c>
       <c r="H30" t="n">
-        <v>97.5</v>
+        <v>78</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.39</v>
+        <v>-92.59</v>
       </c>
       <c r="K30" t="n">
-        <v>-62.88</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>62.89</v>
+        <v>121.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:58:29</t>
+          <t>08:53:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>6.77</v>
+        <v>6.13</v>
       </c>
       <c r="F31" t="n">
-        <v>15.38</v>
+        <v>16.79</v>
       </c>
       <c r="G31" t="n">
-        <v>299</v>
+        <v>286.4</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-126.96</v>
+        <v>0.83</v>
       </c>
       <c r="K31" t="n">
-        <v>90.73</v>
+        <v>-107.28</v>
       </c>
       <c r="L31" t="n">
-        <v>156.05</v>
+        <v>107.29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09:02:42</t>
+          <t>08:59:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5.51</v>
+        <v>5.45</v>
       </c>
       <c r="F32" t="n">
-        <v>12.75</v>
+        <v>13.92</v>
       </c>
       <c r="G32" t="n">
-        <v>278.1</v>
+        <v>273.2</v>
       </c>
       <c r="H32" t="n">
-        <v>97.5</v>
+        <v>69.8</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>47.84</v>
+        <v>-111.44</v>
       </c>
       <c r="K32" t="n">
-        <v>-127.97</v>
+        <v>71.84</v>
       </c>
       <c r="L32" t="n">
-        <v>136.62</v>
+        <v>132.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09:04:18</t>
+          <t>09:00:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6.93</v>
+        <v>5.38</v>
       </c>
       <c r="F33" t="n">
-        <v>15.81</v>
+        <v>15.62</v>
       </c>
       <c r="G33" t="n">
-        <v>280.6</v>
+        <v>289.6</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-125.66</v>
+        <v>-118.75</v>
       </c>
       <c r="K33" t="n">
-        <v>-114.79</v>
+        <v>-46.38</v>
       </c>
       <c r="L33" t="n">
-        <v>170.2</v>
+        <v>127.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09:06:18</t>
+          <t>09:02:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.98</v>
+        <v>6.04</v>
       </c>
       <c r="F34" t="n">
-        <v>15.72</v>
+        <v>15.24</v>
       </c>
       <c r="G34" t="n">
-        <v>289.8</v>
+        <v>291</v>
       </c>
       <c r="H34" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-101.49</v>
+        <v>-178.4</v>
       </c>
       <c r="K34" t="n">
-        <v>23.9</v>
+        <v>2.78</v>
       </c>
       <c r="L34" t="n">
-        <v>104.27</v>
+        <v>178.43</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09:09:36</t>
+          <t>09:06:37</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.84</v>
+        <v>5.82</v>
       </c>
       <c r="F35" t="n">
-        <v>13.69</v>
+        <v>15.33</v>
       </c>
       <c r="G35" t="n">
-        <v>279.7</v>
+        <v>284.4</v>
       </c>
       <c r="H35" t="n">
-        <v>90.8</v>
+        <v>63.1</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>-191.31</v>
+        <v>-101.27</v>
       </c>
       <c r="K35" t="n">
-        <v>143.05</v>
+        <v>209.13</v>
       </c>
       <c r="L35" t="n">
-        <v>238.87</v>
+        <v>232.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09:11:33</t>
+          <t>09:08:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.22</v>
+        <v>6.49</v>
       </c>
       <c r="F36" t="n">
-        <v>10.97</v>
+        <v>14.6</v>
       </c>
       <c r="G36" t="n">
-        <v>289</v>
+        <v>270.6</v>
       </c>
       <c r="H36" t="n">
-        <v>96</v>
+        <v>61.5</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>140.62</v>
+        <v>-74.05</v>
       </c>
       <c r="K36" t="n">
-        <v>149.61</v>
+        <v>199.57</v>
       </c>
       <c r="L36" t="n">
-        <v>205.33</v>
+        <v>212.87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09:13:45</t>
+          <t>09:10:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.51</v>
+        <v>5.6</v>
       </c>
       <c r="F37" t="n">
-        <v>15.17</v>
+        <v>14.87</v>
       </c>
       <c r="G37" t="n">
-        <v>293.6</v>
+        <v>280.2</v>
       </c>
       <c r="H37" t="n">
-        <v>91.40000000000001</v>
+        <v>43.5</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>25.62</v>
+        <v>106.55</v>
       </c>
       <c r="K37" t="n">
-        <v>10.33</v>
+        <v>5.06</v>
       </c>
       <c r="L37" t="n">
-        <v>27.62</v>
+        <v>106.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:17:06</t>
+          <t>09:15:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.62</v>
+        <v>6.93</v>
       </c>
       <c r="F38" t="n">
-        <v>16.79</v>
+        <v>16.67</v>
       </c>
       <c r="G38" t="n">
-        <v>290.7</v>
+        <v>273.6</v>
       </c>
       <c r="H38" t="n">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-106.48</v>
+        <v>-305.02</v>
       </c>
       <c r="K38" t="n">
-        <v>-291.69</v>
+        <v>-150.45</v>
       </c>
       <c r="L38" t="n">
-        <v>310.52</v>
+        <v>340.11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:18:28</t>
+          <t>09:16:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4</v>
+        <v>6.84</v>
       </c>
       <c r="F39" t="n">
-        <v>16.13</v>
+        <v>16.79</v>
       </c>
       <c r="G39" t="n">
-        <v>289.7</v>
+        <v>278.7</v>
       </c>
       <c r="H39" t="n">
-        <v>95.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-258.24</v>
+        <v>-292.73</v>
       </c>
       <c r="K39" t="n">
-        <v>42.75</v>
+        <v>97.41</v>
       </c>
       <c r="L39" t="n">
-        <v>261.76</v>
+        <v>308.52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:20:49</t>
+          <t>09:18:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.43</v>
+        <v>6.36</v>
       </c>
       <c r="F40" t="n">
-        <v>16.19</v>
+        <v>16.49</v>
       </c>
       <c r="G40" t="n">
-        <v>284.3</v>
+        <v>282.9</v>
       </c>
       <c r="H40" t="n">
-        <v>99.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I40" t="n">
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-254.92</v>
+        <v>-213.1</v>
       </c>
       <c r="K40" t="n">
-        <v>49.16</v>
+        <v>298.55</v>
       </c>
       <c r="L40" t="n">
-        <v>259.62</v>
+        <v>366.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:26:08</t>
+          <t>09:22:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.89</v>
+        <v>6.21</v>
       </c>
       <c r="F41" t="n">
-        <v>15.47</v>
+        <v>16.79</v>
       </c>
       <c r="G41" t="n">
-        <v>282</v>
+        <v>294.2</v>
       </c>
       <c r="H41" t="n">
-        <v>95.5</v>
+        <v>30.7</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>559.95</v>
+        <v>-453.3</v>
       </c>
       <c r="K41" t="n">
-        <v>-151.35</v>
+        <v>32.21</v>
       </c>
       <c r="L41" t="n">
-        <v>580.04</v>
+        <v>454.45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09:27:34</t>
+          <t>09:24:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.95</v>
+        <v>6.84</v>
       </c>
       <c r="F42" t="n">
-        <v>11.44</v>
+        <v>16.58</v>
       </c>
       <c r="G42" t="n">
-        <v>277.8</v>
+        <v>278.2</v>
       </c>
       <c r="H42" t="n">
-        <v>99.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-145.15</v>
+        <v>-247.21</v>
       </c>
       <c r="K42" t="n">
-        <v>344.42</v>
+        <v>-254.53</v>
       </c>
       <c r="L42" t="n">
-        <v>373.76</v>
+        <v>354.83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09:28:37</t>
+          <t>09:26:02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.91</v>
+        <v>6.34</v>
       </c>
       <c r="F43" t="n">
-        <v>15.58</v>
+        <v>16.51</v>
       </c>
       <c r="G43" t="n">
-        <v>278.4</v>
+        <v>281.5</v>
       </c>
       <c r="H43" t="n">
-        <v>87.8</v>
+        <v>44.9</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-734.1900000000001</v>
+        <v>214.78</v>
       </c>
       <c r="K43" t="n">
-        <v>99.17</v>
+        <v>-229.2</v>
       </c>
       <c r="L43" t="n">
-        <v>740.86</v>
+        <v>314.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:37:58</t>
+          <t>09:36:33</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.96</v>
+        <v>6.94</v>
       </c>
       <c r="F44" t="n">
-        <v>13.76</v>
+        <v>16.79</v>
       </c>
       <c r="G44" t="n">
-        <v>288.7</v>
+        <v>283.2</v>
       </c>
       <c r="H44" t="n">
-        <v>95.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-91.65000000000001</v>
+        <v>-125.01</v>
       </c>
       <c r="K44" t="n">
-        <v>0.26</v>
+        <v>54.43</v>
       </c>
       <c r="L44" t="n">
-        <v>91.65000000000001</v>
+        <v>136.35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:39:50</t>
+          <t>09:39:11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.95</v>
+        <v>5.82</v>
       </c>
       <c r="F45" t="n">
-        <v>16.79</v>
+        <v>14.85</v>
       </c>
       <c r="G45" t="n">
-        <v>285.8</v>
+        <v>277.6</v>
       </c>
       <c r="H45" t="n">
-        <v>97.7</v>
+        <v>41.2</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>110.72</v>
+        <v>-133.27</v>
       </c>
       <c r="K45" t="n">
-        <v>-23.92</v>
+        <v>72</v>
       </c>
       <c r="L45" t="n">
-        <v>113.27</v>
+        <v>151.48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:41:30</t>
+          <t>09:41:05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.48</v>
+        <v>6.79</v>
       </c>
       <c r="F46" t="n">
-        <v>13.43</v>
+        <v>16.79</v>
       </c>
       <c r="G46" t="n">
-        <v>280.5</v>
+        <v>284.2</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J46" t="n">
-        <v>-92.72</v>
+        <v>-141.81</v>
       </c>
       <c r="K46" t="n">
-        <v>-89.09999999999999</v>
+        <v>46.21</v>
       </c>
       <c r="L46" t="n">
-        <v>128.6</v>
+        <v>149.15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:46:28</t>
+          <t>09:47:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.8</v>
+        <v>5.82</v>
       </c>
       <c r="F47" t="n">
-        <v>14.34</v>
+        <v>16.71</v>
       </c>
       <c r="G47" t="n">
-        <v>292.5</v>
+        <v>285.3</v>
       </c>
       <c r="H47" t="n">
-        <v>92.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-76.92</v>
+        <v>-158.99</v>
       </c>
       <c r="K47" t="n">
-        <v>92.04000000000001</v>
+        <v>-127.74</v>
       </c>
       <c r="L47" t="n">
-        <v>119.95</v>
+        <v>203.95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:47:52</t>
+          <t>09:49:05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>6.03</v>
+        <v>5.44</v>
       </c>
       <c r="F48" t="n">
-        <v>15.66</v>
+        <v>14.91</v>
       </c>
       <c r="G48" t="n">
-        <v>276.1</v>
+        <v>277.2</v>
       </c>
       <c r="H48" t="n">
-        <v>98.09999999999999</v>
+        <v>29.7</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>188.82</v>
+        <v>-176.73</v>
       </c>
       <c r="K48" t="n">
-        <v>16.01</v>
+        <v>41.65</v>
       </c>
       <c r="L48" t="n">
-        <v>189.49</v>
+        <v>181.57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:49:20</t>
+          <t>09:51:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6.94</v>
+        <v>5.35</v>
       </c>
       <c r="F49" t="n">
-        <v>15.7</v>
+        <v>14.76</v>
       </c>
       <c r="G49" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="H49" t="n">
-        <v>99.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-105.56</v>
+        <v>94.97</v>
       </c>
       <c r="K49" t="n">
-        <v>46.82</v>
+        <v>107.24</v>
       </c>
       <c r="L49" t="n">
-        <v>115.47</v>
+        <v>143.25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:53:18</t>
+          <t>09:56:57</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>6.21</v>
+        <v>5.96</v>
       </c>
       <c r="F50" t="n">
-        <v>14.72</v>
+        <v>16.79</v>
       </c>
       <c r="G50" t="n">
-        <v>292.4</v>
+        <v>280.4</v>
       </c>
       <c r="H50" t="n">
-        <v>93.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J50" t="n">
-        <v>-300.37</v>
+        <v>-181.87</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.5</v>
+        <v>-182.01</v>
       </c>
       <c r="L50" t="n">
-        <v>300.37</v>
+        <v>257.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:55:01</t>
+          <t>09:59:05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>7.32</v>
+        <v>6.25</v>
       </c>
       <c r="F51" t="n">
-        <v>16.79</v>
+        <v>16.61</v>
       </c>
       <c r="G51" t="n">
-        <v>269.1</v>
+        <v>283.2</v>
       </c>
       <c r="H51" t="n">
-        <v>98.2</v>
+        <v>46.3</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.3</v>
+        <v>-86.51000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>299.68</v>
+        <v>272.17</v>
       </c>
       <c r="L51" t="n">
-        <v>299.68</v>
+        <v>285.59</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:56:16</t>
+          <t>10:00:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="F52" t="n">
-        <v>14.62</v>
+        <v>14.33</v>
       </c>
       <c r="G52" t="n">
-        <v>289.2</v>
+        <v>285</v>
       </c>
       <c r="H52" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>90.13</v>
+        <v>-216.14</v>
       </c>
       <c r="K52" t="n">
-        <v>190.38</v>
+        <v>-111.63</v>
       </c>
       <c r="L52" t="n">
-        <v>210.64</v>
+        <v>243.26</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:04:54</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6.32</v>
+        <v>6.73</v>
       </c>
       <c r="F53" t="n">
-        <v>16.32</v>
+        <v>16.79</v>
       </c>
       <c r="G53" t="n">
-        <v>268.7</v>
+        <v>279.6</v>
       </c>
       <c r="H53" t="n">
-        <v>93.90000000000001</v>
+        <v>52.6</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-110.03</v>
+        <v>-391.96</v>
       </c>
       <c r="K53" t="n">
-        <v>-439.47</v>
+        <v>-100.79</v>
       </c>
       <c r="L53" t="n">
-        <v>453.04</v>
+        <v>404.71</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10:03:38</t>
+          <t>10:07:13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.31</v>
+        <v>6.19</v>
       </c>
       <c r="F54" t="n">
-        <v>13.82</v>
+        <v>14.53</v>
       </c>
       <c r="G54" t="n">
-        <v>264.2</v>
+        <v>296</v>
       </c>
       <c r="H54" t="n">
-        <v>94.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-304.59</v>
+        <v>-153.64</v>
       </c>
       <c r="K54" t="n">
-        <v>-142.58</v>
+        <v>-402.49</v>
       </c>
       <c r="L54" t="n">
-        <v>336.31</v>
+        <v>430.82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10:04:48</t>
+          <t>10:08:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.66</v>
+        <v>6.43</v>
       </c>
       <c r="F55" t="n">
-        <v>15.58</v>
+        <v>15.05</v>
       </c>
       <c r="G55" t="n">
-        <v>284.6</v>
+        <v>279.5</v>
       </c>
       <c r="H55" t="n">
-        <v>93.3</v>
+        <v>61.5</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.03</v>
+        <v>-214.02</v>
       </c>
       <c r="K55" t="n">
-        <v>-213.75</v>
+        <v>326.14</v>
       </c>
       <c r="L55" t="n">
-        <v>213.77</v>
+        <v>390.09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10:08:55</t>
+          <t>10:14:16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>6.52</v>
+        <v>6.74</v>
       </c>
       <c r="F56" t="n">
-        <v>16.37</v>
+        <v>16.79</v>
       </c>
       <c r="G56" t="n">
-        <v>281.2</v>
+        <v>305.9</v>
       </c>
       <c r="H56" t="n">
-        <v>87.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-358.17</v>
+        <v>-326.25</v>
       </c>
       <c r="K56" t="n">
-        <v>-204.21</v>
+        <v>164.57</v>
       </c>
       <c r="L56" t="n">
-        <v>412.29</v>
+        <v>365.41</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10:10:26</t>
+          <t>10:16:05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>6.01</v>
+        <v>6.6</v>
       </c>
       <c r="F57" t="n">
-        <v>16.79</v>
+        <v>15.66</v>
       </c>
       <c r="G57" t="n">
-        <v>283.5</v>
+        <v>289</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-289.49</v>
+        <v>-334.03</v>
       </c>
       <c r="K57" t="n">
-        <v>360.03</v>
+        <v>206.84</v>
       </c>
       <c r="L57" t="n">
-        <v>461.98</v>
+        <v>392.88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10:11:51</t>
+          <t>10:18:20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.81</v>
+        <v>6.44</v>
       </c>
       <c r="F58" t="n">
-        <v>15.4</v>
+        <v>16.79</v>
       </c>
       <c r="G58" t="n">
-        <v>287.2</v>
+        <v>273.1</v>
       </c>
       <c r="H58" t="n">
-        <v>98.90000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>446.17</v>
+        <v>-427.55</v>
       </c>
       <c r="K58" t="n">
-        <v>627.47</v>
+        <v>91.28</v>
       </c>
       <c r="L58" t="n">
-        <v>769.92</v>
+        <v>437.19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10:20:44</t>
+          <t>10:28:20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6.77</v>
+        <v>6.82</v>
       </c>
       <c r="F59" t="n">
-        <v>16.26</v>
+        <v>16.79</v>
       </c>
       <c r="G59" t="n">
-        <v>267</v>
+        <v>283.7</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>32.9</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>-21.33</v>
+        <v>32.29</v>
       </c>
       <c r="K59" t="n">
-        <v>-113.15</v>
+        <v>-176.08</v>
       </c>
       <c r="L59" t="n">
-        <v>115.14</v>
+        <v>179.02</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10:22:14</t>
+          <t>10:29:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.57</v>
+        <v>6.14</v>
       </c>
       <c r="F60" t="n">
-        <v>16.79</v>
+        <v>14.51</v>
       </c>
       <c r="G60" t="n">
-        <v>296.9</v>
+        <v>295.3</v>
       </c>
       <c r="H60" t="n">
-        <v>91.3</v>
+        <v>81.3</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>66.43000000000001</v>
+        <v>-108.59</v>
       </c>
       <c r="K60" t="n">
-        <v>-90.37</v>
+        <v>35.37</v>
       </c>
       <c r="L60" t="n">
-        <v>112.16</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:23:20</t>
+          <t>10:31:31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>7.07</v>
+        <v>5.51</v>
       </c>
       <c r="F61" t="n">
-        <v>16.79</v>
+        <v>14.72</v>
       </c>
       <c r="G61" t="n">
-        <v>272.3</v>
+        <v>282.6</v>
       </c>
       <c r="H61" t="n">
-        <v>97.59999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-79.65000000000001</v>
+        <v>31.11</v>
       </c>
       <c r="K61" t="n">
-        <v>49.16</v>
+        <v>-129.41</v>
       </c>
       <c r="L61" t="n">
-        <v>93.59999999999999</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:28:14</t>
+          <t>10:36:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>7.17</v>
+        <v>6.82</v>
       </c>
       <c r="F62" t="n">
         <v>16.79</v>
       </c>
       <c r="G62" t="n">
-        <v>290.7</v>
+        <v>279.9</v>
       </c>
       <c r="H62" t="n">
-        <v>96.7</v>
+        <v>52</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-92.61</v>
+        <v>-116.91</v>
       </c>
       <c r="K62" t="n">
-        <v>38.31</v>
+        <v>178.14</v>
       </c>
       <c r="L62" t="n">
-        <v>100.22</v>
+        <v>213.08</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:30:06</t>
+          <t>10:38:08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>6.34</v>
+        <v>6.21</v>
       </c>
       <c r="F63" t="n">
-        <v>16.49</v>
+        <v>16.79</v>
       </c>
       <c r="G63" t="n">
-        <v>274.1</v>
+        <v>288.6</v>
       </c>
       <c r="H63" t="n">
-        <v>93.90000000000001</v>
+        <v>59.1</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>28.62</v>
+        <v>9.44</v>
       </c>
       <c r="K63" t="n">
-        <v>150.85</v>
+        <v>201.5</v>
       </c>
       <c r="L63" t="n">
-        <v>153.54</v>
+        <v>201.72</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:31:17</t>
+          <t>10:39:51</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.57</v>
+        <v>6.83</v>
       </c>
       <c r="F64" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="G64" t="n">
-        <v>287.6</v>
+        <v>281.1</v>
       </c>
       <c r="H64" t="n">
-        <v>95.7</v>
+        <v>27.3</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-130.08</v>
+        <v>-171.78</v>
       </c>
       <c r="K64" t="n">
-        <v>-55.12</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>141.28</v>
+        <v>183.61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:34:23</t>
+          <t>10:44:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6.43</v>
+        <v>5.58</v>
       </c>
       <c r="F65" t="n">
-        <v>15.04</v>
+        <v>15.15</v>
       </c>
       <c r="G65" t="n">
-        <v>279.6</v>
+        <v>277.7</v>
       </c>
       <c r="H65" t="n">
-        <v>96.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-199.03</v>
+        <v>-201.14</v>
       </c>
       <c r="K65" t="n">
-        <v>36.54</v>
+        <v>27.15</v>
       </c>
       <c r="L65" t="n">
-        <v>202.36</v>
+        <v>202.96</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:35:29</t>
+          <t>10:46:51</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>6.95</v>
+        <v>6.32</v>
       </c>
       <c r="F66" t="n">
-        <v>16.79</v>
+        <v>16.63</v>
       </c>
       <c r="G66" t="n">
-        <v>265.7</v>
+        <v>295.7</v>
       </c>
       <c r="H66" t="n">
-        <v>94.8</v>
+        <v>54.7</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>31.31</v>
+        <v>-33.38</v>
       </c>
       <c r="K66" t="n">
-        <v>242.76</v>
+        <v>208.31</v>
       </c>
       <c r="L66" t="n">
-        <v>244.77</v>
+        <v>210.97</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:36:56</t>
+          <t>10:47:59</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.6</v>
+        <v>6.54</v>
       </c>
       <c r="F67" t="n">
-        <v>15.29</v>
+        <v>16.79</v>
       </c>
       <c r="G67" t="n">
-        <v>288.2</v>
+        <v>282</v>
       </c>
       <c r="H67" t="n">
-        <v>96.2</v>
+        <v>78.8</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-34.46</v>
+        <v>-244.75</v>
       </c>
       <c r="K67" t="n">
-        <v>-195.42</v>
+        <v>-137.64</v>
       </c>
       <c r="L67" t="n">
-        <v>198.43</v>
+        <v>280.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:40:37</t>
+          <t>10:52:25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>7.09</v>
+        <v>7.24</v>
       </c>
       <c r="F68" t="n">
         <v>16.79</v>
       </c>
       <c r="G68" t="n">
-        <v>286.3</v>
+        <v>281.8</v>
       </c>
       <c r="H68" t="n">
-        <v>90.5</v>
+        <v>69.5</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-416.81</v>
+        <v>-233.22</v>
       </c>
       <c r="K68" t="n">
-        <v>-118.1</v>
+        <v>-296.62</v>
       </c>
       <c r="L68" t="n">
-        <v>433.22</v>
+        <v>377.33</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:41:38</t>
+          <t>10:54:13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>6.1</v>
+        <v>7.19</v>
       </c>
       <c r="F69" t="n">
-        <v>13.58</v>
+        <v>16.79</v>
       </c>
       <c r="G69" t="n">
-        <v>282.6</v>
+        <v>294.4</v>
       </c>
       <c r="H69" t="n">
-        <v>94</v>
+        <v>54.5</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J69" t="n">
-        <v>-67.45</v>
+        <v>-263.51</v>
       </c>
       <c r="K69" t="n">
-        <v>-287.47</v>
+        <v>-174.86</v>
       </c>
       <c r="L69" t="n">
-        <v>295.28</v>
+        <v>316.25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:43:56</t>
+          <t>10:55:24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.96</v>
+        <v>5.98</v>
       </c>
       <c r="F70" t="n">
         <v>16.79</v>
       </c>
       <c r="G70" t="n">
-        <v>280.3</v>
+        <v>277.6</v>
       </c>
       <c r="H70" t="n">
-        <v>98.2</v>
+        <v>90.2</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J70" t="n">
-        <v>339.3</v>
+        <v>-89.43000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>-180.66</v>
+        <v>-325</v>
       </c>
       <c r="L70" t="n">
-        <v>384.4</v>
+        <v>337.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:47:57</t>
+          <t>11:00:18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.91</v>
+        <v>7.08</v>
       </c>
       <c r="F71" t="n">
         <v>16.79</v>
       </c>
       <c r="G71" t="n">
-        <v>273.9</v>
+        <v>276.6</v>
       </c>
       <c r="H71" t="n">
-        <v>96.5</v>
+        <v>31.3</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-626.3200000000001</v>
+        <v>-473.85</v>
       </c>
       <c r="K71" t="n">
-        <v>-108.16</v>
+        <v>48.88</v>
       </c>
       <c r="L71" t="n">
-        <v>635.59</v>
+        <v>476.36</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:50:05</t>
+          <t>11:02:05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>7.12</v>
+        <v>5.75</v>
       </c>
       <c r="F72" t="n">
-        <v>16.79</v>
+        <v>13.84</v>
       </c>
       <c r="G72" t="n">
-        <v>285.1</v>
+        <v>268.1</v>
       </c>
       <c r="H72" t="n">
-        <v>94.40000000000001</v>
+        <v>49.8</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-495.28</v>
+        <v>255.92</v>
       </c>
       <c r="K72" t="n">
-        <v>-541.26</v>
+        <v>230.81</v>
       </c>
       <c r="L72" t="n">
-        <v>733.66</v>
+        <v>344.63</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:52:15</t>
+          <t>11:03:56</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>6.47</v>
+        <v>7</v>
       </c>
       <c r="F73" t="n">
         <v>16.79</v>
       </c>
       <c r="G73" t="n">
-        <v>282.4</v>
+        <v>293</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-451.63</v>
+        <v>-474.95</v>
       </c>
       <c r="K73" t="n">
-        <v>511.59</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>682.42</v>
+        <v>479.83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11:04:57</t>
+          <t>11:10:28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.82</v>
+        <v>6.35</v>
       </c>
       <c r="F74" t="n">
-        <v>16.79</v>
+        <v>14.77</v>
       </c>
       <c r="G74" t="n">
-        <v>289.3</v>
+        <v>297.7</v>
       </c>
       <c r="H74" t="n">
-        <v>99.90000000000001</v>
+        <v>32.8</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.97</v>
+        <v>-124.45</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.98</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>8.449999999999999</v>
+        <v>149.33</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11:06:53</t>
+          <t>11:11:55</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.47</v>
+        <v>6.43</v>
       </c>
       <c r="F75" t="n">
         <v>16.79</v>
       </c>
       <c r="G75" t="n">
-        <v>278.9</v>
+        <v>263.4</v>
       </c>
       <c r="H75" t="n">
-        <v>94</v>
+        <v>67.3</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-115.09</v>
+        <v>9.01</v>
       </c>
       <c r="K75" t="n">
-        <v>-43.89</v>
+        <v>150.92</v>
       </c>
       <c r="L75" t="n">
-        <v>123.18</v>
+        <v>151.19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:08:39</t>
+          <t>11:13:51</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.65</v>
+        <v>7.79</v>
       </c>
       <c r="F76" t="n">
         <v>16.79</v>
       </c>
       <c r="G76" t="n">
-        <v>286</v>
+        <v>274.6</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I76" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>63.15</v>
+        <v>-154.74</v>
       </c>
       <c r="K76" t="n">
-        <v>-109.72</v>
+        <v>-23.42</v>
       </c>
       <c r="L76" t="n">
-        <v>126.6</v>
+        <v>156.51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11:12:19</t>
+          <t>11:19:24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.77</v>
+        <v>7.34</v>
       </c>
       <c r="F77" t="n">
-        <v>16.09</v>
+        <v>16.79</v>
       </c>
       <c r="G77" t="n">
-        <v>293.5</v>
+        <v>280.7</v>
       </c>
       <c r="H77" t="n">
-        <v>92.09999999999999</v>
+        <v>57</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-51.97</v>
+        <v>-258.72</v>
       </c>
       <c r="K77" t="n">
-        <v>84.25</v>
+        <v>8.98</v>
       </c>
       <c r="L77" t="n">
-        <v>98.98999999999999</v>
+        <v>258.88</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11:15:04</t>
+          <t>11:21:34</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.74</v>
+        <v>6.29</v>
       </c>
       <c r="F78" t="n">
-        <v>16.79</v>
+        <v>15.27</v>
       </c>
       <c r="G78" t="n">
-        <v>279.8</v>
+        <v>283.3</v>
       </c>
       <c r="H78" t="n">
-        <v>96.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>17.13</v>
+        <v>-117.42</v>
       </c>
       <c r="K78" t="n">
-        <v>114.9</v>
+        <v>-139.92</v>
       </c>
       <c r="L78" t="n">
-        <v>116.17</v>
+        <v>182.66</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11:16:57</t>
+          <t>11:22:25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>7.09</v>
+        <v>6.71</v>
       </c>
       <c r="F79" t="n">
         <v>16.79</v>
       </c>
       <c r="G79" t="n">
-        <v>266.2</v>
+        <v>276.2</v>
       </c>
       <c r="H79" t="n">
-        <v>95.8</v>
+        <v>62.6</v>
       </c>
       <c r="I79" t="n">
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>-116.06</v>
+        <v>-184.95</v>
       </c>
       <c r="K79" t="n">
-        <v>-123.92</v>
+        <v>-31.23</v>
       </c>
       <c r="L79" t="n">
-        <v>169.78</v>
+        <v>187.57</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11:20:45</t>
+          <t>11:28:23</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.08</v>
+        <v>6.3</v>
       </c>
       <c r="F80" t="n">
-        <v>16.79</v>
+        <v>14.45</v>
       </c>
       <c r="G80" t="n">
-        <v>277.7</v>
+        <v>290.5</v>
       </c>
       <c r="H80" t="n">
-        <v>91.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>82.05</v>
+        <v>-19.99</v>
       </c>
       <c r="K80" t="n">
-        <v>157.49</v>
+        <v>268.24</v>
       </c>
       <c r="L80" t="n">
-        <v>177.58</v>
+        <v>268.98</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11:22:48</t>
+          <t>11:30:02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.17</v>
+        <v>6.59</v>
       </c>
       <c r="F81" t="n">
-        <v>16</v>
+        <v>16.63</v>
       </c>
       <c r="G81" t="n">
-        <v>277.1</v>
+        <v>279.9</v>
       </c>
       <c r="H81" t="n">
-        <v>95.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>2.81</v>
+        <v>-155.73</v>
       </c>
       <c r="K81" t="n">
-        <v>-185.9</v>
+        <v>226.89</v>
       </c>
       <c r="L81" t="n">
-        <v>185.92</v>
+        <v>275.19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11:23:32</t>
+          <t>11:30:43</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.95</v>
+        <v>6.56</v>
       </c>
       <c r="F82" t="n">
-        <v>16.79</v>
+        <v>16.41</v>
       </c>
       <c r="G82" t="n">
-        <v>281.5</v>
+        <v>294.9</v>
       </c>
       <c r="H82" t="n">
-        <v>98.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-90.59</v>
+        <v>-359.3</v>
       </c>
       <c r="K82" t="n">
-        <v>186</v>
+        <v>-91.55</v>
       </c>
       <c r="L82" t="n">
-        <v>206.89</v>
+        <v>370.78</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:27:31</t>
+          <t>11:35:25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.64</v>
+        <v>7.3</v>
       </c>
       <c r="F83" t="n">
         <v>16.79</v>
       </c>
       <c r="G83" t="n">
-        <v>296.8</v>
+        <v>277.8</v>
       </c>
       <c r="H83" t="n">
-        <v>98.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>72.04000000000001</v>
+        <v>-151.75</v>
       </c>
       <c r="K83" t="n">
-        <v>188.5</v>
+        <v>-366.9</v>
       </c>
       <c r="L83" t="n">
-        <v>201.8</v>
+        <v>397.04</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:29:04</t>
+          <t>11:37:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.87</v>
+        <v>7.57</v>
       </c>
       <c r="F84" t="n">
         <v>16.79</v>
       </c>
       <c r="G84" t="n">
-        <v>295.9</v>
+        <v>271.9</v>
       </c>
       <c r="H84" t="n">
-        <v>91.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>201.88</v>
+        <v>-376.39</v>
       </c>
       <c r="K84" t="n">
-        <v>246.09</v>
+        <v>-117.68</v>
       </c>
       <c r="L84" t="n">
-        <v>318.3</v>
+        <v>394.36</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:30:23</t>
+          <t>11:39:43</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>7.08</v>
+        <v>8.35</v>
       </c>
       <c r="F85" t="n">
         <v>16.79</v>
       </c>
       <c r="G85" t="n">
-        <v>304.6</v>
+        <v>269.5</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-280.42</v>
+        <v>-220.83</v>
       </c>
       <c r="K85" t="n">
-        <v>-274.23</v>
+        <v>-285.35</v>
       </c>
       <c r="L85" t="n">
-        <v>392.22</v>
+        <v>360.82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:35:01</t>
+          <t>11:44:21</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.21</v>
+        <v>7.37</v>
       </c>
       <c r="F86" t="n">
-        <v>12.71</v>
+        <v>16.79</v>
       </c>
       <c r="G86" t="n">
-        <v>288.9</v>
+        <v>293.9</v>
       </c>
       <c r="H86" t="n">
-        <v>92.8</v>
+        <v>55.9</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-242.2</v>
+        <v>-329.78</v>
       </c>
       <c r="K86" t="n">
-        <v>-567.39</v>
+        <v>-239.6</v>
       </c>
       <c r="L86" t="n">
-        <v>616.92</v>
+        <v>407.63</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:36:38</t>
+          <t>11:46:24</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>7.13</v>
+        <v>6.55</v>
       </c>
       <c r="F87" t="n">
         <v>16.79</v>
       </c>
       <c r="G87" t="n">
-        <v>286.7</v>
+        <v>286.2</v>
       </c>
       <c r="H87" t="n">
-        <v>93.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J87" t="n">
-        <v>-164.8</v>
+        <v>-181.22</v>
       </c>
       <c r="K87" t="n">
-        <v>689.92</v>
+        <v>-430.61</v>
       </c>
       <c r="L87" t="n">
-        <v>709.33</v>
+        <v>467.19</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:38:12</t>
+          <t>11:47:38</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.71</v>
+        <v>6.2</v>
       </c>
       <c r="F88" t="n">
-        <v>16.79</v>
+        <v>15.61</v>
       </c>
       <c r="G88" t="n">
-        <v>287</v>
+        <v>280.2</v>
       </c>
       <c r="H88" t="n">
-        <v>90.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>191.1</v>
+        <v>-138.52</v>
       </c>
       <c r="K88" t="n">
-        <v>348.06</v>
+        <v>-411.42</v>
       </c>
       <c r="L88" t="n">
-        <v>397.07</v>
+        <v>434.11</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5.12</v>
+        <v>5.38</v>
       </c>
       <c r="F14" t="n">
-        <v>14.15</v>
+        <v>11.25</v>
       </c>
       <c r="G14" t="n">
-        <v>282.5</v>
+        <v>277.4</v>
       </c>
       <c r="H14" t="n">
-        <v>54.1</v>
+        <v>56.7</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-49.54</v>
+        <v>-42.7</v>
       </c>
       <c r="K14" t="n">
-        <v>86.58</v>
+        <v>121.16</v>
       </c>
       <c r="L14" t="n">
-        <v>99.75</v>
+        <v>128.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:06:42</t>
+          <t>08:07:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.42</v>
+        <v>4.48</v>
       </c>
       <c r="F15" t="n">
-        <v>11.12</v>
+        <v>6.84</v>
       </c>
       <c r="G15" t="n">
-        <v>282.2</v>
+        <v>294.2</v>
       </c>
       <c r="H15" t="n">
-        <v>47.2</v>
+        <v>75.2</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>47.26</v>
+        <v>-99.70999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>61.16</v>
+        <v>-34.11</v>
       </c>
       <c r="L15" t="n">
-        <v>77.29000000000001</v>
+        <v>105.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:08:52</t>
+          <t>08:07:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.25</v>
+        <v>5.85</v>
       </c>
       <c r="F16" t="n">
-        <v>10.2</v>
+        <v>14.46</v>
       </c>
       <c r="G16" t="n">
-        <v>272.9</v>
+        <v>267.4</v>
       </c>
       <c r="H16" t="n">
-        <v>58.8</v>
+        <v>54.5</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>22.9</v>
+        <v>40.08</v>
       </c>
       <c r="K16" t="n">
-        <v>115.08</v>
+        <v>-126.36</v>
       </c>
       <c r="L16" t="n">
-        <v>117.34</v>
+        <v>132.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:14:16</t>
+          <t>08:11:42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>6.73</v>
+        <v>4.54</v>
       </c>
       <c r="F17" t="n">
-        <v>15.94</v>
+        <v>9.92</v>
       </c>
       <c r="G17" t="n">
-        <v>284.4</v>
+        <v>292.4</v>
       </c>
       <c r="H17" t="n">
-        <v>49.9</v>
+        <v>41.8</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>-324.35</v>
+        <v>69.14</v>
       </c>
       <c r="K17" t="n">
-        <v>0.53</v>
+        <v>55.82</v>
       </c>
       <c r="L17" t="n">
-        <v>324.35</v>
+        <v>88.86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:15:34</t>
+          <t>08:13:16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.05</v>
+        <v>5.06</v>
       </c>
       <c r="F18" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="G18" t="n">
-        <v>283.2</v>
+        <v>275.3</v>
       </c>
       <c r="H18" t="n">
-        <v>52.5</v>
+        <v>43.5</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-51.88</v>
+        <v>-50.55</v>
       </c>
       <c r="K18" t="n">
-        <v>187.29</v>
+        <v>115.24</v>
       </c>
       <c r="L18" t="n">
-        <v>194.34</v>
+        <v>125.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:16:34</t>
+          <t>08:14:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.37</v>
+        <v>4.87</v>
       </c>
       <c r="F19" t="n">
-        <v>12.73</v>
+        <v>11.99</v>
       </c>
       <c r="G19" t="n">
-        <v>265.5</v>
+        <v>281.3</v>
       </c>
       <c r="H19" t="n">
-        <v>84.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>19.88</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-121.43</v>
+        <v>144.61</v>
       </c>
       <c r="L19" t="n">
-        <v>123.05</v>
+        <v>163.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:20:45</t>
+          <t>08:18:50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.91</v>
+        <v>4.89</v>
       </c>
       <c r="F20" t="n">
-        <v>12.65</v>
+        <v>10.94</v>
       </c>
       <c r="G20" t="n">
-        <v>292.9</v>
+        <v>271.1</v>
       </c>
       <c r="H20" t="n">
-        <v>79.2</v>
+        <v>67.3</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J20" t="n">
-        <v>-216.95</v>
+        <v>-231.6</v>
       </c>
       <c r="K20" t="n">
-        <v>18.98</v>
+        <v>-61.27</v>
       </c>
       <c r="L20" t="n">
-        <v>217.78</v>
+        <v>239.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:22:47</t>
+          <t>08:21:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.95</v>
+        <v>5.37</v>
       </c>
       <c r="F21" t="n">
-        <v>13.43</v>
+        <v>13.56</v>
       </c>
       <c r="G21" t="n">
-        <v>272.5</v>
+        <v>275.9</v>
       </c>
       <c r="H21" t="n">
-        <v>95.3</v>
+        <v>81</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J21" t="n">
-        <v>-114.31</v>
+        <v>-188.51</v>
       </c>
       <c r="K21" t="n">
-        <v>237.53</v>
+        <v>-42.64</v>
       </c>
       <c r="L21" t="n">
-        <v>263.61</v>
+        <v>193.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:23:38</t>
+          <t>08:23:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,28 +961,28 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.34</v>
+        <v>5.25</v>
       </c>
       <c r="F22" t="n">
-        <v>14.13</v>
+        <v>11.67</v>
       </c>
       <c r="G22" t="n">
-        <v>285.5</v>
+        <v>285.6</v>
       </c>
       <c r="H22" t="n">
-        <v>60.9</v>
+        <v>48.7</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>178.01</v>
+        <v>-171.53</v>
       </c>
       <c r="K22" t="n">
-        <v>-49.62</v>
+        <v>183.59</v>
       </c>
       <c r="L22" t="n">
-        <v>184.8</v>
+        <v>251.25</v>
       </c>
     </row>
     <row r="23">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.63</v>
+        <v>5.71</v>
       </c>
       <c r="F23" t="n">
-        <v>13.76</v>
+        <v>12.7</v>
       </c>
       <c r="G23" t="n">
-        <v>281.8</v>
+        <v>274.6</v>
       </c>
       <c r="H23" t="n">
-        <v>27.1</v>
+        <v>67.8</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-87.59</v>
+        <v>-314.67</v>
       </c>
       <c r="K23" t="n">
-        <v>238.08</v>
+        <v>276.36</v>
       </c>
       <c r="L23" t="n">
-        <v>253.68</v>
+        <v>418.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:30:41</t>
+          <t>08:31:20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>6.11</v>
+        <v>5.07</v>
       </c>
       <c r="F24" t="n">
-        <v>16.79</v>
+        <v>16.48</v>
       </c>
       <c r="G24" t="n">
-        <v>294.3</v>
+        <v>292.7</v>
       </c>
       <c r="H24" t="n">
-        <v>79.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>-216</v>
+        <v>203.1</v>
       </c>
       <c r="K24" t="n">
-        <v>276.8</v>
+        <v>243.64</v>
       </c>
       <c r="L24" t="n">
-        <v>351.11</v>
+        <v>317.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:32:43</t>
+          <t>08:33:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.9</v>
+        <v>5.89</v>
       </c>
       <c r="F25" t="n">
-        <v>14.42</v>
+        <v>13.64</v>
       </c>
       <c r="G25" t="n">
-        <v>279.9</v>
+        <v>276.1</v>
       </c>
       <c r="H25" t="n">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-260.36</v>
+        <v>254.87</v>
       </c>
       <c r="K25" t="n">
-        <v>-183.47</v>
+        <v>164.24</v>
       </c>
       <c r="L25" t="n">
-        <v>318.51</v>
+        <v>303.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:37:19</t>
+          <t>08:38:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>6.12</v>
+        <v>4.84</v>
       </c>
       <c r="F26" t="n">
-        <v>14.75</v>
+        <v>11.2</v>
       </c>
       <c r="G26" t="n">
-        <v>279.9</v>
+        <v>282.1</v>
       </c>
       <c r="H26" t="n">
-        <v>49.4</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>-450.32</v>
+        <v>-268.41</v>
       </c>
       <c r="K26" t="n">
-        <v>-91.09</v>
+        <v>266.35</v>
       </c>
       <c r="L26" t="n">
-        <v>459.44</v>
+        <v>378.13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:39:24</t>
+          <t>08:40:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>6.24</v>
+        <v>5.66</v>
       </c>
       <c r="F27" t="n">
-        <v>14.52</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>279.4</v>
+        <v>281.1</v>
       </c>
       <c r="H27" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J27" t="n">
-        <v>-537.9</v>
+        <v>221.74</v>
       </c>
       <c r="K27" t="n">
-        <v>-322.44</v>
+        <v>275.47</v>
       </c>
       <c r="L27" t="n">
-        <v>627.14</v>
+        <v>353.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:40:15</t>
+          <t>08:40:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>6.42</v>
+        <v>5.34</v>
       </c>
       <c r="F28" t="n">
-        <v>15.86</v>
+        <v>15.35</v>
       </c>
       <c r="G28" t="n">
-        <v>292.1</v>
+        <v>288.4</v>
       </c>
       <c r="H28" t="n">
-        <v>24.7</v>
+        <v>51.6</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>94.05</v>
+        <v>-398.34</v>
       </c>
       <c r="K28" t="n">
-        <v>-349.77</v>
+        <v>220.76</v>
       </c>
       <c r="L28" t="n">
-        <v>362.19</v>
+        <v>455.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:51:35</t>
+          <t>08:48:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>6.01</v>
+        <v>5.74</v>
       </c>
       <c r="F29" t="n">
         <v>16.79</v>
       </c>
       <c r="G29" t="n">
-        <v>293.1</v>
+        <v>281.8</v>
       </c>
       <c r="H29" t="n">
-        <v>80</v>
+        <v>54.8</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>-107.68</v>
+        <v>-151.91</v>
       </c>
       <c r="K29" t="n">
-        <v>16.01</v>
+        <v>12.6</v>
       </c>
       <c r="L29" t="n">
-        <v>108.87</v>
+        <v>152.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:52:12</t>
+          <t>08:49:53</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="F30" t="n">
-        <v>13.6</v>
+        <v>13.36</v>
       </c>
       <c r="G30" t="n">
-        <v>287.1</v>
+        <v>285.8</v>
       </c>
       <c r="H30" t="n">
-        <v>78</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>-92.59</v>
+        <v>76.59</v>
       </c>
       <c r="K30" t="n">
-        <v>78.59999999999999</v>
+        <v>-119.26</v>
       </c>
       <c r="L30" t="n">
-        <v>121.45</v>
+        <v>141.73</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:53:47</t>
+          <t>08:51:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>6.13</v>
+        <v>5.57</v>
       </c>
       <c r="F31" t="n">
-        <v>16.79</v>
+        <v>11.92</v>
       </c>
       <c r="G31" t="n">
-        <v>286.4</v>
+        <v>295.1</v>
       </c>
       <c r="H31" t="n">
-        <v>67</v>
+        <v>11.9</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>0.83</v>
+        <v>-159.4</v>
       </c>
       <c r="K31" t="n">
-        <v>-107.28</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>107.29</v>
+        <v>185.18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:59:28</t>
+          <t>08:56:02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5.45</v>
+        <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>13.92</v>
+        <v>14.36</v>
       </c>
       <c r="G32" t="n">
-        <v>273.2</v>
+        <v>294.9</v>
       </c>
       <c r="H32" t="n">
-        <v>69.8</v>
+        <v>8.4</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-111.44</v>
+        <v>-216.63</v>
       </c>
       <c r="K32" t="n">
-        <v>71.84</v>
+        <v>-53.95</v>
       </c>
       <c r="L32" t="n">
-        <v>132.59</v>
+        <v>223.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09:00:46</t>
+          <t>08:57:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.38</v>
+        <v>5.49</v>
       </c>
       <c r="F33" t="n">
-        <v>15.62</v>
+        <v>14.27</v>
       </c>
       <c r="G33" t="n">
-        <v>289.6</v>
+        <v>285.2</v>
       </c>
       <c r="H33" t="n">
-        <v>72.59999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-118.75</v>
+        <v>161.22</v>
       </c>
       <c r="K33" t="n">
-        <v>-46.38</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>127.49</v>
+        <v>173.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09:02:38</t>
+          <t>08:59:03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>6.04</v>
+        <v>5.74</v>
       </c>
       <c r="F34" t="n">
-        <v>15.24</v>
+        <v>16.31</v>
       </c>
       <c r="G34" t="n">
-        <v>291</v>
+        <v>274.8</v>
       </c>
       <c r="H34" t="n">
-        <v>75.90000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>-178.4</v>
+        <v>-10.08</v>
       </c>
       <c r="K34" t="n">
-        <v>2.78</v>
+        <v>-140.77</v>
       </c>
       <c r="L34" t="n">
-        <v>178.43</v>
+        <v>141.13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09:06:37</t>
+          <t>09:03:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.82</v>
+        <v>5.49</v>
       </c>
       <c r="F35" t="n">
-        <v>15.33</v>
+        <v>14.05</v>
       </c>
       <c r="G35" t="n">
-        <v>284.4</v>
+        <v>285.9</v>
       </c>
       <c r="H35" t="n">
-        <v>63.1</v>
+        <v>46.8</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-101.27</v>
+        <v>189.44</v>
       </c>
       <c r="K35" t="n">
-        <v>209.13</v>
+        <v>133.13</v>
       </c>
       <c r="L35" t="n">
-        <v>232.37</v>
+        <v>231.54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09:08:05</t>
+          <t>09:05:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>6.49</v>
+        <v>5.23</v>
       </c>
       <c r="F36" t="n">
-        <v>14.6</v>
+        <v>14.37</v>
       </c>
       <c r="G36" t="n">
-        <v>270.6</v>
+        <v>296.6</v>
       </c>
       <c r="H36" t="n">
-        <v>61.5</v>
+        <v>59.9</v>
       </c>
       <c r="I36" t="n">
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-74.05</v>
+        <v>-224.92</v>
       </c>
       <c r="K36" t="n">
-        <v>199.57</v>
+        <v>111.54</v>
       </c>
       <c r="L36" t="n">
-        <v>212.87</v>
+        <v>251.06</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09:10:33</t>
+          <t>09:08:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1594,31 +1594,31 @@
         <v>5.6</v>
       </c>
       <c r="F37" t="n">
-        <v>14.87</v>
+        <v>14.38</v>
       </c>
       <c r="G37" t="n">
-        <v>280.2</v>
+        <v>275.1</v>
       </c>
       <c r="H37" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>106.55</v>
+        <v>-217.07</v>
       </c>
       <c r="K37" t="n">
-        <v>5.06</v>
+        <v>30.37</v>
       </c>
       <c r="L37" t="n">
-        <v>106.67</v>
+        <v>219.19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:15:29</t>
+          <t>09:14:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.93</v>
+        <v>5.38</v>
       </c>
       <c r="F38" t="n">
-        <v>16.67</v>
+        <v>16.74</v>
       </c>
       <c r="G38" t="n">
-        <v>273.6</v>
+        <v>266.3</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>47.4</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>-305.02</v>
+        <v>-327.5</v>
       </c>
       <c r="K38" t="n">
-        <v>-150.45</v>
+        <v>-135.81</v>
       </c>
       <c r="L38" t="n">
-        <v>340.11</v>
+        <v>354.55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:16:54</t>
+          <t>09:15:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6.84</v>
+        <v>5.8</v>
       </c>
       <c r="F39" t="n">
-        <v>16.79</v>
+        <v>11.4</v>
       </c>
       <c r="G39" t="n">
-        <v>278.7</v>
+        <v>269.7</v>
       </c>
       <c r="H39" t="n">
-        <v>79.40000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="I39" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-292.73</v>
+        <v>180.41</v>
       </c>
       <c r="K39" t="n">
-        <v>97.41</v>
+        <v>-26.32</v>
       </c>
       <c r="L39" t="n">
-        <v>308.52</v>
+        <v>182.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:18:12</t>
+          <t>09:17:13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>6.36</v>
+        <v>5.82</v>
       </c>
       <c r="F40" t="n">
-        <v>16.49</v>
+        <v>13.23</v>
       </c>
       <c r="G40" t="n">
-        <v>282.9</v>
+        <v>292.9</v>
       </c>
       <c r="H40" t="n">
-        <v>66.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J40" t="n">
-        <v>-213.1</v>
+        <v>-331.63</v>
       </c>
       <c r="K40" t="n">
-        <v>298.55</v>
+        <v>-12.83</v>
       </c>
       <c r="L40" t="n">
-        <v>366.8</v>
+        <v>331.88</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:22:36</t>
+          <t>09:20:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>6.21</v>
+        <v>6.43</v>
       </c>
       <c r="F41" t="n">
-        <v>16.79</v>
+        <v>15.48</v>
       </c>
       <c r="G41" t="n">
-        <v>294.2</v>
+        <v>272.5</v>
       </c>
       <c r="H41" t="n">
-        <v>30.7</v>
+        <v>95.3</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J41" t="n">
-        <v>-453.3</v>
+        <v>-79.43000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>32.21</v>
+        <v>529.78</v>
       </c>
       <c r="L41" t="n">
-        <v>454.45</v>
+        <v>535.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09:24:46</t>
+          <t>09:21:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>6.84</v>
+        <v>5.82</v>
       </c>
       <c r="F42" t="n">
-        <v>16.58</v>
+        <v>16.09</v>
       </c>
       <c r="G42" t="n">
-        <v>278.2</v>
+        <v>285.5</v>
       </c>
       <c r="H42" t="n">
-        <v>95</v>
+        <v>60.9</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-247.21</v>
+        <v>396.19</v>
       </c>
       <c r="K42" t="n">
-        <v>-254.53</v>
+        <v>-110.29</v>
       </c>
       <c r="L42" t="n">
-        <v>354.83</v>
+        <v>411.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09:26:02</t>
+          <t>09:23:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>6.34</v>
+        <v>6.07</v>
       </c>
       <c r="F43" t="n">
-        <v>16.51</v>
+        <v>15.6</v>
       </c>
       <c r="G43" t="n">
-        <v>281.5</v>
+        <v>281.8</v>
       </c>
       <c r="H43" t="n">
-        <v>44.9</v>
+        <v>27.1</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>214.78</v>
+        <v>-25.82</v>
       </c>
       <c r="K43" t="n">
-        <v>-229.2</v>
+        <v>382.24</v>
       </c>
       <c r="L43" t="n">
-        <v>314.11</v>
+        <v>383.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:36:33</t>
+          <t>09:33:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>6.94</v>
+        <v>6.62</v>
       </c>
       <c r="F44" t="n">
         <v>16.79</v>
       </c>
       <c r="G44" t="n">
-        <v>283.2</v>
+        <v>294.3</v>
       </c>
       <c r="H44" t="n">
-        <v>66.7</v>
+        <v>79.2</v>
       </c>
       <c r="I44" t="n">
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-125.01</v>
+        <v>-71.72</v>
       </c>
       <c r="K44" t="n">
-        <v>54.43</v>
+        <v>134.48</v>
       </c>
       <c r="L44" t="n">
-        <v>136.35</v>
+        <v>152.41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:39:11</t>
+          <t>09:34:21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.82</v>
+        <v>5.39</v>
       </c>
       <c r="F45" t="n">
-        <v>14.85</v>
+        <v>16.39</v>
       </c>
       <c r="G45" t="n">
-        <v>277.6</v>
+        <v>279.9</v>
       </c>
       <c r="H45" t="n">
-        <v>41.2</v>
+        <v>91</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-133.27</v>
+        <v>-96.36</v>
       </c>
       <c r="K45" t="n">
-        <v>72</v>
+        <v>-107.17</v>
       </c>
       <c r="L45" t="n">
-        <v>151.48</v>
+        <v>144.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:41:05</t>
+          <t>09:35:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.79</v>
+        <v>6.59</v>
       </c>
       <c r="F46" t="n">
-        <v>16.79</v>
+        <v>16.78</v>
       </c>
       <c r="G46" t="n">
-        <v>284.2</v>
+        <v>279.9</v>
       </c>
       <c r="H46" t="n">
-        <v>69.40000000000001</v>
+        <v>49.4</v>
       </c>
       <c r="I46" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-141.81</v>
+        <v>-145.75</v>
       </c>
       <c r="K46" t="n">
-        <v>46.21</v>
+        <v>-51.06</v>
       </c>
       <c r="L46" t="n">
-        <v>149.15</v>
+        <v>154.43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:47:01</t>
+          <t>09:40:16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.82</v>
+        <v>6.72</v>
       </c>
       <c r="F47" t="n">
-        <v>16.71</v>
+        <v>16.63</v>
       </c>
       <c r="G47" t="n">
-        <v>285.3</v>
+        <v>279.4</v>
       </c>
       <c r="H47" t="n">
-        <v>74.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-158.99</v>
+        <v>-200.75</v>
       </c>
       <c r="K47" t="n">
-        <v>-127.74</v>
+        <v>-197.84</v>
       </c>
       <c r="L47" t="n">
-        <v>203.95</v>
+        <v>281.86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:49:05</t>
+          <t>09:41:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.44</v>
+        <v>6.9</v>
       </c>
       <c r="F48" t="n">
-        <v>14.91</v>
+        <v>16.79</v>
       </c>
       <c r="G48" t="n">
-        <v>277.2</v>
+        <v>292.1</v>
       </c>
       <c r="H48" t="n">
-        <v>29.7</v>
+        <v>24.7</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-176.73</v>
+        <v>126.75</v>
       </c>
       <c r="K48" t="n">
-        <v>41.65</v>
+        <v>-191.01</v>
       </c>
       <c r="L48" t="n">
-        <v>181.57</v>
+        <v>229.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:51:26</t>
+          <t>09:44:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.35</v>
+        <v>6.42</v>
       </c>
       <c r="F49" t="n">
-        <v>14.76</v>
+        <v>16.79</v>
       </c>
       <c r="G49" t="n">
-        <v>287</v>
+        <v>293.1</v>
       </c>
       <c r="H49" t="n">
-        <v>69.2</v>
+        <v>80</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>94.97</v>
+        <v>-170.08</v>
       </c>
       <c r="K49" t="n">
-        <v>107.24</v>
+        <v>8.73</v>
       </c>
       <c r="L49" t="n">
-        <v>143.25</v>
+        <v>170.31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:56:57</t>
+          <t>09:49:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.96</v>
+        <v>5.67</v>
       </c>
       <c r="F50" t="n">
-        <v>16.79</v>
+        <v>15.4</v>
       </c>
       <c r="G50" t="n">
-        <v>280.4</v>
+        <v>287.1</v>
       </c>
       <c r="H50" t="n">
-        <v>66.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="I50" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-181.87</v>
+        <v>-180.76</v>
       </c>
       <c r="K50" t="n">
-        <v>-182.01</v>
+        <v>201.86</v>
       </c>
       <c r="L50" t="n">
-        <v>257.3</v>
+        <v>270.97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:59:05</t>
+          <t>09:51:55</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.25</v>
+        <v>6.56</v>
       </c>
       <c r="F51" t="n">
-        <v>16.61</v>
+        <v>16.79</v>
       </c>
       <c r="G51" t="n">
-        <v>283.2</v>
+        <v>286.4</v>
       </c>
       <c r="H51" t="n">
-        <v>46.3</v>
+        <v>67</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-86.51000000000001</v>
+        <v>60.77</v>
       </c>
       <c r="K51" t="n">
-        <v>272.17</v>
+        <v>-195.38</v>
       </c>
       <c r="L51" t="n">
-        <v>285.59</v>
+        <v>204.61</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10:00:45</t>
+          <t>09:53:49</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2224,31 +2224,31 @@
         <v>5.85</v>
       </c>
       <c r="F52" t="n">
-        <v>14.33</v>
+        <v>15.6</v>
       </c>
       <c r="G52" t="n">
-        <v>285</v>
+        <v>273.2</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>69.8</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-216.14</v>
+        <v>-157.42</v>
       </c>
       <c r="K52" t="n">
-        <v>-111.63</v>
+        <v>145.95</v>
       </c>
       <c r="L52" t="n">
-        <v>243.26</v>
+        <v>214.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10:04:54</t>
+          <t>09:58:25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6.73</v>
+        <v>5.8</v>
       </c>
       <c r="F53" t="n">
         <v>16.79</v>
       </c>
       <c r="G53" t="n">
-        <v>279.6</v>
+        <v>289.6</v>
       </c>
       <c r="H53" t="n">
-        <v>52.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J53" t="n">
-        <v>-391.96</v>
+        <v>-246.13</v>
       </c>
       <c r="K53" t="n">
-        <v>-100.79</v>
+        <v>-167.27</v>
       </c>
       <c r="L53" t="n">
-        <v>404.71</v>
+        <v>297.59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10:07:13</t>
+          <t>10:00:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.19</v>
+        <v>6.46</v>
       </c>
       <c r="F54" t="n">
-        <v>14.53</v>
+        <v>16.79</v>
       </c>
       <c r="G54" t="n">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="H54" t="n">
-        <v>83.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J54" t="n">
-        <v>-153.64</v>
+        <v>-360.82</v>
       </c>
       <c r="K54" t="n">
-        <v>-402.49</v>
+        <v>-41.54</v>
       </c>
       <c r="L54" t="n">
-        <v>430.82</v>
+        <v>363.21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10:08:34</t>
+          <t>10:02:13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>6.43</v>
+        <v>6.21</v>
       </c>
       <c r="F55" t="n">
-        <v>15.05</v>
+        <v>16.79</v>
       </c>
       <c r="G55" t="n">
-        <v>279.5</v>
+        <v>284.4</v>
       </c>
       <c r="H55" t="n">
-        <v>61.5</v>
+        <v>63.1</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-214.02</v>
+        <v>-71.78</v>
       </c>
       <c r="K55" t="n">
-        <v>326.14</v>
+        <v>389.84</v>
       </c>
       <c r="L55" t="n">
-        <v>390.09</v>
+        <v>396.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10:14:16</t>
+          <t>10:07:34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>6.74</v>
+        <v>6.91</v>
       </c>
       <c r="F56" t="n">
-        <v>16.79</v>
+        <v>16.5</v>
       </c>
       <c r="G56" t="n">
-        <v>305.9</v>
+        <v>270.6</v>
       </c>
       <c r="H56" t="n">
-        <v>92.40000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>-326.25</v>
+        <v>-12.43</v>
       </c>
       <c r="K56" t="n">
-        <v>164.57</v>
+        <v>437.9</v>
       </c>
       <c r="L56" t="n">
-        <v>365.41</v>
+        <v>438.08</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10:16:05</t>
+          <t>10:08:54</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>6.6</v>
+        <v>6.01</v>
       </c>
       <c r="F57" t="n">
-        <v>15.66</v>
+        <v>16.62</v>
       </c>
       <c r="G57" t="n">
-        <v>289</v>
+        <v>280.2</v>
       </c>
       <c r="H57" t="n">
-        <v>86.7</v>
+        <v>43.5</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>-334.03</v>
+        <v>240.81</v>
       </c>
       <c r="K57" t="n">
-        <v>206.84</v>
+        <v>-3.12</v>
       </c>
       <c r="L57" t="n">
-        <v>392.88</v>
+        <v>240.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10:18:20</t>
+          <t>10:09:55</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.44</v>
+        <v>7.3</v>
       </c>
       <c r="F58" t="n">
         <v>16.79</v>
       </c>
       <c r="G58" t="n">
-        <v>273.1</v>
+        <v>273.6</v>
       </c>
       <c r="H58" t="n">
-        <v>18.3</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J58" t="n">
-        <v>-427.55</v>
+        <v>320</v>
       </c>
       <c r="K58" t="n">
-        <v>91.28</v>
+        <v>-387.84</v>
       </c>
       <c r="L58" t="n">
-        <v>437.19</v>
+        <v>502.82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10:28:20</t>
+          <t>10:22:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6.82</v>
+        <v>5.95</v>
       </c>
       <c r="F59" t="n">
         <v>16.79</v>
       </c>
       <c r="G59" t="n">
-        <v>283.7</v>
+        <v>282</v>
       </c>
       <c r="H59" t="n">
-        <v>32.9</v>
+        <v>64.3</v>
       </c>
       <c r="I59" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>32.29</v>
+        <v>-299.18</v>
       </c>
       <c r="K59" t="n">
-        <v>-176.08</v>
+        <v>-310.36</v>
       </c>
       <c r="L59" t="n">
-        <v>179.02</v>
+        <v>431.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10:29:30</t>
+          <t>10:24:22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.14</v>
+        <v>6.33</v>
       </c>
       <c r="F60" t="n">
-        <v>14.51</v>
+        <v>16.79</v>
       </c>
       <c r="G60" t="n">
-        <v>295.3</v>
+        <v>290.5</v>
       </c>
       <c r="H60" t="n">
-        <v>81.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>-108.59</v>
+        <v>3.44</v>
       </c>
       <c r="K60" t="n">
-        <v>35.37</v>
+        <v>157.09</v>
       </c>
       <c r="L60" t="n">
-        <v>114.2</v>
+        <v>157.13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:31:31</t>
+          <t>10:25:19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.51</v>
+        <v>6.92</v>
       </c>
       <c r="F61" t="n">
-        <v>14.72</v>
+        <v>16.79</v>
       </c>
       <c r="G61" t="n">
-        <v>282.6</v>
+        <v>282.5</v>
       </c>
       <c r="H61" t="n">
-        <v>63.9</v>
+        <v>34.6</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>31.11</v>
+        <v>74.38</v>
       </c>
       <c r="K61" t="n">
-        <v>-129.41</v>
+        <v>-33.04</v>
       </c>
       <c r="L61" t="n">
-        <v>133.1</v>
+        <v>81.39</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:36:01</t>
+          <t>10:30:25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.82</v>
+        <v>5.68</v>
       </c>
       <c r="F62" t="n">
-        <v>16.79</v>
+        <v>15.54</v>
       </c>
       <c r="G62" t="n">
-        <v>279.9</v>
+        <v>290.3</v>
       </c>
       <c r="H62" t="n">
-        <v>52</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>-116.91</v>
+        <v>85.16</v>
       </c>
       <c r="K62" t="n">
-        <v>178.14</v>
+        <v>189.79</v>
       </c>
       <c r="L62" t="n">
-        <v>213.08</v>
+        <v>208.02</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:38:08</t>
+          <t>10:31:52</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>6.21</v>
+        <v>7.19</v>
       </c>
       <c r="F63" t="n">
         <v>16.79</v>
       </c>
       <c r="G63" t="n">
-        <v>288.6</v>
+        <v>275.6</v>
       </c>
       <c r="H63" t="n">
-        <v>59.1</v>
+        <v>66.8</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>9.44</v>
+        <v>58.83</v>
       </c>
       <c r="K63" t="n">
-        <v>201.5</v>
+        <v>54.72</v>
       </c>
       <c r="L63" t="n">
-        <v>201.72</v>
+        <v>80.34</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:39:51</t>
+          <t>10:33:10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.83</v>
+        <v>6.82</v>
       </c>
       <c r="F64" t="n">
         <v>16.79</v>
       </c>
       <c r="G64" t="n">
-        <v>281.1</v>
+        <v>290.1</v>
       </c>
       <c r="H64" t="n">
-        <v>27.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-171.78</v>
+        <v>-164.97</v>
       </c>
       <c r="K64" t="n">
-        <v>64.84999999999999</v>
+        <v>-64.31999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>183.61</v>
+        <v>177.07</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:44:29</t>
+          <t>10:39:17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.58</v>
+        <v>6.14</v>
       </c>
       <c r="F65" t="n">
-        <v>15.15</v>
+        <v>16.54</v>
       </c>
       <c r="G65" t="n">
-        <v>277.7</v>
+        <v>279</v>
       </c>
       <c r="H65" t="n">
-        <v>54.8</v>
+        <v>63</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-201.14</v>
+        <v>-140.94</v>
       </c>
       <c r="K65" t="n">
-        <v>27.15</v>
+        <v>172.78</v>
       </c>
       <c r="L65" t="n">
-        <v>202.96</v>
+        <v>222.97</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:46:51</t>
+          <t>10:40:40</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>6.32</v>
+        <v>6.14</v>
       </c>
       <c r="F66" t="n">
-        <v>16.63</v>
+        <v>15.5</v>
       </c>
       <c r="G66" t="n">
-        <v>295.7</v>
+        <v>277.2</v>
       </c>
       <c r="H66" t="n">
-        <v>54.7</v>
+        <v>50.1</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-33.38</v>
+        <v>146.74</v>
       </c>
       <c r="K66" t="n">
-        <v>208.31</v>
+        <v>-145.83</v>
       </c>
       <c r="L66" t="n">
-        <v>210.97</v>
+        <v>206.88</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:47:59</t>
+          <t>10:42:34</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6.54</v>
+        <v>7.17</v>
       </c>
       <c r="F67" t="n">
         <v>16.79</v>
       </c>
       <c r="G67" t="n">
-        <v>282</v>
+        <v>286.9</v>
       </c>
       <c r="H67" t="n">
-        <v>78.8</v>
+        <v>62.4</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>-244.75</v>
+        <v>-218.61</v>
       </c>
       <c r="K67" t="n">
-        <v>-137.64</v>
+        <v>-102.16</v>
       </c>
       <c r="L67" t="n">
-        <v>280.8</v>
+        <v>241.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:52:25</t>
+          <t>10:47:34</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>7.24</v>
+        <v>6.16</v>
       </c>
       <c r="F68" t="n">
         <v>16.79</v>
       </c>
       <c r="G68" t="n">
-        <v>281.8</v>
+        <v>288.4</v>
       </c>
       <c r="H68" t="n">
-        <v>69.5</v>
+        <v>52.1</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>-233.22</v>
+        <v>-232.97</v>
       </c>
       <c r="K68" t="n">
-        <v>-296.62</v>
+        <v>348.98</v>
       </c>
       <c r="L68" t="n">
-        <v>377.33</v>
+        <v>419.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:54:13</t>
+          <t>10:49:22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>7.19</v>
+        <v>6.53</v>
       </c>
       <c r="F69" t="n">
-        <v>16.79</v>
+        <v>16.44</v>
       </c>
       <c r="G69" t="n">
-        <v>294.4</v>
+        <v>277.2</v>
       </c>
       <c r="H69" t="n">
-        <v>54.5</v>
+        <v>29.7</v>
       </c>
       <c r="I69" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J69" t="n">
-        <v>-263.51</v>
+        <v>-371.45</v>
       </c>
       <c r="K69" t="n">
-        <v>-174.86</v>
+        <v>100.8</v>
       </c>
       <c r="L69" t="n">
-        <v>316.25</v>
+        <v>384.88</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:55:24</t>
+          <t>10:51:47</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.98</v>
+        <v>5.67</v>
       </c>
       <c r="F70" t="n">
-        <v>16.79</v>
+        <v>16.13</v>
       </c>
       <c r="G70" t="n">
-        <v>277.6</v>
+        <v>286.3</v>
       </c>
       <c r="H70" t="n">
-        <v>90.2</v>
+        <v>33</v>
       </c>
       <c r="I70" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-89.43000000000001</v>
+        <v>-11.85</v>
       </c>
       <c r="K70" t="n">
-        <v>-325</v>
+        <v>-286</v>
       </c>
       <c r="L70" t="n">
-        <v>337.08</v>
+        <v>286.25</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11:00:18</t>
+          <t>10:57:31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>7.08</v>
+        <v>6.76</v>
       </c>
       <c r="F71" t="n">
         <v>16.79</v>
       </c>
       <c r="G71" t="n">
-        <v>276.6</v>
+        <v>280.4</v>
       </c>
       <c r="H71" t="n">
-        <v>31.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-473.85</v>
+        <v>-238.73</v>
       </c>
       <c r="K71" t="n">
-        <v>48.88</v>
+        <v>-422.41</v>
       </c>
       <c r="L71" t="n">
-        <v>476.36</v>
+        <v>485.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11:02:05</t>
+          <t>10:59:09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.75</v>
+        <v>6.56</v>
       </c>
       <c r="F72" t="n">
-        <v>13.84</v>
+        <v>16.79</v>
       </c>
       <c r="G72" t="n">
-        <v>268.1</v>
+        <v>277.2</v>
       </c>
       <c r="H72" t="n">
-        <v>49.8</v>
+        <v>49.3</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>255.92</v>
+        <v>-407.66</v>
       </c>
       <c r="K72" t="n">
-        <v>230.81</v>
+        <v>394.28</v>
       </c>
       <c r="L72" t="n">
-        <v>344.63</v>
+        <v>567.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11:03:56</t>
+          <t>11:01:31</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>6.35</v>
       </c>
       <c r="F73" t="n">
         <v>16.79</v>
       </c>
       <c r="G73" t="n">
-        <v>293</v>
+        <v>277.5</v>
       </c>
       <c r="H73" t="n">
-        <v>91.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>-474.95</v>
+        <v>-444.01</v>
       </c>
       <c r="K73" t="n">
-        <v>68.20999999999999</v>
+        <v>-207.24</v>
       </c>
       <c r="L73" t="n">
-        <v>479.83</v>
+        <v>489.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11:10:28</t>
+          <t>11:12:04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.35</v>
+        <v>6.14</v>
       </c>
       <c r="F74" t="n">
-        <v>14.77</v>
+        <v>16.79</v>
       </c>
       <c r="G74" t="n">
-        <v>297.7</v>
+        <v>295.5</v>
       </c>
       <c r="H74" t="n">
-        <v>32.8</v>
+        <v>37.6</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-124.45</v>
+        <v>-77.73999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>82.54000000000001</v>
+        <v>117.13</v>
       </c>
       <c r="L74" t="n">
-        <v>149.33</v>
+        <v>140.58</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11:11:55</t>
+          <t>11:13:31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.43</v>
+        <v>7.15</v>
       </c>
       <c r="F75" t="n">
         <v>16.79</v>
       </c>
       <c r="G75" t="n">
-        <v>263.4</v>
+        <v>281.8</v>
       </c>
       <c r="H75" t="n">
-        <v>67.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>9.01</v>
+        <v>-114.22</v>
       </c>
       <c r="K75" t="n">
-        <v>150.92</v>
+        <v>-134.96</v>
       </c>
       <c r="L75" t="n">
-        <v>151.19</v>
+        <v>176.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:13:51</t>
+          <t>11:15:11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>7.79</v>
+        <v>7.35</v>
       </c>
       <c r="F76" t="n">
         <v>16.79</v>
       </c>
       <c r="G76" t="n">
-        <v>274.6</v>
+        <v>285.8</v>
       </c>
       <c r="H76" t="n">
-        <v>98.2</v>
+        <v>97.2</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J76" t="n">
-        <v>-154.74</v>
+        <v>22.32</v>
       </c>
       <c r="K76" t="n">
-        <v>-23.42</v>
+        <v>-119.98</v>
       </c>
       <c r="L76" t="n">
-        <v>156.51</v>
+        <v>122.04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11:19:24</t>
+          <t>11:20:44</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7.34</v>
+        <v>6.55</v>
       </c>
       <c r="F77" t="n">
         <v>16.79</v>
       </c>
       <c r="G77" t="n">
-        <v>280.7</v>
+        <v>290.6</v>
       </c>
       <c r="H77" t="n">
-        <v>57</v>
+        <v>51.8</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-258.72</v>
+        <v>-246.84</v>
       </c>
       <c r="K77" t="n">
-        <v>8.98</v>
+        <v>-29.12</v>
       </c>
       <c r="L77" t="n">
-        <v>258.88</v>
+        <v>248.55</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11:21:34</t>
+          <t>11:22:18</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.29</v>
+        <v>6.9</v>
       </c>
       <c r="F78" t="n">
-        <v>15.27</v>
+        <v>16.79</v>
       </c>
       <c r="G78" t="n">
-        <v>283.3</v>
+        <v>283.7</v>
       </c>
       <c r="H78" t="n">
-        <v>99.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="I78" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J78" t="n">
-        <v>-117.42</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-139.92</v>
+        <v>-191.01</v>
       </c>
       <c r="L78" t="n">
-        <v>182.66</v>
+        <v>208.18</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11:22:25</t>
+          <t>11:23:15</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>6.71</v>
+        <v>7.34</v>
       </c>
       <c r="F79" t="n">
         <v>16.79</v>
       </c>
       <c r="G79" t="n">
-        <v>276.2</v>
+        <v>277</v>
       </c>
       <c r="H79" t="n">
-        <v>62.6</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-184.95</v>
+        <v>204.29</v>
       </c>
       <c r="K79" t="n">
-        <v>-31.23</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>187.57</v>
+        <v>218.64</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11:28:23</t>
+          <t>11:28:05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.3</v>
+        <v>5.61</v>
       </c>
       <c r="F80" t="n">
-        <v>14.45</v>
+        <v>16.34</v>
       </c>
       <c r="G80" t="n">
-        <v>290.5</v>
+        <v>282.3</v>
       </c>
       <c r="H80" t="n">
-        <v>84.09999999999999</v>
+        <v>43</v>
       </c>
       <c r="I80" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-19.99</v>
+        <v>112.8</v>
       </c>
       <c r="K80" t="n">
-        <v>268.24</v>
+        <v>-196.24</v>
       </c>
       <c r="L80" t="n">
-        <v>268.98</v>
+        <v>226.35</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11:30:02</t>
+          <t>11:30:13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.59</v>
+        <v>6.77</v>
       </c>
       <c r="F81" t="n">
-        <v>16.63</v>
+        <v>16.79</v>
       </c>
       <c r="G81" t="n">
-        <v>279.9</v>
+        <v>293.7</v>
       </c>
       <c r="H81" t="n">
-        <v>72.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J81" t="n">
-        <v>-155.73</v>
+        <v>-161.55</v>
       </c>
       <c r="K81" t="n">
-        <v>226.89</v>
+        <v>181.31</v>
       </c>
       <c r="L81" t="n">
-        <v>275.19</v>
+        <v>242.84</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11:30:43</t>
+          <t>11:31:42</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.56</v>
+        <v>7.09</v>
       </c>
       <c r="F82" t="n">
-        <v>16.41</v>
+        <v>16.79</v>
       </c>
       <c r="G82" t="n">
-        <v>294.9</v>
+        <v>270.6</v>
       </c>
       <c r="H82" t="n">
-        <v>79.59999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J82" t="n">
-        <v>-359.3</v>
+        <v>-225.53</v>
       </c>
       <c r="K82" t="n">
-        <v>-91.55</v>
+        <v>-57.54</v>
       </c>
       <c r="L82" t="n">
-        <v>370.78</v>
+        <v>232.76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:35:25</t>
+          <t>11:36:52</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>7.3</v>
+        <v>6.12</v>
       </c>
       <c r="F83" t="n">
-        <v>16.79</v>
+        <v>16.72</v>
       </c>
       <c r="G83" t="n">
-        <v>277.8</v>
+        <v>285.7</v>
       </c>
       <c r="H83" t="n">
-        <v>75.40000000000001</v>
+        <v>54.6</v>
       </c>
       <c r="I83" t="n">
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>-151.75</v>
+        <v>8.48</v>
       </c>
       <c r="K83" t="n">
-        <v>-366.9</v>
+        <v>-317.06</v>
       </c>
       <c r="L83" t="n">
-        <v>397.04</v>
+        <v>317.18</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:37:26</t>
+          <t>11:39:06</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7.57</v>
+        <v>6.42</v>
       </c>
       <c r="F84" t="n">
         <v>16.79</v>
       </c>
       <c r="G84" t="n">
-        <v>271.9</v>
+        <v>286.9</v>
       </c>
       <c r="H84" t="n">
-        <v>73.2</v>
+        <v>36.2</v>
       </c>
       <c r="I84" t="n">
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-376.39</v>
+        <v>15.71</v>
       </c>
       <c r="K84" t="n">
-        <v>-117.68</v>
+        <v>401.78</v>
       </c>
       <c r="L84" t="n">
-        <v>394.36</v>
+        <v>402.09</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:39:43</t>
+          <t>11:40:51</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>8.35</v>
+        <v>6.85</v>
       </c>
       <c r="F85" t="n">
         <v>16.79</v>
       </c>
       <c r="G85" t="n">
-        <v>269.5</v>
+        <v>290.9</v>
       </c>
       <c r="H85" t="n">
-        <v>80.09999999999999</v>
+        <v>55.3</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-220.83</v>
+        <v>-98.81999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>-285.35</v>
+        <v>-396.09</v>
       </c>
       <c r="L85" t="n">
-        <v>360.82</v>
+        <v>408.23</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:44:21</t>
+          <t>11:46:04</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>7.37</v>
+        <v>6.95</v>
       </c>
       <c r="F86" t="n">
         <v>16.79</v>
       </c>
       <c r="G86" t="n">
-        <v>293.9</v>
+        <v>276.3</v>
       </c>
       <c r="H86" t="n">
-        <v>55.9</v>
+        <v>42</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J86" t="n">
-        <v>-329.78</v>
+        <v>-235.38</v>
       </c>
       <c r="K86" t="n">
-        <v>-239.6</v>
+        <v>344.34</v>
       </c>
       <c r="L86" t="n">
-        <v>407.63</v>
+        <v>417.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:46:24</t>
+          <t>11:48:37</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.55</v>
+        <v>6.34</v>
       </c>
       <c r="F87" t="n">
-        <v>16.79</v>
+        <v>14.99</v>
       </c>
       <c r="G87" t="n">
-        <v>286.2</v>
+        <v>278.6</v>
       </c>
       <c r="H87" t="n">
-        <v>65.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="I87" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J87" t="n">
-        <v>-181.22</v>
+        <v>-342.39</v>
       </c>
       <c r="K87" t="n">
-        <v>-430.61</v>
+        <v>-298.83</v>
       </c>
       <c r="L87" t="n">
-        <v>467.19</v>
+        <v>454.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:47:38</t>
+          <t>11:50:17</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.2</v>
+        <v>6.87</v>
       </c>
       <c r="F88" t="n">
-        <v>15.61</v>
+        <v>16.79</v>
       </c>
       <c r="G88" t="n">
-        <v>280.2</v>
+        <v>291.2</v>
       </c>
       <c r="H88" t="n">
-        <v>65.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-138.52</v>
+        <v>366.88</v>
       </c>
       <c r="K88" t="n">
-        <v>-411.42</v>
+        <v>255.37</v>
       </c>
       <c r="L88" t="n">
-        <v>434.11</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>45.63</v>
+        <v>52.63</v>
       </c>
       <c r="K14" t="n">
-        <v>85.98999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="L14" t="n">
-        <v>97.34999999999999</v>
+        <v>112.29</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>69.02</v>
+        <v>78.98</v>
       </c>
       <c r="K15" t="n">
-        <v>10.12</v>
+        <v>11.58</v>
       </c>
       <c r="L15" t="n">
-        <v>69.76000000000001</v>
+        <v>79.81999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>10.29</v>
+        <v>12.06</v>
       </c>
       <c r="K16" t="n">
-        <v>65.58</v>
+        <v>76.81</v>
       </c>
       <c r="L16" t="n">
-        <v>66.38</v>
+        <v>77.75</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-57.65</v>
+        <v>-70.28</v>
       </c>
       <c r="K17" t="n">
-        <v>-63.65</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>85.88</v>
+        <v>104.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>63.94</v>
+        <v>84.39</v>
       </c>
       <c r="K18" t="n">
-        <v>-22.33</v>
+        <v>-29.47</v>
       </c>
       <c r="L18" t="n">
-        <v>67.73</v>
+        <v>89.39</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>70.54000000000001</v>
+        <v>82.03</v>
       </c>
       <c r="K19" t="n">
-        <v>39.51</v>
+        <v>45.94</v>
       </c>
       <c r="L19" t="n">
-        <v>80.84999999999999</v>
+        <v>94.02</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>53.5</v>
+        <v>65.7</v>
       </c>
       <c r="K20" t="n">
-        <v>132.45</v>
+        <v>162.64</v>
       </c>
       <c r="L20" t="n">
-        <v>142.85</v>
+        <v>175.41</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-68.18000000000001</v>
+        <v>-92.95999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-114.42</v>
+        <v>-156.02</v>
       </c>
       <c r="L21" t="n">
-        <v>133.19</v>
+        <v>181.62</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>63.34</v>
+        <v>80.55</v>
       </c>
       <c r="K22" t="n">
-        <v>-134.94</v>
+        <v>-171.6</v>
       </c>
       <c r="L22" t="n">
-        <v>149.07</v>
+        <v>189.56</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-33.39</v>
+        <v>-44.67</v>
       </c>
       <c r="K23" t="n">
-        <v>158.75</v>
+        <v>212.36</v>
       </c>
       <c r="L23" t="n">
-        <v>162.22</v>
+        <v>217.01</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-17.79</v>
+        <v>-26.69</v>
       </c>
       <c r="K24" t="n">
-        <v>-140.83</v>
+        <v>-211.22</v>
       </c>
       <c r="L24" t="n">
-        <v>141.95</v>
+        <v>212.9</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-132.1</v>
+        <v>-188.33</v>
       </c>
       <c r="K25" t="n">
-        <v>140.46</v>
+        <v>200.25</v>
       </c>
       <c r="L25" t="n">
-        <v>192.82</v>
+        <v>274.9</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-261.96</v>
+        <v>-399.4</v>
       </c>
       <c r="K26" t="n">
-        <v>34.88</v>
+        <v>53.17</v>
       </c>
       <c r="L26" t="n">
-        <v>264.27</v>
+        <v>402.92</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-173.62</v>
+        <v>-243.57</v>
       </c>
       <c r="K27" t="n">
-        <v>315.58</v>
+        <v>442.72</v>
       </c>
       <c r="L27" t="n">
-        <v>360.19</v>
+        <v>505.3</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-52.11</v>
+        <v>-72.51000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>410.94</v>
+        <v>571.77</v>
       </c>
       <c r="L28" t="n">
-        <v>414.23</v>
+        <v>576.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="K29" t="n">
-        <v>81.48999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>81.48999999999999</v>
+        <v>99.16</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>88.76000000000001</v>
+        <v>94.83</v>
       </c>
       <c r="K30" t="n">
-        <v>45.99</v>
+        <v>49.14</v>
       </c>
       <c r="L30" t="n">
-        <v>99.97</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>68.8</v>
+        <v>81.75</v>
       </c>
       <c r="K31" t="n">
-        <v>-38.91</v>
+        <v>-46.23</v>
       </c>
       <c r="L31" t="n">
-        <v>79.04000000000001</v>
+        <v>93.92</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-72.54000000000001</v>
+        <v>-86.79000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-70.06</v>
+        <v>-83.81</v>
       </c>
       <c r="L32" t="n">
-        <v>100.85</v>
+        <v>120.65</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-22.53</v>
+        <v>-29.95</v>
       </c>
       <c r="K33" t="n">
-        <v>67.48</v>
+        <v>89.72</v>
       </c>
       <c r="L33" t="n">
-        <v>71.15000000000001</v>
+        <v>94.58</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>19.52</v>
+        <v>25.13</v>
       </c>
       <c r="K34" t="n">
-        <v>-76.18000000000001</v>
+        <v>-98.08</v>
       </c>
       <c r="L34" t="n">
-        <v>78.64</v>
+        <v>101.24</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-178.08</v>
+        <v>-213.98</v>
       </c>
       <c r="K35" t="n">
-        <v>-152.11</v>
+        <v>-182.78</v>
       </c>
       <c r="L35" t="n">
-        <v>234.2</v>
+        <v>281.42</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-128.86</v>
+        <v>-163.94</v>
       </c>
       <c r="K36" t="n">
-        <v>111.64</v>
+        <v>142.04</v>
       </c>
       <c r="L36" t="n">
-        <v>170.49</v>
+        <v>216.92</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-20.68</v>
+        <v>-27.02</v>
       </c>
       <c r="K37" t="n">
-        <v>-135.68</v>
+        <v>-177.24</v>
       </c>
       <c r="L37" t="n">
-        <v>137.25</v>
+        <v>179.29</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-196.33</v>
+        <v>-254.42</v>
       </c>
       <c r="K38" t="n">
-        <v>263.09</v>
+        <v>340.94</v>
       </c>
       <c r="L38" t="n">
-        <v>328.27</v>
+        <v>425.41</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-271.95</v>
+        <v>-374.51</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.25</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>272.03</v>
+        <v>374.61</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-197.76</v>
+        <v>-297.43</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.17</v>
+        <v>-1.77</v>
       </c>
       <c r="L40" t="n">
-        <v>197.76</v>
+        <v>297.43</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-496.89</v>
+        <v>-636.03</v>
       </c>
       <c r="K41" t="n">
-        <v>360.71</v>
+        <v>461.73</v>
       </c>
       <c r="L41" t="n">
-        <v>614.01</v>
+        <v>785.96</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-168.23</v>
+        <v>-245.04</v>
       </c>
       <c r="K42" t="n">
-        <v>-215.59</v>
+        <v>-314.02</v>
       </c>
       <c r="L42" t="n">
-        <v>273.46</v>
+        <v>398.31</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-105.01</v>
+        <v>-140.34</v>
       </c>
       <c r="K43" t="n">
-        <v>468.57</v>
+        <v>626.21</v>
       </c>
       <c r="L43" t="n">
-        <v>480.2</v>
+        <v>641.75</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-38.9</v>
+        <v>-48.55</v>
       </c>
       <c r="K44" t="n">
-        <v>-33.82</v>
+        <v>-42.2</v>
       </c>
       <c r="L44" t="n">
-        <v>51.54</v>
+        <v>64.33</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-70.52</v>
+        <v>-80.86</v>
       </c>
       <c r="K45" t="n">
-        <v>-116.98</v>
+        <v>-134.14</v>
       </c>
       <c r="L45" t="n">
-        <v>136.59</v>
+        <v>156.63</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>51</v>
+        <v>64.83</v>
       </c>
       <c r="K46" t="n">
-        <v>-44.26</v>
+        <v>-56.27</v>
       </c>
       <c r="L46" t="n">
-        <v>67.53</v>
+        <v>85.84999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-73.28</v>
+        <v>-99.18000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.76</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>73.59</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-22.81</v>
+        <v>-30.43</v>
       </c>
       <c r="K48" t="n">
-        <v>79.02</v>
+        <v>105.41</v>
       </c>
       <c r="L48" t="n">
-        <v>82.25</v>
+        <v>109.71</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>45.84</v>
+        <v>61.26</v>
       </c>
       <c r="K49" t="n">
-        <v>13.86</v>
+        <v>18.53</v>
       </c>
       <c r="L49" t="n">
-        <v>47.89</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-29.03</v>
+        <v>-34.34</v>
       </c>
       <c r="K50" t="n">
-        <v>244.11</v>
+        <v>288.76</v>
       </c>
       <c r="L50" t="n">
-        <v>245.82</v>
+        <v>290.79</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>188.45</v>
+        <v>237.21</v>
       </c>
       <c r="K51" t="n">
-        <v>-58.14</v>
+        <v>-73.18000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>197.21</v>
+        <v>248.24</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>134.26</v>
+        <v>181.74</v>
       </c>
       <c r="K52" t="n">
-        <v>62.13</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>147.94</v>
+        <v>200.25</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-308.2</v>
+        <v>-382.03</v>
       </c>
       <c r="K53" t="n">
-        <v>-251.54</v>
+        <v>-311.8</v>
       </c>
       <c r="L53" t="n">
-        <v>397.82</v>
+        <v>493.12</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-171.51</v>
+        <v>-227.86</v>
       </c>
       <c r="K54" t="n">
-        <v>-211.52</v>
+        <v>-281.01</v>
       </c>
       <c r="L54" t="n">
-        <v>272.31</v>
+        <v>361.78</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-196.9</v>
+        <v>-278.06</v>
       </c>
       <c r="K55" t="n">
-        <v>145.12</v>
+        <v>204.93</v>
       </c>
       <c r="L55" t="n">
-        <v>244.6</v>
+        <v>345.42</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-232.38</v>
+        <v>-343.38</v>
       </c>
       <c r="K56" t="n">
-        <v>-249.8</v>
+        <v>-369.13</v>
       </c>
       <c r="L56" t="n">
-        <v>341.17</v>
+        <v>504.15</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>30.61</v>
+        <v>43.54</v>
       </c>
       <c r="K57" t="n">
-        <v>357.78</v>
+        <v>508.91</v>
       </c>
       <c r="L57" t="n">
-        <v>359.09</v>
+        <v>510.76</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>443.01</v>
+        <v>596.86</v>
       </c>
       <c r="K58" t="n">
-        <v>286.33</v>
+        <v>385.77</v>
       </c>
       <c r="L58" t="n">
-        <v>527.49</v>
+        <v>710.6799999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-86.44</v>
+        <v>-100.16</v>
       </c>
       <c r="K59" t="n">
-        <v>21.78</v>
+        <v>25.23</v>
       </c>
       <c r="L59" t="n">
-        <v>89.14</v>
+        <v>103.29</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-85.8</v>
+        <v>-101.18</v>
       </c>
       <c r="K60" t="n">
-        <v>24.16</v>
+        <v>28.49</v>
       </c>
       <c r="L60" t="n">
-        <v>89.13</v>
+        <v>105.12</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-54.22</v>
+        <v>-68.8</v>
       </c>
       <c r="K61" t="n">
-        <v>36.8</v>
+        <v>46.69</v>
       </c>
       <c r="L61" t="n">
-        <v>65.53</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-72.17</v>
+        <v>-100.25</v>
       </c>
       <c r="K62" t="n">
-        <v>28.32</v>
+        <v>39.33</v>
       </c>
       <c r="L62" t="n">
-        <v>77.52</v>
+        <v>107.69</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>30.05</v>
+        <v>35.57</v>
       </c>
       <c r="K63" t="n">
-        <v>129.28</v>
+        <v>153.02</v>
       </c>
       <c r="L63" t="n">
-        <v>132.73</v>
+        <v>157.1</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-114.2</v>
+        <v>-136.89</v>
       </c>
       <c r="K64" t="n">
-        <v>-53.09</v>
+        <v>-63.63</v>
       </c>
       <c r="L64" t="n">
-        <v>125.93</v>
+        <v>150.96</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-139.69</v>
+        <v>-182.22</v>
       </c>
       <c r="K65" t="n">
-        <v>28.55</v>
+        <v>37.25</v>
       </c>
       <c r="L65" t="n">
-        <v>142.57</v>
+        <v>185.99</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>55.68</v>
+        <v>69.09</v>
       </c>
       <c r="K66" t="n">
-        <v>207.86</v>
+        <v>257.91</v>
       </c>
       <c r="L66" t="n">
-        <v>215.19</v>
+        <v>267</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="K67" t="n">
-        <v>-149.52</v>
+        <v>-188.28</v>
       </c>
       <c r="L67" t="n">
-        <v>149.52</v>
+        <v>188.28</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-273.16</v>
+        <v>-386.62</v>
       </c>
       <c r="K68" t="n">
-        <v>-113.76</v>
+        <v>-161.01</v>
       </c>
       <c r="L68" t="n">
-        <v>295.9</v>
+        <v>418.81</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>4.93</v>
+        <v>7.15</v>
       </c>
       <c r="K69" t="n">
-        <v>-193.63</v>
+        <v>-280.6</v>
       </c>
       <c r="L69" t="n">
-        <v>193.69</v>
+        <v>280.69</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>263.26</v>
+        <v>358.67</v>
       </c>
       <c r="K70" t="n">
-        <v>-121.55</v>
+        <v>-165.6</v>
       </c>
       <c r="L70" t="n">
-        <v>289.96</v>
+        <v>395.05</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-447.2</v>
+        <v>-608.58</v>
       </c>
       <c r="K71" t="n">
-        <v>-73.37</v>
+        <v>-99.84999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>453.18</v>
+        <v>616.71</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-328.53</v>
+        <v>-428.21</v>
       </c>
       <c r="K72" t="n">
-        <v>-436.15</v>
+        <v>-568.48</v>
       </c>
       <c r="L72" t="n">
-        <v>546.04</v>
+        <v>711.71</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-257.98</v>
+        <v>-357.2</v>
       </c>
       <c r="K73" t="n">
-        <v>356.14</v>
+        <v>493.1</v>
       </c>
       <c r="L73" t="n">
-        <v>439.76</v>
+        <v>608.89</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.02</v>
+        <v>-1.31</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.88</v>
+        <v>-7.6</v>
       </c>
       <c r="L74" t="n">
-        <v>5.97</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-83.65000000000001</v>
+        <v>-99.75</v>
       </c>
       <c r="K75" t="n">
-        <v>-32.96</v>
+        <v>-39.3</v>
       </c>
       <c r="L75" t="n">
-        <v>89.91</v>
+        <v>107.21</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>44.32</v>
+        <v>52.62</v>
       </c>
       <c r="K76" t="n">
-        <v>-73.48</v>
+        <v>-87.23999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>85.81</v>
+        <v>101.88</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-21.74</v>
+        <v>-29.69</v>
       </c>
       <c r="K77" t="n">
-        <v>45.98</v>
+        <v>62.77</v>
       </c>
       <c r="L77" t="n">
-        <v>50.86</v>
+        <v>69.43000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>23.08</v>
+        <v>29.51</v>
       </c>
       <c r="K78" t="n">
-        <v>92.2</v>
+        <v>117.87</v>
       </c>
       <c r="L78" t="n">
-        <v>95.05</v>
+        <v>121.51</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-78.23999999999999</v>
+        <v>-95.66</v>
       </c>
       <c r="K79" t="n">
-        <v>-88.8</v>
+        <v>-108.56</v>
       </c>
       <c r="L79" t="n">
-        <v>118.35</v>
+        <v>144.69</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>111.92</v>
+        <v>153.88</v>
       </c>
       <c r="K80" t="n">
-        <v>83.18000000000001</v>
+        <v>114.36</v>
       </c>
       <c r="L80" t="n">
-        <v>139.44</v>
+        <v>191.72</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>62.3</v>
+        <v>86.16</v>
       </c>
       <c r="K81" t="n">
-        <v>-116.01</v>
+        <v>-160.44</v>
       </c>
       <c r="L81" t="n">
-        <v>131.68</v>
+        <v>182.11</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>7.89</v>
+        <v>11.07</v>
       </c>
       <c r="K82" t="n">
-        <v>126.47</v>
+        <v>177.28</v>
       </c>
       <c r="L82" t="n">
-        <v>126.72</v>
+        <v>177.63</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>125.24</v>
+        <v>191.81</v>
       </c>
       <c r="K83" t="n">
-        <v>67.63</v>
+        <v>103.58</v>
       </c>
       <c r="L83" t="n">
-        <v>142.33</v>
+        <v>218</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>198.59</v>
+        <v>291.07</v>
       </c>
       <c r="K84" t="n">
-        <v>145.11</v>
+        <v>212.69</v>
       </c>
       <c r="L84" t="n">
-        <v>245.96</v>
+        <v>360.49</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-196.12</v>
+        <v>-270.54</v>
       </c>
       <c r="K85" t="n">
-        <v>-241.4</v>
+        <v>-333.01</v>
       </c>
       <c r="L85" t="n">
-        <v>311.02</v>
+        <v>429.06</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-142.46</v>
+        <v>-194.12</v>
       </c>
       <c r="K86" t="n">
-        <v>-446.82</v>
+        <v>-608.84</v>
       </c>
       <c r="L86" t="n">
-        <v>468.99</v>
+        <v>639.03</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-34.45</v>
+        <v>-47.78</v>
       </c>
       <c r="K87" t="n">
-        <v>456.46</v>
+        <v>633.13</v>
       </c>
       <c r="L87" t="n">
-        <v>457.76</v>
+        <v>634.9299999999999</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>287.93</v>
+        <v>455.31</v>
       </c>
       <c r="K88" t="n">
-        <v>156.47</v>
+        <v>247.44</v>
       </c>
       <c r="L88" t="n">
-        <v>327.7</v>
+        <v>518.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-24.xlsx
+++ b/output/2024-10-24.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>52.63</v>
+        <v>95.23</v>
       </c>
       <c r="K14" t="n">
-        <v>99.19</v>
+        <v>179.47</v>
       </c>
       <c r="L14" t="n">
-        <v>112.29</v>
+        <v>203.17</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>78.98</v>
+        <v>109.49</v>
       </c>
       <c r="K15" t="n">
-        <v>11.58</v>
+        <v>16.05</v>
       </c>
       <c r="L15" t="n">
-        <v>79.81999999999999</v>
+        <v>110.66</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>12.06</v>
+        <v>19.01</v>
       </c>
       <c r="K16" t="n">
-        <v>76.81</v>
+        <v>121.11</v>
       </c>
       <c r="L16" t="n">
-        <v>77.75</v>
+        <v>122.59</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-70.28</v>
+        <v>-103.85</v>
       </c>
       <c r="K17" t="n">
-        <v>-77.59999999999999</v>
+        <v>-114.67</v>
       </c>
       <c r="L17" t="n">
-        <v>104.69</v>
+        <v>154.71</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>84.39</v>
+        <v>121.11</v>
       </c>
       <c r="K18" t="n">
-        <v>-29.47</v>
+        <v>-42.29</v>
       </c>
       <c r="L18" t="n">
-        <v>89.39</v>
+        <v>128.28</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>82.03</v>
+        <v>110.07</v>
       </c>
       <c r="K19" t="n">
-        <v>45.94</v>
+        <v>61.65</v>
       </c>
       <c r="L19" t="n">
-        <v>94.02</v>
+        <v>126.16</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>0.95</v>
+        <v>1.74</v>
       </c>
       <c r="K29" t="n">
-        <v>99.15000000000001</v>
+        <v>181.86</v>
       </c>
       <c r="L29" t="n">
-        <v>99.16</v>
+        <v>181.87</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>94.83</v>
+        <v>153.43</v>
       </c>
       <c r="K30" t="n">
-        <v>49.14</v>
+        <v>79.5</v>
       </c>
       <c r="L30" t="n">
-        <v>106.8</v>
+        <v>172.8</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>81.75</v>
+        <v>142.12</v>
       </c>
       <c r="K31" t="n">
-        <v>-46.23</v>
+        <v>-80.38</v>
       </c>
       <c r="L31" t="n">
-        <v>93.92</v>
+        <v>163.28</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-86.79000000000001</v>
+        <v>-134.85</v>
       </c>
       <c r="K32" t="n">
-        <v>-83.81</v>
+        <v>-130.23</v>
       </c>
       <c r="L32" t="n">
-        <v>120.65</v>
+        <v>187.46</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-29.95</v>
+        <v>-47.06</v>
       </c>
       <c r="K33" t="n">
-        <v>89.72</v>
+        <v>140.98</v>
       </c>
       <c r="L33" t="n">
-        <v>94.58</v>
+        <v>148.63</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>25.13</v>
+        <v>38.82</v>
       </c>
       <c r="K34" t="n">
-        <v>-98.08</v>
+        <v>-151.53</v>
       </c>
       <c r="L34" t="n">
-        <v>101.24</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-48.55</v>
+        <v>-79.27</v>
       </c>
       <c r="K44" t="n">
-        <v>-42.2</v>
+        <v>-68.91</v>
       </c>
       <c r="L44" t="n">
-        <v>64.33</v>
+        <v>105.04</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-80.86</v>
+        <v>-175.33</v>
       </c>
       <c r="K45" t="n">
-        <v>-134.14</v>
+        <v>-290.85</v>
       </c>
       <c r="L45" t="n">
-        <v>156.63</v>
+        <v>339.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>64.83</v>
+        <v>134.21</v>
       </c>
       <c r="K46" t="n">
-        <v>-56.27</v>
+        <v>-116.48</v>
       </c>
       <c r="L46" t="n">
-        <v>85.84999999999999</v>
+        <v>177.7</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-99.18000000000001</v>
+        <v>-153.24</v>
       </c>
       <c r="K47" t="n">
-        <v>-9.140000000000001</v>
+        <v>-14.13</v>
       </c>
       <c r="L47" t="n">
-        <v>99.61</v>
+        <v>153.89</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-30.43</v>
+        <v>-50.2</v>
       </c>
       <c r="K48" t="n">
-        <v>105.41</v>
+        <v>173.89</v>
       </c>
       <c r="L48" t="n">
-        <v>109.71</v>
+        <v>180.99</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>61.26</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>18.53</v>
+        <v>26.32</v>
       </c>
       <c r="L49" t="n">
-        <v>64</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-100.16</v>
+        <v>-179.66</v>
       </c>
       <c r="K59" t="n">
-        <v>25.23</v>
+        <v>45.26</v>
       </c>
       <c r="L59" t="n">
-        <v>103.29</v>
+        <v>185.27</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-101.18</v>
+        <v>-203.55</v>
       </c>
       <c r="K60" t="n">
-        <v>28.49</v>
+        <v>57.32</v>
       </c>
       <c r="L60" t="n">
-        <v>105.12</v>
+        <v>211.47</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-68.8</v>
+        <v>-133.34</v>
       </c>
       <c r="K61" t="n">
-        <v>46.69</v>
+        <v>90.5</v>
       </c>
       <c r="L61" t="n">
-        <v>83.15000000000001</v>
+        <v>161.15</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-100.25</v>
+        <v>-182.02</v>
       </c>
       <c r="K62" t="n">
-        <v>39.33</v>
+        <v>71.41</v>
       </c>
       <c r="L62" t="n">
-        <v>107.69</v>
+        <v>195.52</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>35.57</v>
+        <v>57.8</v>
       </c>
       <c r="K63" t="n">
-        <v>153.02</v>
+        <v>248.64</v>
       </c>
       <c r="L63" t="n">
-        <v>157.1</v>
+        <v>255.27</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-136.89</v>
+        <v>-229.55</v>
       </c>
       <c r="K64" t="n">
-        <v>-63.63</v>
+        <v>-106.71</v>
       </c>
       <c r="L64" t="n">
-        <v>150.96</v>
+        <v>253.14</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.31</v>
+        <v>-2.66</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.6</v>
+        <v>-15.42</v>
       </c>
       <c r="L74" t="n">
-        <v>7.71</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-99.75</v>
+        <v>-191.43</v>
       </c>
       <c r="K75" t="n">
-        <v>-39.3</v>
+        <v>-75.42</v>
       </c>
       <c r="L75" t="n">
-        <v>107.21</v>
+        <v>205.75</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>52.62</v>
+        <v>103.83</v>
       </c>
       <c r="K76" t="n">
-        <v>-87.23999999999999</v>
+        <v>-172.15</v>
       </c>
       <c r="L76" t="n">
-        <v>101.88</v>
+        <v>201.04</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-29.69</v>
+        <v>-44.57</v>
       </c>
       <c r="K77" t="n">
-        <v>62.77</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>69.43000000000001</v>
+        <v>104.25</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>29.51</v>
+        <v>50.7</v>
       </c>
       <c r="K78" t="n">
-        <v>117.87</v>
+        <v>202.52</v>
       </c>
       <c r="L78" t="n">
-        <v>121.51</v>
+        <v>208.77</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-95.66</v>
+        <v>-171.88</v>
       </c>
       <c r="K79" t="n">
-        <v>-108.56</v>
+        <v>-195.08</v>
       </c>
       <c r="L79" t="n">
-        <v>144.69</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80">
